--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agentes_y_Artistas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Organizaciones" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lugares_y_Sedes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesauro_SKOS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formacion_Academica" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trayectoria_Laboral" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publicaciones" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exposiciones_Curadurias" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyectos_y_Fondos" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medios_y_Congresos" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portafolio_Digital_Web" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relaciones_Grafo_LOD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Agentes_y_Artistas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Organizaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Lugares_y_Sedes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tesauro_SKOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Formacion_Academica" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Trayectoria_Laboral" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Publicaciones" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Exposiciones_Curadurias" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Proyectos_y_Fondos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Medios_y_Congresos" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Portafolio_Digital_Web" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Relaciones_Grafo_LOD" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10030,7 +10030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10084,6 +10084,21 @@
           <t>wikidata_id</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>parent_org_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>is_user_primary</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>precision_type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10130,6 +10145,19 @@
           <t>Q1138865</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10176,6 +10204,19 @@
           <t>Q3329153</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ORG_0001</t>
+        </is>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10222,6 +10263,19 @@
           <t>Q232438</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ORG_0034</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10268,6 +10322,19 @@
           <t>Q1465225</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ORG_0004</t>
+        </is>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10314,6 +10381,19 @@
           <t>Q219615</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ORG_0005</t>
+        </is>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10360,6 +10440,19 @@
           <t>Q5761404</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ORG_0006</t>
+        </is>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10406,6 +10499,19 @@
           <t>Q50682283</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ORG_0008</t>
+        </is>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10452,6 +10558,19 @@
           <t>Q7894229</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ORG_0009</t>
+        </is>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10498,6 +10617,19 @@
           <t>Q1138767</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ORG_0010</t>
+        </is>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10544,6 +10676,19 @@
           <t>Q6034177</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ORG_0011</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10590,6 +10735,19 @@
           <t>Q6034346</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ORG_0012</t>
+        </is>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10636,6 +10794,19 @@
           <t>Q54865181</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ORG_0013</t>
+        </is>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10682,6 +10853,19 @@
           <t>Q13371</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ORG_0015</t>
+        </is>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10728,6 +10912,19 @@
           <t>Q124618790</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ORG_0016</t>
+        </is>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10774,6 +10971,19 @@
           <t>Q6940540</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ORG_0018</t>
+        </is>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10820,6 +11030,19 @@
           <t>Q1464673</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ORG_0019</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10866,6 +11089,19 @@
           <t>Q16609935</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ORG_0020</t>
+        </is>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10912,6 +11148,19 @@
           <t>Q7894297</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ORG_0021</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10958,6 +11207,19 @@
           <t>Q5961605</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ORG_0022</t>
+        </is>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11004,6 +11266,19 @@
           <t>Q5761159</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ORG_0023</t>
+        </is>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11050,6 +11325,19 @@
           <t>Q5763160</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ORG_0024</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11096,6 +11384,19 @@
           <t>Q2931448</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ORG_0018</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11142,6 +11443,19 @@
           <t>Q2006767</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ORG_0026</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11188,6 +11502,19 @@
           <t>Q6033842</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ORG_0027</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11234,6 +11561,19 @@
           <t>Q5047879</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ORG_0028</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11280,6 +11620,14 @@
           <t>Q1050516</t>
         </is>
       </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11326,6 +11674,14 @@
           <t>Q201016</t>
         </is>
       </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11372,6 +11728,14 @@
           <t>Q7126294</t>
         </is>
       </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11418,6 +11782,19 @@
           <t>Q6034388</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ORG_0018</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11464,6 +11841,14 @@
           <t>Q2931448</t>
         </is>
       </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11510,6 +11895,14 @@
           <t>Q3691</t>
         </is>
       </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11556,6 +11949,14 @@
           <t>Q56125</t>
         </is>
       </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11602,6 +12003,14 @@
           <t>Q14424</t>
         </is>
       </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11648,6 +12057,14 @@
           <t>Q51594</t>
         </is>
       </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11694,6 +12111,14 @@
           <t>Q14484</t>
         </is>
       </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11740,6 +12165,19 @@
           <t>Q51079</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ORG_0009</t>
+        </is>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -11786,6 +12224,14 @@
           <t>Q13063</t>
         </is>
       </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11832,6 +12278,14 @@
           <t>Q51048</t>
         </is>
       </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>centroid</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11878,6 +12332,19 @@
           <t>Q6940509</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ORG_0039</t>
+        </is>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11924,6 +12391,19 @@
           <t>Q1142270</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ORG_0030</t>
+        </is>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11970,6 +12450,19 @@
           <t>Q3551676</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ORG_0032</t>
+        </is>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12016,6 +12509,19 @@
           <t>Q287900</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ORG_0033</t>
+        </is>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12062,6 +12568,19 @@
           <t>Q7894220</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ORG_0034</t>
+        </is>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12108,6 +12627,19 @@
           <t>Q50682284</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ORG_0035</t>
+        </is>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12154,6 +12686,19 @@
           <t>Q124618791</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ORG_0036</t>
+        </is>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12200,6 +12745,19 @@
           <t>Q124618792</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ORG_0003</t>
+        </is>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12246,6 +12804,19 @@
           <t>Q5918342</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ORG_0038</t>
+        </is>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12292,6 +12863,19 @@
           <t>Q232438</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ORG_0037</t>
+        </is>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12338,6 +12922,19 @@
           <t>Q2478544</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ORG_0029</t>
+        </is>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12384,6 +12981,14 @@
           <t>Q7203673</t>
         </is>
       </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>approximate</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12430,6 +13035,14 @@
           <t>Q124618795</t>
         </is>
       </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12476,6 +13089,14 @@
           <t>Q6033182</t>
         </is>
       </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12522,6 +13143,14 @@
           <t>Q61</t>
         </is>
       </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12568,6 +13197,14 @@
           <t>Q38</t>
         </is>
       </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12614,6 +13251,14 @@
           <t>Q954318</t>
         </is>
       </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12660,6 +13305,19 @@
           <t>Q124618814</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ORG_0040</t>
+        </is>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12704,6 +13362,14 @@
       <c r="J58" t="inlineStr">
         <is>
           <t>Q124618815</t>
+        </is>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>exact</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -639,11 +639,6 @@
           <t>https://uai.academia.edu/MarcelaDrien</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Q124618797</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -716,11 +711,6 @@
           <t>https://uc-cl.academia.edu/ManuelAlvaradoCornejo</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Q124618798</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -793,11 +783,6 @@
           <t>https://rileditores.com</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Q124618799</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -870,11 +855,6 @@
           <t>https://artesliberales.uai.cl</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Q124618800</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -947,11 +927,6 @@
           <t>https://anid.cl</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Q124618801</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1024,11 +999,6 @@
           <t>https://museodelmundo.org</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Q124618802</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1101,11 +1071,6 @@
           <t>https://callejera-madrid.vercel.app</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Q124618803</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1178,11 +1143,6 @@
           <t>https://mac.uchile.cl</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Q124618804</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1255,11 +1215,6 @@
           <t>https://mac.uchile.cl</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Q124618805</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1409,11 +1364,6 @@
           <t>https://uai.cl</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Q124618806</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1486,11 +1436,6 @@
           <t>https://uai.cl</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Q124618807</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1794,11 +1739,6 @@
           <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39977.html</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Q124618808</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2410,11 +2350,6 @@
           <t>https://www.mnba.gob.cl</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Q124618809</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2487,11 +2422,6 @@
           <t>https://www.mnba.gob.cl</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Q124618810</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2718,11 +2648,6 @@
           <t>https://www.mnba.gob.cl</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Q124618811</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2795,11 +2720,6 @@
           <t>https://cceguatemala.org</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Q124618812</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2872,11 +2792,6 @@
           <t>https://cceguatemala.org</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Q124618813</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -3565,11 +3480,6 @@
           <t>https://soledadpinto.com</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Q124618816</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -3642,11 +3552,6 @@
           <t>https://nicolasgrum.cl</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Q124618817</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -3717,11 +3622,6 @@
       <c r="I43" t="inlineStr">
         <is>
           <t>https://gonzalocueto.cl</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Q124618818</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -8921,11 +8821,6 @@
           <t>https://typa.org.ar</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Q124618790</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9761,11 +9656,6 @@
           <t>https://imcr.mx</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Q124618791</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9803,11 +9693,6 @@
           <t>https://isuch.uchile.cl</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Q124618792</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9929,11 +9814,6 @@
           <t>https://isabelcroxattogaleria.com</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Q124618814</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9969,11 +9849,6 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>https://cecal.udec.cl</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Q124618815</t>
         </is>
       </c>
     </row>
@@ -10907,11 +10782,6 @@
       <c r="I15" t="n">
         <v>3435910</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Q124618790</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>ORG_0016</t>
@@ -12681,11 +12551,6 @@
       <c r="I46" t="n">
         <v>3530597</v>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Q124618791</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>ORG_0036</t>
@@ -12740,11 +12605,6 @@
       <c r="I47" t="n">
         <v>3871336</v>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Q124618792</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>ORG_0003</t>
@@ -13030,11 +12890,6 @@
       <c r="I52" t="n">
         <v>3893894</v>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Q124618795</t>
-        </is>
-      </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
@@ -13300,11 +13155,6 @@
       <c r="I57" t="n">
         <v>3871336</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Q124618814</t>
-        </is>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>ORG_0040</t>
@@ -13358,11 +13208,6 @@
       </c>
       <c r="I58" t="n">
         <v>3894406</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Q124618815</t>
-        </is>
       </c>
       <c r="L58" t="b">
         <v>0</v>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0000-00-2563-6676</t>
+          <t>0000-0002-2563-6676</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0000-00-0223-0276</t>
+          <t>0000-0002-0223-0276</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0000-00-0239-0872</t>
+          <t>0000-0002-0239-0872</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0000-00-0164-8842</t>
+          <t>0000-0001-0164-8842</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0000-00-0284-486X</t>
+          <t>0000-0002-0284-486X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0000-00-0218-5061</t>
+          <t>0000-0002-0218-5061</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -9851,6 +9851,11 @@
           <t>https://cecal.udec.cl</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Q113665601</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -13209,6 +13214,11 @@
       <c r="I58" t="n">
         <v>3894406</v>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Q113665601</t>
+        </is>
+      </c>
       <c r="L58" t="b">
         <v>0</v>
       </c>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6400,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8096,6 +8096,706 @@
       <c r="F53" t="inlineStr">
         <is>
           <t>FONDART Nacional 89451 fue financiado por CNCA / MINCAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>REL_0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ORG_0001</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Asistente Curatorial y de Exposiciones Temporales</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>REL_0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>REL_0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ORG_0004</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Profesor Universitario de Cátedra</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>REL_0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ORG_0006</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Investigador Independiente de Patrimonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>REL_0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ORG_0008</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Evaluador de Proyectos Culturales (FONDART)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>REL_0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ORG_0011</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Asistente de Investigación y Catalogación</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>REL_0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ORG_0012</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asistente de Investigación en Archivística y Documentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>REL_0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ORG_0022</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Co-Editor y Gestor Editorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>REL_0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ORG_0034</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Evaluador Externo (Arbitraje por pares ciego)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>REL_0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ORG_0037</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Profesor de Estética y Diseño Múltiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>REL_0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ORG_0038</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Formación: Prevención de Riesgos</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>REL_0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ORG_0003</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>REL_0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ORG_0005</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Máster Universitario en Humanidades Digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>REL_0066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ORG_0007</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>REL_0067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ORG_0009</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Diplomado en Gobierno y Gestión Pública</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>REL_0068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ORG_0010</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Diplomado en Museos y Museología (IDEA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>REL_0069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ORG_0013</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>REL_0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ORG_0014</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Equivalencia a nivel académico de Grado en España</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>REL_0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ORG_0033</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Curso Estatuto Administrativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>REL_0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ORG_0035</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>REL_0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ORG_0036</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>REL_0074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PER_0008</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Co-curador: Camila Caris Seguel</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>REL_0075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PER_0004</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Co-curador: Manuel Alvarado Cornejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>REL_0076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PER_0011</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Co-curadora: Montserrat Rojas Corradi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>REL_0077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PER_0008</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PER_0011</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Colaboración en exposiciones</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6400,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8120,7 +8120,6 @@
           <t>ORG_0001</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Asistente Curatorial y de Exposiciones Temporales</t>
@@ -8148,7 +8147,6 @@
           <t>ORG_0002</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
@@ -8176,7 +8174,6 @@
           <t>ORG_0004</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Profesor Universitario de Cátedra</t>
@@ -8204,7 +8201,6 @@
           <t>ORG_0006</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Investigador Independiente de Patrimonio</t>
@@ -8232,7 +8228,6 @@
           <t>ORG_0008</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Evaluador de Proyectos Culturales (FONDART)</t>
@@ -8260,7 +8255,6 @@
           <t>ORG_0011</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Asistente de Investigación y Catalogación</t>
@@ -8288,7 +8282,6 @@
           <t>ORG_0012</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Asistente de Investigación en Archivística y Documentación</t>
@@ -8316,7 +8309,6 @@
           <t>ORG_0022</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Co-Editor y Gestor Editorial</t>
@@ -8344,7 +8336,6 @@
           <t>ORG_0034</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Evaluador Externo (Arbitraje por pares ciego)</t>
@@ -8372,7 +8363,6 @@
           <t>ORG_0037</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Profesor de Estética y Diseño Múltiple</t>
@@ -8400,7 +8390,6 @@
           <t>ORG_0038</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Formación: Prevención de Riesgos</t>
@@ -8428,7 +8417,6 @@
           <t>ORG_0003</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
@@ -8456,7 +8444,6 @@
           <t>ORG_0005</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Máster Universitario en Humanidades Digitales</t>
@@ -8484,7 +8471,6 @@
           <t>ORG_0007</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
@@ -8512,7 +8498,6 @@
           <t>ORG_0009</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Diplomado en Gobierno y Gestión Pública</t>
@@ -8540,7 +8525,6 @@
           <t>ORG_0010</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Diplomado en Museos y Museología (IDEA)</t>
@@ -8568,7 +8552,6 @@
           <t>ORG_0013</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
@@ -8596,7 +8579,6 @@
           <t>ORG_0014</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Equivalencia a nivel académico de Grado en España</t>
@@ -8624,7 +8606,6 @@
           <t>ORG_0033</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Curso Estatuto Administrativo</t>
@@ -8652,7 +8633,6 @@
           <t>ORG_0035</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
@@ -8680,7 +8660,6 @@
           <t>ORG_0036</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
@@ -8708,7 +8687,6 @@
           <t>PER_0008</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Co-curador: Camila Caris Seguel</t>
@@ -8736,7 +8714,6 @@
           <t>PER_0004</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Co-curador: Manuel Alvarado Cornejo</t>
@@ -8764,7 +8741,6 @@
           <t>PER_0011</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Co-curadora: Montserrat Rojas Corradi</t>
@@ -8792,10 +8768,171 @@
           <t>PER_0011</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Colaboración en exposiciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>REL_0078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PRJ_0009</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Rodrigo Rojas De Negri es sujeto del FONDART Archivo Fotográfico</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>REL_0079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PUB_0003</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Rodrigo Rojas De Negri es sujeto del libro de investigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>REL_0080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EXP_0006</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Exposición "A 30 años de Rodrigo Rojas de Negri" (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>REL_0081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EXP_0007</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Exposición "Un exilio sin retorno. Rodrigo Rojas De Negri"</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>REL_0082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LOC_0053</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>crm:P74_has_current_or_former_residence</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Rodrigo Rojas De Negri residió en exilio en Washington D.C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>REL_0083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>COM_0012</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Tema de charla de mediación curatorial</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6400,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8933,6 +8933,2355 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>Tema de charla de mediación curatorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>REL_0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>REL_0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EXP_0001_M01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M01</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>REL_0086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>EXP_0001_M02</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M02</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>REL_0087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXP_0001_M03</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M03</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>REL_0088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EXP_0001_M04</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M04</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>REL_0089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EXP_0001_M05</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M05</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>REL_0090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>EXP_0001_M06</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>REL_0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>EXP_0001_M07</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M07</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>REL_0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EXP_0001_M08</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M08</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>REL_0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EXP_0001_M09</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M09</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>REL_0094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>EXP_0001_M10</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>REL_0095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EXP_0001_M11</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M11</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>REL_0096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EXP_0001_M12</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M12</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>REL_0097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EXP_0001_M13</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M13</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>REL_0098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>EXP_0002</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>REL_0099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EXP_0005</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>REL_0100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>EXP_0006</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>REL_0101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EXP_0007</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>REL_0102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>EXP_0008</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>REL_0103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>EXP_0009</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>REL_0104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>REL_0105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EXP_0010_1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>REL_0106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EXP_0011_01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>REL_0107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EXP_0011_02</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_02</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>REL_0108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EXP_0011_03</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_03</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>REL_0109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>COM_0001</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>REL_0110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>COM_0002</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>REL_0111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>COM_0003</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>REL_0112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>COM_0004</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>REL_0113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>COM_0005</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>REL_0114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>COM_0006</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>REL_0115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>COM_0007</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>REL_0116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>COM_0008</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>REL_0117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>COM_0009</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>REL_0118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>COM_0010</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>REL_0119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>COM_0011</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>REL_0120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>COM_0012</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>REL_0121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>COM_0013</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>REL_0122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>COM_0014</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>REL_0123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>COM_0015</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>REL_0124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>COM_0016</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>REL_0125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>COM_0017</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>REL_0126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>COM_0018</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>REL_0127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>COM_0019</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0019</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>REL_0128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>COM_0020</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>REL_0129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>COM_0021</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>REL_0130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>COM_0022</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0022</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>REL_0131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>COM_0023</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>REL_0132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>COM_0024</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0024</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>REL_0133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>COM_0025</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0025</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>REL_0134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>COM_0026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>REL_0135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>COM_0027</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0027</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>REL_0136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PRJ_0003</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>REL_0137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PRJ_0004</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>REL_0138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PRJ_0007</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>REL_0139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PRJ_0008_N01</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N01</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>REL_0140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PRJ_0008_N02</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>REL_0141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>PRJ_0008_N03</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N03</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>REL_0142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PRJ_0008_N04</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N04</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>REL_0143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PRJ_0011</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>REL_0144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PRJ_0012</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>REL_0145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>PRJ_0013</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>REL_0146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PRJ_0014</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>REL_0147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PRJ_0015</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>REL_0148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>PUB_0001</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>REL_0149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>PUB_0002</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>REL_0150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PUB_0003</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>REL_0151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>PUB_0004</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>REL_0152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PUB_0006</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>REL_0153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>PUB_0007</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>REL_0154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PUB_0008</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>REL_0155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PUB_0009</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>REL_0156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PUB_0010</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>REL_0157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>PUB_0011</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>REL_0158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>PUB_0012</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>REL_0159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PUB_0013</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>REL_0160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PUB_0014</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>REL_0161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>PUB_0015</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0015</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>REL_0162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PUB_0016</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>REL_0163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PUB_0017</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>REL_0164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>PUB_0018</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>REL_0165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PER_0004</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Manuel Alvarado Cornejo participated/curated EXP_0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>REL_0166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>PER_0004</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>EXP_0004</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Manuel Alvarado Cornejo participated/curated EXP_0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>REL_0167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PER_0008</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>EXP_0002</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Camila Caris Seguel participated/curated EXP_0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>REL_0168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>PER_0008</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>EXP_0008</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Camila Caris Seguel participated/curated EXP_0008</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>REL_0169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>PER_0011</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EXP_0007</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Montserrat Rojas Corradi participated/curated EXP_0007</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>REL_0170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>PER_0011</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EXP_0009</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6400,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11282,6 +11282,96 @@
       <c r="E171" t="inlineStr">
         <is>
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>REL_0171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PER_0015</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>PUB_0014</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Raymond Quinsac Monvoisin es sujeto de documentación y catastro de obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>REL_0172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PER_0023</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EXP_0009</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Luis Camnitzer como sujeto de Antología MAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>REL_0173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PER_0031</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EXP_0013</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Wladymir Bernechea como artista en exposición individual Sonata</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6400,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11372,6 +11372,96 @@
       <c r="F174" t="inlineStr">
         <is>
           <t>Wladymir Bernechea como artista en exposición individual Sonata</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>REL_0174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PER_0003</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>PRJ_0005</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Marcela Drien investigadora en proyecto Maturana - Coleccionismo Chile S. XIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>REL_0175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PER_0003</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Marcela Drien investigadora en proyecto Monvoisin en América (Nodo Central)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>REL_0176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PER_0003</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>PRJ_0004</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Marcela Drien investigadora en proyecto Comercio de arte en Chile 1811-1920</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,27 +596,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PER_0003</t>
+          <t>PER_0002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marcela Drien Fábregas</t>
+          <t>Gloria Cortés Aliaga</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marcela Drien</t>
+          <t>Gloria Cortés</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Doctora en Historia del Arte | Directora Núcleo Historia del Arte UAI</t>
+          <t>Investigadora | Editora</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persona (Colaborador)</t>
+          <t>Persona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -626,64 +626,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Contemporánea</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0000-0002-0223-0276</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>https://uai.academia.edu/MarcelaDrien</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://uai.academia.edu/MarcelaDrien</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
+          <t>2010-presente</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PER_0004</t>
+          <t>PER_0003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manuel Alvarado Cornejo</t>
+          <t>Marcela Drien Fábregas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manuel Alvarado</t>
+          <t>Marcela Drien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Historiador del Arte | Co-curador | Co-editor</t>
+          <t>Doctora en Historia del Arte | Directora Núcleo Historia del Arte UAI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -703,12 +668,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0000-0002-0239-0872</t>
+          <t>0000-0002-0223-0276</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://uc-cl.academia.edu/ManuelAlvaradoCornejo</t>
+          <t>https://uai.academia.edu/MarcelaDrien</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -718,7 +683,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://uc-cl.academia.edu/ManuelAlvaradoCornejo</t>
+          <t>https://uai.academia.edu/MarcelaDrien</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -740,22 +705,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PER_0005</t>
+          <t>PER_0004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Milencka Vidal Consiglieri</t>
+          <t>Manuel Alvarado Cornejo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milencka Vidal</t>
+          <t>Manuel Alvarado</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Historiadora del Arte | Co-autora Libro Catastro Afromestizos</t>
+          <t>Historiador del Arte | Co-curador | Co-editor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -775,12 +740,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[N/A]</t>
+          <t>0000-0002-0239-0872</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://rileditores.com</t>
+          <t>https://uc-cl.academia.edu/ManuelAlvaradoCornejo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -790,7 +755,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[N/A]</t>
+          <t>https://uc-cl.academia.edu/ManuelAlvaradoCornejo</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -812,22 +777,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PER_0006</t>
+          <t>PER_0005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Antonia Viu</t>
+          <t>Milencka Vidal Consiglieri</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Antonia Viu</t>
+          <t>Milencka Vidal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doctora en Literatura | Investigadora Responsable Proyecto Harvard-UAI</t>
+          <t>Historiadora del Arte | Co-autora Libro Catastro Afromestizos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -847,12 +812,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0000-0001-0164-8842</t>
+          <t>[N/A]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://artesliberales.uai.cl</t>
+          <t>https://rileditores.com</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -884,22 +849,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PER_0007</t>
+          <t>PER_0006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Noemí Cinelli</t>
+          <t>Antonia Viu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Noemí Cinelli</t>
+          <t>Antonia Viu</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Doctora en Historia del Arte | Investigadora Responsable (IP) FONDECYT Regular 1241154 Mármoles y Bronces</t>
+          <t>Doctora en Literatura | Investigadora Responsable Proyecto Harvard-UAI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -909,7 +874,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Italiana | Chilena</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -919,12 +884,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0000-0002-0284-486X</t>
+          <t>0000-0001-0164-8842</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://anid.cl</t>
+          <t>https://artesliberales.uai.cl</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -956,22 +921,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PER_0008</t>
+          <t>PER_0007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camila Caris Seguel</t>
+          <t>Noemí Cinelli</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camila Caris</t>
+          <t>Noemí Cinelli</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Curadora | Fundadora Museo del Mundo | Co-curadora Prácticas de Reiteración</t>
+          <t>Doctora en Historia del Arte | Investigadora Responsable (IP) FONDECYT Regular 1241154 Mármoles y Bronces</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -981,7 +946,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Italiana | Chilena</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -991,12 +956,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[N/A]</t>
+          <t>0000-0002-0284-486X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://museodelmundo.org</t>
+          <t>https://anid.cl</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1028,22 +993,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PER_0009</t>
+          <t>PER_0008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Estefanía Granja</t>
+          <t>Camila Caris Seguel</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estefanía Granja</t>
+          <t>Camila Caris</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Investigadora | Co-autora Proyecto Callejera Madrid</t>
+          <t>Curadora | Fundadora Museo del Mundo | Co-curadora Prácticas de Reiteración</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1053,7 +1018,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ecuatoriana | Española</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1068,7 +1033,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://callejera-madrid.vercel.app</t>
+          <t>https://museodelmundo.org</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1093,29 +1058,29 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://github.com/jaimecuevas/callejera-madrid</t>
+          <t>[N/A]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PER_0010</t>
+          <t>PER_0009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daniela Colleoni</t>
+          <t>Estefanía Granja</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daniela Colleoni</t>
+          <t>Estefanía Granja</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Co-autora Catálogo Salón de Estudiantes 2013</t>
+          <t>Investigadora | Co-autora Proyecto Callejera Madrid</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1125,7 +1090,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Ecuatoriana | Española</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1140,7 +1105,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://mac.uchile.cl</t>
+          <t>https://callejera-madrid.vercel.app</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1165,29 +1130,29 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>[N/A]</t>
+          <t>https://github.com/jaimecuevas/callejera-madrid</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PER_0011</t>
+          <t>PER_0010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Montserrat Rojas Corradi</t>
+          <t>Daniela Colleoni</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Montserrat Rojas</t>
+          <t>Daniela Colleoni</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Curadora de Fotografía | Directora Proyecto Rodrigo Rojas De Negri | Editora Principal S/T Revista</t>
+          <t>Co-autora Catálogo Salón de Estudiantes 2013</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1244,22 +1209,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PER_0012</t>
+          <t>PER_0011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nury González</t>
+          <t>Montserrat Rojas Corradi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nury González</t>
+          <t>Montserrat Rojas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Artista Visual | Directora Museo de Arte Popular Americano (MAPA)</t>
+          <t>Curadora de Fotografía | Directora Proyecto Rodrigo Rojas De Negri | Editora Principal S/T Revista</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1284,12 +1249,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://mapa.uchile.cl</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Q6047240</t>
+          <t>https://mac.uchile.cl</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1321,22 +1281,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PER_0013</t>
+          <t>PER_0012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fernando Guzmán Schiappacasse</t>
+          <t>Nury González</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fernando Guzmán</t>
+          <t>Nury González</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Doctor en Historia del Arte | Académico Senior UAI</t>
+          <t>Artista Visual | Directora Museo de Arte Popular Americano (MAPA)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1356,12 +1316,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0000-0002-0218-5061</t>
+          <t>[N/A]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://uai.cl</t>
+          <t>https://mapa.uchile.cl</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Q6047240</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1393,22 +1358,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PER_0014</t>
+          <t>PER_0013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Katherine Vyhmeister</t>
+          <t>Fernando Guzmán Schiappacasse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Katherine Vyhmeister</t>
+          <t>Fernando Guzmán</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Historiadora | Docente e Investigadora UAI</t>
+          <t>Doctor en Historia del Arte | Académico Senior UAI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1428,7 +1393,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[N/A]</t>
+          <t>0000-0002-0218-5061</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1465,37 +1430,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PER_0015</t>
+          <t>PER_0014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Raymond Quinsac Monvoisin</t>
+          <t>Katherine Vyhmeister</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raymond Monvoisin</t>
+          <t>Katherine Vyhmeister</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pintor del Siglo XIX | Eje Central Proyecto Quinsac y Episodio Monvoisin</t>
+          <t>Historiadora | Docente e Investigadora UAI</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Artista Histórico</t>
+          <t>Persona (Colaborador)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Francesa</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1794-1870</t>
+          <t>Contemporánea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1505,12 +1470,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.mnba.gob.cl/artistas/raymond-monvoisin</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Q3421074</t>
+          <t>https://uai.cl</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1542,27 +1502,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PER_0016</t>
+          <t>PER_0015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clara Filleul</t>
+          <t>Raymond Quinsac Monvoisin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clara Filleul</t>
+          <t>Raymond Monvoisin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pintora del Siglo XIX | Taller Monvoisin</t>
+          <t>Pintor del Siglo XIX | Eje Central Proyecto Quinsac y Episodio Monvoisin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Artista Histórica</t>
+          <t>Artista Histórico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1572,7 +1532,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1822-1878</t>
+          <t>1794-1870</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1582,12 +1542,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.mnba.gob.cl</t>
+          <t>https://www.mnba.gob.cl/artistas/raymond-monvoisin</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Q19816550</t>
+          <t>Q3421074</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1619,22 +1579,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PER_0017</t>
+          <t>PER_0016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Procesa Sarmiento de Lenoir</t>
+          <t>Clara Filleul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Procesa Sarmiento</t>
+          <t>Clara Filleul</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pintora del Siglo XIX | Discípula Monvoisin (San Juan, Argentina)</t>
+          <t>Pintora del Siglo XIX | Taller Monvoisin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1644,12 +1604,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Francesa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1818-1899</t>
+          <t>1822-1878</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1659,12 +1619,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://es.wikipedia.org/wiki/Procesa_Sarmiento</t>
+          <t>https://www.mnba.gob.cl</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Q6087249</t>
+          <t>Q19816550</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1696,37 +1656,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PER_0018</t>
+          <t>PER_0017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gregorio Torres</t>
+          <t>Procesa Sarmiento de Lenoir</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gregorio Torres</t>
+          <t>Procesa Sarmiento</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pintor del Siglo XIX | Discípulo Monvoisin (Chile)</t>
+          <t>Pintora del Siglo XIX | Discípula Monvoisin (San Juan, Argentina)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Artista Histórico</t>
+          <t>Artista Histórica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1814-1879</t>
+          <t>1818-1899</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1736,7 +1696,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39977.html</t>
+          <t>https://es.wikipedia.org/wiki/Procesa_Sarmiento</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Q6087249</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1768,17 +1733,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PER_0019</t>
+          <t>PER_0018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Francisco Javier Mandiola</t>
+          <t>Gregorio Torres</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Francisco J. Mandiola</t>
+          <t>Gregorio Torres</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1798,7 +1763,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1820-1900</t>
+          <t>1814-1879</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1808,12 +1773,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39978.html</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Q5866185</t>
+          <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39977.html</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1845,22 +1805,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PER_0020</t>
+          <t>PER_0019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nemesio Antúnez Zañartu</t>
+          <t>Francisco Javier Mandiola</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nemesio Antúnez</t>
+          <t>Francisco J. Mandiola</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pintor | Grabador | Director MNBA | Monumentos Nacionales Murales</t>
+          <t>Pintor del Siglo XIX | Discípulo Monvoisin (Chile)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1875,7 +1835,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1918-1993</t>
+          <t>1820-1900</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1885,12 +1845,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://fundacionnemesioantunez.cl</t>
+          <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39978.html</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Q3338025</t>
+          <t>Q5866185</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1922,27 +1882,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PER_0021</t>
+          <t>PER_0020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Violeta Parra Sandoval</t>
+          <t>Nemesio Antúnez Zañartu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Violeta Parra</t>
+          <t>Nemesio Antúnez</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Artista Visual (Arpilleras/Pintura) | Folclorista</t>
+          <t>Pintor | Grabador | Director MNBA | Monumentos Nacionales Murales</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Artista Histórica</t>
+          <t>Artista Histórico</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1952,7 +1912,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1917-1967</t>
+          <t>1918-1993</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1962,12 +1922,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.museovioletaparra.cl</t>
+          <t>https://fundacionnemesioantunez.cl</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Q230887</t>
+          <t>Q3338025</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1999,27 +1959,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PER_0022</t>
+          <t>PER_0021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rodrigo Rojas De Negri</t>
+          <t>Violeta Parra Sandoval</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rodrigo Rojas De Negri</t>
+          <t>Violeta Parra</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Fotógrafo | Sujeto de Investigación y Archivo Fotográfico</t>
+          <t>Artista Visual (Arpilleras/Pintura) | Folclorista</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Artista Histórico</t>
+          <t>Artista Histórica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2029,7 +1989,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1967-1986</t>
+          <t>1917-1967</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2039,12 +1999,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://museodelamemoria.cl</t>
+          <t>https://www.museovioletaparra.cl</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Q6110795</t>
+          <t>Q230887</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2076,37 +2036,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PER_0023</t>
+          <t>PER_0022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Luis Camnitzer</t>
+          <t>Rodrigo Rojas De Negri</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Luis Camnitzer</t>
+          <t>Rodrigo Rojas De Negri</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Artista Conceptual | Sujeto de Exposición Antología MAC</t>
+          <t>Fotógrafo | Sujeto de Investigación y Archivo Fotográfico</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Artista Contemporáneo</t>
+          <t>Artista Histórico</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Uruguaya | Estadounidense</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1937-presente</t>
+          <t>1967-1986</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2116,12 +2076,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.mac.uchile.cl</t>
+          <t>https://museodelamemoria.cl</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Q1876370</t>
+          <t>Q6110795</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2153,37 +2113,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PER_0024</t>
+          <t>PER_0023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pedro Lira Rencoret</t>
+          <t>Luis Camnitzer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pedro Lira</t>
+          <t>Luis Camnitzer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pintor del Siglo XIX | Fundador Sociedad Nacional de Bellas Artes</t>
+          <t>Artista Conceptual | Sujeto de Exposición Antología MAC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Artista Histórico</t>
+          <t>Artista Contemporáneo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Uruguaya | Estadounidense</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1845-1912</t>
+          <t>1937-presente</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2193,12 +2153,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.mnba.gob.cl</t>
+          <t>https://www.mac.uchile.cl</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Q2411933</t>
+          <t>Q1876370</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2230,22 +2190,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PER_0025</t>
+          <t>PER_0024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alessandro Ciccarelli Manzoni</t>
+          <t>Pedro Lira Rencoret</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alessandro Ciccarelli</t>
+          <t>Pedro Lira</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pintor | Primer Director Academia de Pintura de Chile</t>
+          <t>Pintor del Siglo XIX | Fundador Sociedad Nacional de Bellas Artes</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2255,12 +2215,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Italiana | Chilena</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1811-1879</t>
+          <t>1845-1912</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2275,7 +2235,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Q1779373</t>
+          <t>Q2411933</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2307,22 +2267,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PER_0026</t>
+          <t>PER_0025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oskar Trepte</t>
+          <t>Alessandro Ciccarelli Manzoni</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oskar Trepte</t>
+          <t>Alessandro Ciccarelli</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pintor | Adquisiciones SNBA</t>
+          <t>Pintor | Primer Director Academia de Pintura de Chile</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2332,12 +2292,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alemana | Chilena</t>
+          <t>Italiana | Chilena</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1890-1969</t>
+          <t>1811-1879</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2348,6 +2308,11 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>https://www.mnba.gob.cl</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Q1779373</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2379,22 +2344,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PER_0027</t>
+          <t>PER_0026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pedro Reszka Moreau</t>
+          <t>Oskar Trepte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pedro Reszka</t>
+          <t>Oskar Trepte</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pintor | Presidente SNBA</t>
+          <t>Pintor | Adquisiciones SNBA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2404,12 +2369,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Alemana | Chilena</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1872-1960</t>
+          <t>1890-1969</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2451,22 +2416,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PER_0028</t>
+          <t>PER_0027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Virginio Arias Cruz</t>
+          <t>Pedro Reszka Moreau</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Virginio Arias</t>
+          <t>Pedro Reszka</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Escultor | Director Escuela de Bellas Artes</t>
+          <t>Pintor | Presidente SNBA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2481,7 +2446,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1855-1941</t>
+          <t>1872-1960</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2492,11 +2457,6 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>https://www.mnba.gob.cl</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Q3560706</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2528,22 +2488,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PER_0029</t>
+          <t>PER_0028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Benito Rebolledo Correa</t>
+          <t>Virginio Arias Cruz</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Benito Rebolledo</t>
+          <t>Virginio Arias</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pintor | Adquisiciones SNBA</t>
+          <t>Escultor | Director Escuela de Bellas Artes</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2558,7 +2518,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1880-1964</t>
+          <t>1855-1941</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2573,7 +2533,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Q5725916</t>
+          <t>Q3560706</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2605,17 +2565,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PER_0030</t>
+          <t>PER_0029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aristodemo Lattanzi Borghini</t>
+          <t>Benito Rebolledo Correa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aristodemo Lattanzi</t>
+          <t>Benito Rebolledo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2630,12 +2590,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Italiana | Chilena</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1886-1964</t>
+          <t>1880-1964</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2646,6 +2606,11 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>https://www.mnba.gob.cl</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Q5725916</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2677,37 +2642,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PER_0031</t>
+          <t>PER_0030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wladymir Bernechea</t>
+          <t>Aristodemo Lattanzi Borghini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wladymir Bernechea</t>
+          <t>Aristodemo Lattanzi</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Artista Visual Contemporáneo | Prácticas de Reiteración</t>
+          <t>Pintor | Adquisiciones SNBA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Artista Contemporáneo</t>
+          <t>Artista Histórico</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Italiana | Chilena</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Contemporáneo</t>
+          <t>1886-1964</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2717,7 +2682,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://cceguatemala.org</t>
+          <t>https://www.mnba.gob.cl</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2749,22 +2714,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PER_0032</t>
+          <t>PER_0031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jesús Arana</t>
+          <t>Wladymir Bernechea</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jesús Arana</t>
+          <t>Wladymir Bernechea</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Artista Visual | Museo del Mundo</t>
+          <t>Artista Visual Contemporáneo | Prácticas de Reiteración</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2774,7 +2739,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Española</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2821,22 +2786,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PER_0033</t>
+          <t>PER_0032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Iván Navarro</t>
+          <t>Jesús Arana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iván Navarro</t>
+          <t>Jesús Arana</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Artista Visual Contemporáneo | Colección CCU</t>
+          <t>Artista Visual | Museo del Mundo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2846,12 +2811,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Española</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1972-presente</t>
+          <t>Contemporáneo</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2861,12 +2826,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://ccuenelarte.cl</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Q1675579</t>
+          <t>https://cceguatemala.org</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2898,22 +2858,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PER_0034</t>
+          <t>PER_0033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alfredo Jaar</t>
+          <t>Iván Navarro</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alfredo Jaar</t>
+          <t>Iván Navarro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Artista Visual | Premio Nacional de Artes Plásticas 2013</t>
+          <t>Artista Visual Contemporáneo | Colección CCU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2928,7 +2888,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1956-presente</t>
+          <t>1972-presente</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2938,12 +2898,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://alfredojaar.net</t>
+          <t>https://ccuenelarte.cl</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Q329402</t>
+          <t>Q1675579</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2975,27 +2935,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PER_0035</t>
+          <t>PER_0034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Voluspa Jarpa</t>
+          <t>Alfredo Jaar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Voluspa Jarpa</t>
+          <t>Alfredo Jaar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Artista Visual Contemporánea | Pabellón Bienal de Venecia 2019</t>
+          <t>Artista Visual | Premio Nacional de Artes Plásticas 2013</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Artista Contemporánea</t>
+          <t>Artista Contemporáneo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3005,7 +2965,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1971-presente</t>
+          <t>1956-presente</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3015,12 +2975,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://ccuenelarte.cl</t>
+          <t>https://alfredojaar.net</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Q28008544</t>
+          <t>Q329402</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3052,27 +3012,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PER_0036</t>
+          <t>PER_0035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Inés Puyó</t>
+          <t>Voluspa Jarpa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Inés Puyó</t>
+          <t>Voluspa Jarpa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pintora | Exposición Violeta y sus contemporáneas</t>
+          <t>Artista Visual Contemporánea | Pabellón Bienal de Venecia 2019</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Artista Histórica</t>
+          <t>Artista Contemporánea</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3082,7 +3042,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1906-1996</t>
+          <t>1971-presente</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3092,12 +3052,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.mnba.gob.cl</t>
+          <t>https://ccuenelarte.cl</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Q5919720</t>
+          <t>Q28008544</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3129,17 +3089,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PER_0037</t>
+          <t>PER_0036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ximena Cristi</t>
+          <t>Inés Puyó</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ximena Cristi</t>
+          <t>Inés Puyó</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3159,7 +3119,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1920-2022</t>
+          <t>1906-1996</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3174,7 +3134,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Q6169254</t>
+          <t>Q5919720</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3206,22 +3166,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PER_0038</t>
+          <t>PER_0037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Laura Rodig Pizarro</t>
+          <t>Ximena Cristi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Laura Rodig</t>
+          <t>Ximena Cristi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Escultora | Pintora | Educadora de Museos</t>
+          <t>Pintora | Exposición Violeta y sus contemporáneas</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3236,7 +3196,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1901-1972</t>
+          <t>1920-2022</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3251,7 +3211,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Q5971694</t>
+          <t>Q6169254</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3283,22 +3243,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PER_0039</t>
+          <t>PER_0038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Henriette Petit</t>
+          <t>Laura Rodig Pizarro</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Henriette Petit</t>
+          <t>Laura Rodig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pintora | Grupo Montparnasse</t>
+          <t>Escultora | Pintora | Educadora de Museos</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3313,7 +3273,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1894-1983</t>
+          <t>1901-1972</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3328,7 +3288,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Q5894519</t>
+          <t>Q5971694</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3360,37 +3320,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PER_0040</t>
+          <t>PER_0039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sebastián Calfuqueo Aliste</t>
+          <t>Henriette Petit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sebastián Calfuqueo</t>
+          <t>Henriette Petit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Artista Visual | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
+          <t>Pintora | Grupo Montparnasse</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Persona (Artista Contemporáneo)</t>
+          <t>Artista Histórica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chilena | Mapuche</t>
+          <t>Chilena</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1991-presente</t>
+          <t>1894-1983</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3400,12 +3360,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://calfuqueo.com</t>
+          <t>https://www.mnba.gob.cl</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Q107560803</t>
+          <t>Q5894519</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3437,37 +3397,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PER_0041</t>
+          <t>PER_0040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Soledad Pinto</t>
+          <t>Sebastián Calfuqueo Aliste</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Soledad Pinto</t>
+          <t>Sebastián Calfuqueo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Artista Visual | Académica UMCE | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
+          <t>Artista Visual | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Persona (Artista Contemporánea)</t>
+          <t>Persona (Artista Contemporáneo)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Chilena</t>
+          <t>Chilena | Mapuche</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1978-presente</t>
+          <t>1991-presente</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3477,7 +3437,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://soledadpinto.com</t>
+          <t>https://calfuqueo.com</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Q107560803</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3509,27 +3474,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PER_0042</t>
+          <t>PER_0041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nicolás Grum</t>
+          <t>Soledad Pinto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nicolás Grum</t>
+          <t>Soledad Pinto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Artista Visual | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
+          <t>Artista Visual | Académica UMCE | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Persona (Artista Contemporáneo)</t>
+          <t>Persona (Artista Contemporánea)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3539,7 +3504,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1977-presente</t>
+          <t>1978-presente</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3549,7 +3514,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://nicolasgrum.cl</t>
+          <t>https://soledadpinto.com</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3581,70 +3546,142 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>PER_0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nicolás Grum</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nicolás Grum</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Artista Visual | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Persona (Artista Contemporáneo)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Chilena</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1977-presente</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://nicolasgrum.cl</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>PER_0043</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Gonzalo Cueto</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Gonzalo Cueto</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Artista Visual | Académico UCT | Sujeto de Exposición Laboratorio Arte y Crisis M100</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Persona (Artista Contemporáneo)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Chilena</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Contemporáneo</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>https://gonzalocueto.cl</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>[N/A]</t>
         </is>
@@ -6400,7 +6437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F171"/>
+  <dimension ref="A1:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11282,6 +11319,444 @@
       <c r="E171" t="inlineStr">
         <is>
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>REL_0171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PER_0002</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>PUB_0001</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Gloria Cortés co-editó y co-autorizó el libro Monvoisin en América</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>REL_0172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>PER_0002</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Gloria Cortés co-dirige el proyecto Monvoisin en América</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>REL_0173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PER_0006</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PRJ_0007</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2015-2020</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Antonia Viu participó en proyecto Cultures of reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>REL_0174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>PER_0014</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>PRJ_0001</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2018-2024</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Katherine Vyhmeister trabajó en proyecto Arquitectura Art Déco</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>REL_0175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>PER_0013</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2005-2010</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas fue asistente de investigación de Fernando Guzmán en la UAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>REL_0176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PER_0003</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2005-2010</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas fue asistente de investigación de Marcela Drien en la UAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>REL_0177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PER_0014</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2005-2010</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas fue asistente de investigación de Katherine Vyhmeister en la UAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>REL_0178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>ORG_0031</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas participó en congreso internacional de CAIA en Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>REL_0179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ORG_0017</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas ganó Premio Iberoamericano de Wikimedia Argentina/TyPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>REL_0180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>EXP_0005</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas participó/curó exposición de Corporación CCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>REL_0181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PER_0006</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ORG_0015</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2015-2017</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Antonia Viu realizó pasantía académica en Harvard University</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>REL_0182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>PER_0038</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>EXP_0014</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Laura Rodig fue artista principal en exposición Desacatos</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>REL_0183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>PER_0009</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PRJ_0017</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Estefanía Granja desarrolló plataforma digital de Callejera Madrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>REL_0184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PRJ_0017</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2019-2020</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas participó en curación de Callejera Madrid</t>
         </is>
       </c>
     </row>
@@ -21633,7 +22108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25235,6 +25710,56 @@
       <c r="X30" t="inlineStr">
         <is>
           <t>Wladymir Bernechea | Sonata | Retrato contemporáneo | Ficción estética | Empaste matérico | Galería Isabel Croxatto | Identidad digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXP_0014</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PER_0038</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Artista Featured</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Desacatos: Serie de obras de Laura Rodig</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PER_0038</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Galería / Museo</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ORG_0001</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2018-09-01</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2018-11-30</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26869,6 +27394,36 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PRJ_0017</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PER_0009</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Desarrolladora Digital | Investigadora</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Callejera Madrid: Desarrollo digital y curación web</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Proyecto Colaborativo</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2019</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6437,7 +6437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11757,6 +11757,638 @@
       <c r="F185" t="inlineStr">
         <is>
           <t>Jaime Cuevas participó en curación de Callejera Madrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>REL_0185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>PER_0015</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>PUB_0001</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Raymond Monvoisin es sujeto principal de Monvoisin en América</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>REL_0186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>PER_0015</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>PUB_0010</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Monvoisin es tema central en introducción</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>REL_0187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>PER_0015</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>PUB_0014</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Catastro y documentación de obra de Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>REL_0188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>PER_0016</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PUB_0011</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Clara Filleul mencionada en estudio de comercialización</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>REL_0189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>PER_0016</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PUB_0015</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Clara Filleul es sujeto de investigación sobre discipulaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>REL_0190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>PER_0017</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PUB_0015</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Procesa Sarmiento es sujeto de investigación sobre discipulaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>REL_0191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>PER_0025</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>PUB_0016</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Alessandro Ciccarelli es sujeto único del artículo sobre Fuerte Bulnes</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>REL_0192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>PER_0033</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>EXP_0005</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Iván Navarro participó en exposición La segunda naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>REL_0193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PER_0034</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>EXP_0005</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Alfredo Jaar participó en exposición La segunda naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>REL_0194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PER_0035</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>EXP_0005</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Voluspa Jarpa participó en exposición La segunda naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>REL_0195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>PER_0033</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>PUB_0006</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Iván Navarro es artista estudiado en La segunda naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>REL_0196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PER_0034</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>PUB_0006</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Alfredo Jaar es artista estudiado en La segunda naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>REL_0197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PER_0035</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>PUB_0006</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Voluspa Jarpa es artista estudiado en La segunda naturaleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>REL_0198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PER_0015</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Raymond Monvoisin es artista principal en Episodio Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>REL_0199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>PER_0016</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Clara Filleul participó en exposición Episodio Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>REL_0200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>PER_0017</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Procesa Sarmiento participó en exposición Episodio Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>REL_0201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>PER_0018</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Gregorio Torres participó en exposición Episodio Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>REL_0202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>PER_0019</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Francisco Javier Mandiola participó en exposición Episodio Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>REL_0203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>PER_0015</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Raymond Monvoisin es sujeto del proyecto Monvoisin en América</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>REL_0204</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>PER_0016</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PRJ_0006</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Clara Filleul es sujeto del proyecto sobre ausencias femeninas</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>REL_0205</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>PER_0017</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PRJ_0006</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Procesa Sarmiento es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6437,7 +6437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12389,6 +12389,636 @@
       <c r="F206" t="inlineStr">
         <is>
           <t>Procesa Sarmiento es sujeto del proyecto sobre ausencias femeninas</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>REL_0206</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>PER_0005</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>PUB_0002</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Milencka Vidal co-autora de Catastro y visualidad de afromestizos</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>REL_0207</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>PER_0010</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>PUB_0007</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Daniela Colleoni co-autora de Matriz imaginada</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>REL_0208</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>PER_0032</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EXP_0002</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Jesús Arana participó en Prácticas de reiteración</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>REL_0209</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>PER_0043</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>EXP_0012</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Gonzalo Cueto participó en Crisis, crisis, crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>REL_0210</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>PER_0026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Oskar Trepte participó en exposición Adquisiciones en contexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>REL_0211</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>PER_0027</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Pedro Reszka Moreau participó en exposición Adquisiciones en contexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>REL_0212</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>PER_0028</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Virginio Arias Cruz participó en exposición Adquisiciones en contexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>REL_0213</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>PER_0029</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Benito Rebolledo Correa participó en exposición Adquisiciones en contexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>REL_0214</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>PER_0030</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Aristodemo Lattanzi Borghini participó en exposición Adquisiciones en contexto</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>REL_0215</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>PER_0021</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Violeta Parra artista en Violeta y sus contemporáneas</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>REL_0216</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>PER_0036</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Inés Puyó participó en Violeta y sus contemporáneas</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>REL_0217</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>PER_0037</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Ximena Cristi participó en Violeta y sus contemporáneas</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>REL_0218</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>PER_0038</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Laura Rodig participó en Violeta y sus contemporáneas</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>REL_0219</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>PER_0039</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Henriette Petit participó en Violeta y sus contemporáneas</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>REL_0220</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>PER_0020</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>EXP_0011_01</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Nemesio Antúnez en centenario - Estación Ñuble</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>REL_0221</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>PER_0020</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>EXP_0011_02</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Nemesio Antúnez en centenario - Estación Biobío</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>REL_0222</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>PER_0020</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>EXP_0011_03</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Nemesio Antúnez en centenario - Estación Maule</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>REL_0223</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>PER_0023</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>EXP_0009</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Luis Camnitzer participó en Sala de Fotografía Emergente</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>REL_0224</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>PER_0031</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>EXP_0013</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Wladymir Bernechea artista en Sonata</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>REL_0225</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>EXP_0006</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Rodrigo Rojas De Negri en A 30 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>REL_0226</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>PER_0022</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>EXP_0007</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Rodrigo Rojas De Negri en Un exilio sin retorno</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0000-0002-0223-0276</t>
+          <t>0000-0001-9386-7022</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0000-0001-0164-8842</t>
+          <t>0000-0003-0378-6101</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[N/A]</t>
+          <t>0000-0002-3548-9331</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -738,11 +738,6 @@
           <t>Contemporánea</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0000-0002-0239-0872</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>https://uc-cl.academia.edu/ManuelAlvaradoCornejo</t>
@@ -954,11 +949,6 @@
           <t>Contemporánea</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0000-0002-0284-486X</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>https://anid.cl</t>
@@ -1389,11 +1379,6 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>Contemporánea</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0000-0002-0218-5061</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -1021,11 +1021,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://museodelmundo.org</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1756,11 +1751,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39977.html</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -1828,11 +1818,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>https://www.artistasvisualeschilenos.cl/658/w3-article-39978.html</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Q5866185</t>
@@ -1905,11 +1890,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://fundacionnemesioantunez.cl</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Q3338025</t>
@@ -1982,11 +1962,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>https://www.museovioletaparra.cl</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Q230887</t>
@@ -2059,11 +2034,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>https://museodelamemoria.cl</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Q6110795</t>
@@ -2737,11 +2707,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>https://cceguatemala.org</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2809,11 +2774,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>https://cceguatemala.org</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -2881,11 +2841,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>https://ccuenelarte.cl</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Q1675579</t>
@@ -2958,11 +2913,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>https://alfredojaar.net</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>Q329402</t>
@@ -3035,11 +2985,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>https://ccuenelarte.cl</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Q28008544</t>
@@ -3420,11 +3365,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>https://calfuqueo.com</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Q107560803</t>
@@ -3497,11 +3437,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://soledadpinto.com</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -3569,11 +3504,6 @@
           <t>[N/A]</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>https://nicolasgrum.cl</t>
-        </is>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>[N/A]</t>
@@ -3639,11 +3569,6 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>[N/A]</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>https://gonzalocueto.cl</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5910,11 +5835,6 @@
           <t>QUINSAC. Estudios razonados de arte y coleccionismo</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Museo Nacional de Bellas Artes</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>ORG_0002</t>
@@ -5997,11 +5917,6 @@
           <t>Monvoisin: huellas territoriales de un artista</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Biblioteca Nacional Digital / CNCR</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>ORG_0029</t>
@@ -6084,11 +5999,6 @@
           <t>Plataforma virtual Salón de Estudiantes</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Universidad de Chile / MAC</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>ORG_0001</t>
@@ -6171,11 +6081,6 @@
           <t>Callejera Madrid</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Infraestructura Crítica de Datos</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>ORG_0005</t>
@@ -6258,11 +6163,6 @@
           <t>Arquitectura Art Déco en Santiago centro</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FONDART Regional / Plataforma Abierta</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>ORG_0008</t>
@@ -6343,11 +6243,6 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>Mármoles y Bronces entre el Mediterráneo y los Andes</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FONDECYT Regular 1241154</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -25078,7 +25078,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prácticas de reiteración: Colección Museo del Mundo</t>
+          <t>Prácticas de reiteración: Colección Museo del Mundo + Wladimir Bernechea</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6317,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12899,6 +12899,87 @@
       <c r="F227" t="inlineStr">
         <is>
           <t>Rodrigo Rojas De Negri en Un exilio sin retorno</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>REL_CUSTOM_001</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>LOC_0058</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Proyecto Monvoisin registra colecciones en Nancagua</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>REL_CUSTOM_002</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>EXP_0001_M13</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>LOC_0058</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Traslado de colección privada en Nancagua</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>REL_CUSTOM_003</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>LOC_0058</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>rdfs:seeAlso</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Colección documentada en contexto de investigación MNBA</t>
         </is>
       </c>
     </row>
@@ -14713,7 +14794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15066,7 +15147,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ORG_0005</t>
+          <t>Maestría en Estudios Curatoriales (2024-2025)</t>
         </is>
       </c>
       <c r="L6" t="b">
@@ -15823,7 +15904,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Q7894297</t>
+          <t>Q1486</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -18029,6 +18110,41 @@
         <is>
           <t>exact</t>
         </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LOC_0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Colección Privada Nancagua</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Colección / Patrimonio</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Colección privada documentada en Proyecto Monvoisin (traslado obra)</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -20300,16 +20416,14 @@
           <t>Museo Nacional de Bellas Artes (MNBA)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ORG_0002</t>
-        </is>
+      <c r="E2" t="n">
+        <v>2026</v>
       </c>
       <c r="F2" t="n">
         <v>2017</v>
       </c>
       <c r="G2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -20383,16 +20497,14 @@
           <t>Subsecretaría de las Culturas y las Artes, Chile</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ORG_0008</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2026</v>
       </c>
       <c r="F3" t="n">
         <v>2018</v>
       </c>
       <c r="G3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -15147,7 +15147,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Maestría en Estudios Curatoriales (2024-2025)</t>
+          <t>ORG_0005</t>
         </is>
       </c>
       <c r="L6" t="b">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -20416,14 +20416,16 @@
           <t>Museo Nacional de Bellas Artes (MNBA)</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2026</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>2017</v>
       </c>
       <c r="G2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -20497,14 +20499,16 @@
           <t>Subsecretaría de las Culturas y las Artes, Chile</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>2026</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ORG_0007</t>
+        </is>
       </c>
       <c r="F3" t="n">
         <v>2018</v>
       </c>
       <c r="G3" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -18138,11 +18138,6 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Colección privada documentada en Proyecto Monvoisin (traslado obra)</t>
-        </is>
-      </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -3879,7 +3879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Pinacoteca do Estado de São Paulo, Praça da Luz 2, São Paulo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>UAI Errázuriz, Pdte Errázuriz 3485, Las Condes</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>UAC Providencia, Av. Pedro de Valdivia 425, Providencia</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>UAI Peñalolén, Av. Diag. Las Torres 2640, Peñalolén</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>PUC Campus Oriente, Jaime Guzmán Errázuriz 3300, Providencia</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Buenos Aires, Argentina</t>
+          <t>UBA Facultad de Humanidades, Puán 480, Buenos Aires</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Concepción, Región del Biobío</t>
+          <t>Artistas del Acero, Bernardo O'Higgins 1255, Concepción</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>IDEA USACH, Román Díaz 89, Providencia</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Museo Vicuña Mackenna, Av. Vicuña Mackenna 94, Providencia</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Archivo Central Andrés Bello, Arturo Prat 23, Santiago</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Madrid, España</t>
+          <t>Tabacalera, Calle de Embajadores 51, Madrid</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -6317,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F230"/>
+  <dimension ref="A1:F272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12980,6 +12980,1182 @@
       <c r="F230" t="inlineStr">
         <is>
           <t>Colección documentada en contexto de investigación MNBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>REL_227</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>COM_0001</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Jaime participó en entrevista radial</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>REL_228</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>COM_0001</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Comunicación trata sobre exposición</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>REL_229</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>COM_0002</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Jaime participó en podcast</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>REL_230</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>COM_0002</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Podcast trata sobre Monvoisin en América</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>REL_231</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>COM_0004</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>REL_232</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>COM_0004</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Ponencia resultado de investigación Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>REL_233</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>COM_0006</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>REL_234</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>COM_0006</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PRJ_0006</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Ponencia resultado de proyecto Clara Filleul</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>REL_235</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>COM_0016</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Jaime mencionado como experto</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>REL_236</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>COM_0016</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Reportaje trata sobre exposición Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>REL_237</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>COM_0020</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Jaime condujo ciclo de Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>REL_238</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>COM_0020</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Ciclo divulga proyecto Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>REL_239</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>COM_0025</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Jaime participó en lanzamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>REL_240</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>COM_0025</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Lanzamiento presenta proyecto Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>REL_241</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>COM_0027</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Jaime creó/participó en cápsula</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>REL_242</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>COM_0027</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Cápsula trata sobre exposición Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>REL_243</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>COM_0003</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>REL_244</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>COM_0005</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>REL_245</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>COM_0005</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PRJ_0006</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>REL_246</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>COM_0005</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Ponencia se relaciona con Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>REL_247</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>COM_0007</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia en UNIFESP</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>REL_248</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>COM_0008</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>REL_249</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>COM_0009</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>REL_250</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>COM_0010</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>REL_251</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>COM_0011</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>REL_252</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>COM_0012</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Jaime dio charla de mediación</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>REL_253</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>COM_0013</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Jaime organizó y moderó encuentro</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>REL_254</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>COM_0014</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Jaime dio charla especializada</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>REL_255</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>COM_0018</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Jaime dio charla de archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>REL_256</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>COM_0018</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>EXP_0008</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Charla trata sobre Salón de Estudiantes 2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>REL_257</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>COM_0019</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Jaime presentó modelo de gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>REL_258</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>COM_0019</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>EXP_0008</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Presentación trata sobre Salón de Estudiantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>REL_259</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>COM_0021</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Jaime fue invitado a conversatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>REL_260</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>COM_0022</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Jaime fue invitado a conversatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>REL_261</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>COM_0023</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Jaime curó conversatorio</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>REL_262</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>COM_0023</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Conversatorio trata sobre exposición</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>REL_263</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>COM_0024</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Jaime hizo visita mediada</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>REL_264</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>COM_0024</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Visita mediada trata sobre exposición</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>REL_265</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>COM_0015</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Jaime es sujeto/experto mencionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>REL_266</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>COM_0015</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Entrevista trata sobre Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>REL_267</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>COM_0017</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>crm:P129_subject_of</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Jaime es experto mencionado en noticia</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>REL_268</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>COM_0026</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Jaime presentó ponencia técnica</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6317,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F272"/>
+  <dimension ref="A1:F273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13004,7 +13004,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Jaime participó en entrevista radial</t>
@@ -13032,7 +13031,6 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Comunicación trata sobre exposición</t>
@@ -13060,7 +13058,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Jaime participó en podcast</t>
@@ -13088,7 +13085,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Podcast trata sobre Monvoisin en América</t>
@@ -13116,7 +13112,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13144,7 +13139,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Ponencia resultado de investigación Monvoisin</t>
@@ -13172,7 +13166,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13200,7 +13193,6 @@
           <t>PRJ_0006</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto Clara Filleul</t>
@@ -13228,7 +13220,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Jaime mencionado como experto</t>
@@ -13256,7 +13247,6 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Reportaje trata sobre exposición Monvoisin</t>
@@ -13284,7 +13274,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>Jaime condujo ciclo de Instagram</t>
@@ -13312,7 +13301,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>Ciclo divulga proyecto Monvoisin</t>
@@ -13340,7 +13328,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>Jaime participó en lanzamiento</t>
@@ -13368,7 +13355,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>Lanzamiento presenta proyecto Monvoisin</t>
@@ -13396,7 +13382,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>Jaime creó/participó en cápsula</t>
@@ -13424,7 +13409,6 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>Cápsula trata sobre exposición Monvoisin</t>
@@ -13452,7 +13436,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13480,7 +13463,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13508,7 +13490,6 @@
           <t>PRJ_0006</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
@@ -13536,7 +13517,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Ponencia se relaciona con Monvoisin</t>
@@ -13564,7 +13544,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia en UNIFESP</t>
@@ -13592,7 +13571,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13620,7 +13598,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13648,7 +13625,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13676,7 +13652,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13704,7 +13679,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Jaime dio charla de mediación</t>
@@ -13732,7 +13706,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Jaime organizó y moderó encuentro</t>
@@ -13760,7 +13733,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Jaime dio charla especializada</t>
@@ -13788,7 +13760,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Jaime dio charla de archivo</t>
@@ -13816,7 +13787,6 @@
           <t>EXP_0008</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Charla trata sobre Salón de Estudiantes 2013</t>
@@ -13844,7 +13814,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Jaime presentó modelo de gestión</t>
@@ -13872,7 +13841,6 @@
           <t>EXP_0008</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Presentación trata sobre Salón de Estudiantes</t>
@@ -13900,7 +13868,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
@@ -13928,7 +13895,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
@@ -13956,7 +13922,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Jaime curó conversatorio</t>
@@ -13984,7 +13949,6 @@
           <t>EXP_0003</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Conversatorio trata sobre exposición</t>
@@ -14012,7 +13976,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Jaime hizo visita mediada</t>
@@ -14040,7 +14003,6 @@
           <t>EXP_0003</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Visita mediada trata sobre exposición</t>
@@ -14068,7 +14030,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>Jaime es sujeto/experto mencionado</t>
@@ -14096,7 +14057,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>Entrevista trata sobre Monvoisin</t>
@@ -14124,7 +14084,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>Jaime es experto mencionado en noticia</t>
@@ -14152,10 +14111,36 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia técnica</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>REL_269</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>COM_0025</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>DIG_0001</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Communication produces digital resource (QUINSAC platform launch)</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6317,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F273"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14141,6 +14141,141 @@
       <c r="E273" t="inlineStr">
         <is>
           <t>Communication produces digital resource (QUINSAC platform launch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>REL_270</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>COM_0012</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>PRJ_0009</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Charla Artistas del Acero es producto de investigación Archivo Fotográfico Rodrigo Rojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>REL_271</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>COM_0018</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>PRJ_0010</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Matriz Imaginada es producto de investigación Salón de Estudiantes (FVL + FDI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>REL_272</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>COM_0019</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PRJ_0010</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Presentación Tabacalera Madrid es producto de investigación Salón de Estudiantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>REL_273</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>COM_0012</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>EXP_0006</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Charla sobre archivo Rodrigo Rojas trata exposición A 30 años (Museo Memoria DDHH)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>REL_274</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>PER_0003</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Marcela Drien participó en proyecto Monvoisin</t>
         </is>
       </c>
     </row>
@@ -26840,12 +26975,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Explanada MMDH / Plaza de la Constitución</t>
+          <t>Museo de la Memoria y los DDHH, Estación Metro - Av. Matucana 501, Santiago</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ORG_0026</t>
+          <t>https://www.cultura.gob.cl/eventos-actividades/en-emotivo-homenaje-la-imagen-de-rodrigo-rojas-de-negri-recorrio-las-calles-de-santiago/; https://radio.uchile.cl/agenda_cultural/a-30-anos-rodrigo-rojas-de-negri/</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -29287,7 +29422,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Salón de Estudiantes 2013 Desde el resto; (FVL-2011)</t>
+          <t>Salón de Estudiantes 2013 Desde el resto; (FVL-2011 + FDI-MinEducación)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6317,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14276,6 +14276,546 @@
       <c r="F278" t="inlineStr">
         <is>
           <t>Marcela Drien participó en proyecto Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>REL_275</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>PUB_0001</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Proyecto Monvoisin produjo libro colectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>REL_276</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>PUB_0003</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>PRJ_0009</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Proyecto Archivo Rodrigo Rojas produjo libro</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>REL_277</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>PUB_0004</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>EXP_0003</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Exposición produjo catálogo investigación SNBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>REL_278</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>PUB_0005</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>EXP_0004</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Exposición produjo catálogo arte europeo/latinoamericano</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>REL_279</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>PUB_0006</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>EXP_0005</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Exposición CCU produjo catálogo curatorial</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>REL_280</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>PUB_0007</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>PRJ_0010</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Proyecto Salón de Estudiantes produjo catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>REL_281</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>PUB_0010</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Prólogo del libro Monvoisin en América</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>REL_282</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>PUB_0011</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Capítulo sobre mercado de arte en libro Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>REL_283</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>PUB_0012</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>PRJ_0005</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Proyecto Coleccionismo Chile siglo XIX produjo capítulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>REL_284</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>PUB_0014</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Capítulo sobre catastro Monvoisin en libro investigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>REL_285</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>PUB_0015</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>PRJ_0006</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Proyecto Clara Filleul/Procesa produjo capítulo género</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>REL_286</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>PUB_0017</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>PRJ_0016</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Proyecto Revista Fotografía FONDART produjo publicación periódica</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>REL_287</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>PUB_0018</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>EXP_0014</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Exposición Desacatos produjo comentario obra en catálogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>REL_288</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>COM_0012</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>EXP_0007</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Charla sobre curaduría archivo Rodrigo Rojas trata sobre exposición</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>REL_289</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>EXP_0001_M01</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>crm:P129_is_subject_of</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>COM_0017</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Nota de prensa trata sobre traslado Cristo y Magdalena</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>REL_290</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PUB_0002</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>PRJ_0018</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Magister Historia del Arte UAI produjo libro catastro afromestizos</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>REL_291</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>PUB_0008</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>PRJ_0018</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Magister Historia del Arte UAI produjo artículo científico afromestizos</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>REL_292</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>PUB_0013</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>PRJ_0018</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Magister Historia del Arte UAI produjo capítulo visualidades</t>
         </is>
       </c>
     </row>
@@ -28323,7 +28863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29973,6 +30513,41 @@
         <v>2019</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PRJ_0018</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Estudiante de Postgrado</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Magister en Historia del Arte</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Universidad Adolfo Ibáñez (UAI)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ORG_0012</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>2014</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -14747,7 +14747,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>PRJ_0018</t>
+          <t>EDU_0003</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -14777,7 +14777,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>PRJ_0018</t>
+          <t>EDU_0003</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>PRJ_0018</t>
+          <t>EDU_0003</t>
         </is>
       </c>
       <c r="E296" t="n">
@@ -28863,7 +28863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30513,41 +30513,6 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PRJ_0018</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PER_0001</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Estudiante de Postgrado</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Magister en Historia del Arte</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Universidad Adolfo Ibáñez (UAI)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ORG_0012</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>2014</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,6 +515,11 @@
           <t>github_url</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>perfil_profesional</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,7 +539,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Investigador Principal | Historiador del Arte | Arquitecto de Datos</t>
+          <t>INNOVACIÓN PATRIMONIAL &amp; ARQUITECTURA DE DATOS | Historiador del Arte | Curador de Colecciones</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -590,6 +595,11 @@
       <c r="O2" t="inlineStr">
         <is>
           <t>https://github.com/jaimecuevas</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Especialista en catalogación científica, conservación preventiva y diseño de guiones curatoriales con más de una década de trayectoria en museos nacionales de Chile. En Humanidades Digitales, se especializa en el modelado de datos bajo CIDOC-CRM (ISO 21127) y esquemas LOD para auditar sesgos coloniales y de género en el patrimonio.</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6303,6 +6313,254 @@
       <c r="Q7" t="inlineStr">
         <is>
           <t>Plataforma web analítica del proyecto FONDECYT Mármoles y Bronces con base de datos relacional de esculturas, visualización de rutas de importación transatlánticas y fichas biográficas de agentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DIG_0012</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Podcast | Entrevistas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Archivo de Podcast: Humanidades Digitales &amp; Patrimonio</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Plataformas de Audio Digital</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>[Por determinar]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Colección de podcasts y conversaciones sobre metodologías en humanidades digitales, catalogación patrimonial y descolonización de datos</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Nacional | Digital</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Difusión oral | Educación digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DIG_0013</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Radio | Participaciones</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Participaciones en Programas de Radio</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Estaciones de Radio Chile</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>[Por determinar]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Intervenciones en programas de radio sobre memoria, patrimonio cultural y tecnología en museos</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Nacional | Digital</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mediación radiofónica | Circulación de conocimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DIG_0014</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Instagram Live | Transmisiones</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Transmisiones en Vivo: Conversaciones sobre Curaduría Digital</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>@jaime_cuevas (Instagram)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>[Por determinar]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sesiones en vivo en plataformas sociales abordando temas de curatoría digital, gestión de colecciones y estudios poscoloniales</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Nacional | Digital</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Redes sociales | Educación digital distribuida</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DIG_0015</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Video | Conferencias</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Archivo de Conferencias y Webinars</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Plataformas de Video (YouTube, Vimeo)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>[Por determinar]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Grabaciones de conferencias, seminarios y webinars sobre CIDOC-CRM, LOD y arquitectura de datos culturales</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Nacional | Digital</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Difusión audiovisual | Educación abierta</t>
         </is>
       </c>
     </row>
@@ -14830,7 +15088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16427,12 +16685,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>PUDU. Cultural Data Lab</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Organismo Público Laboral</t>
+          <t>Centro de Investigación | Laboratorio</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -16447,7 +16705,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://isl.gob.cl</t>
+          <t>https://pudu.cl</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -16616,6 +16874,28 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>Q1398246</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ORG_0038</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
         </is>
       </c>
     </row>
@@ -22136,7 +22416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23136,6 +23416,86 @@
       <c r="Q12" t="inlineStr">
         <is>
           <t>Formación inicial | Discipulaje académico</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CAR_0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Director de Infraestructuras Culturales | Arquitecto de Datos &amp; Curador de Colecciones</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PUDU. Cultural Data Lab</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ORG_0038</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Humanidades Digitales | Infraestructura Patrimonial | Gobernanza de Datos Culturales | Curaduría Algorítmica | CIDOC-CRM | LOD | Descolonización Digital</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dirección de laboratorio de investigación en datos culturales | Arquitectura de sistemas de información patrimonial | Innovación en metodologías de catalogación digital</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://pudu.cl</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nacional | Transnacional</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Laboratorio de investigación | Infraestructura digital patrimonial</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>INNOVACIÓN PATRIMONIAL &amp; ARQUITECTURA DE DATOS | Historiador del Arte | Curador de Colecciones</t>
+          <t>Innovación Patrimonial &amp; Arquitectura de datos | Historiador del Arte | Curador de Colecciones</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -16910,7 +16910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17012,10 +17012,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-33.4352</v>
+        <v>-33.43515306708146</v>
       </c>
       <c r="H2" t="n">
-        <v>-70.6439</v>
+        <v>-70.64354723358485</v>
       </c>
       <c r="I2" t="n">
         <v>3871336</v>
@@ -17071,10 +17071,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-33.4414</v>
+        <v>-33.44198933167025</v>
       </c>
       <c r="H3" t="n">
-        <v>-70.682</v>
+        <v>-70.68037428569774</v>
       </c>
       <c r="I3" t="n">
         <v>3871336</v>
@@ -17779,10 +17779,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-34.6037</v>
+        <v>-34.62815117682938</v>
       </c>
       <c r="H15" t="n">
-        <v>-58.3816</v>
+        <v>-58.44653347584588</v>
       </c>
       <c r="I15" t="n">
         <v>3435910</v>
@@ -18305,10 +18305,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-33.4398</v>
+        <v>-33.43993915856012</v>
       </c>
       <c r="H24" t="n">
-        <v>-70.6823</v>
+        <v>-70.67955889415381</v>
       </c>
       <c r="I24" t="n">
         <v>3871336</v>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-35.8454</v>
+        <v>-35.84964236458835</v>
       </c>
       <c r="H25" t="n">
-        <v>-71.5976</v>
+        <v>-71.59618571625025</v>
       </c>
       <c r="I25" t="n">
         <v>3883167</v>
@@ -19312,10 +19312,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>-38.0055</v>
+        <v>-38.02110909200199</v>
       </c>
       <c r="H42" t="n">
-        <v>-57.5426</v>
+        <v>-57.56565559316239</v>
       </c>
       <c r="I42" t="n">
         <v>3430863</v>
@@ -19887,10 +19887,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>-36.8282</v>
+        <v>-36.82410307907857</v>
       </c>
       <c r="H52" t="n">
-        <v>-73.0498</v>
+        <v>-73.04222691804569</v>
       </c>
       <c r="I52" t="n">
         <v>3893894</v>
@@ -20256,6 +20256,363 @@
       </c>
       <c r="L59" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LOC_0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pinacoteca do Estado (Sao Paulo)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sede Institucional / Museo</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>-23.53422346887216</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-46.63368673405564</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ORG_0040</t>
+        </is>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LOC_0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Centro de Extensión de la Universidad de Concepción - CELCAL Chillán</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Centro Educativo</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>-36.60655467138508</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-72.09909088922245</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ORG_0034</t>
+        </is>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LOC_0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Universidad Adolfo Ibáñez - Sede Presidente Errázuriz</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sede Universitaria</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>-33.42121365946592</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-70.59154788940485</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ORG_0004</t>
+        </is>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Universidad Adolfo Ibáñez - Campus Peñalolén</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sede Universitaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>-33.48439393710956</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-70.5182663382937</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>ORG_0004</t>
+        </is>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LOC_0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Universidad de Chile - Campus Juan Gómez Millas</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sede Universitaria</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>-33.46665877200571</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-70.59598366056628</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ORG_0034</t>
+        </is>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LOC_0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Archivo Central Andrés Bello - Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Biblioteca / Archivo</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Santiago Centro</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>-33.44432093080183</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-70.65069471823976</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ORG_0034</t>
+        </is>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LOC_0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fundación FIMA - Universidad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Centro de Investigación</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Comuna 12</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>41.38154687801553</v>
+      </c>
+      <c r="H66" t="n">
+        <v>2.139053349698989</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ORG_0031</t>
+        </is>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F296"/>
+  <dimension ref="A1:F299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15074,6 +15074,102 @@
       <c r="F296" t="inlineStr">
         <is>
           <t>Magister Historia del Arte UAI produjo capítulo visualidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>REL_0076</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>PUB_0016</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>crm:P74_has_current_or_former_residence</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>LOC_0059</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Artículo presentado en conferencia en UNIFESP (Pinacoteca São Paulo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>REL_0077</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ORG_0030</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>LOC_0040</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>UNIFESP ubicada en São Paulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>REL_0078</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>crm:P108_has_produced</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>ORG_0030</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Jaime ha publicado artículos en UNIFESP</t>
         </is>
       </c>
     </row>
@@ -20297,7 +20393,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>ORG_0040</t>
+          <t>ORG_0030</t>
         </is>
       </c>
       <c r="L60" t="b">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F296"/>
+  <dimension ref="A1:F297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15074,6 +15074,38 @@
       <c r="F296" t="inlineStr">
         <is>
           <t>Magister Historia del Arte UAI produjo capítulo visualidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>REL_0293</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>COM_0019</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>LOC_0059</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Presentación realizada en Tabacalera</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -16910,7 +16942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20256,6 +20288,57 @@
       </c>
       <c r="L59" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>LOC_0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Tabacalera, Calle de Embajadores 51</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Centro Cultural / Espacio Experimental</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lavapiés</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>40.4168</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-3.7038</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Q9256</t>
+        </is>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -19865,10 +19865,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>-33.4428</v>
+        <v>-33.4410215508963</v>
       </c>
       <c r="H51" t="n">
-        <v>-70.6538</v>
+        <v>-70.65409015407023</v>
       </c>
       <c r="I51" t="n">
         <v>3871336</v>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -16942,7 +16942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17044,10 +17044,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-33.4352</v>
+        <v>-33.43515306708146</v>
       </c>
       <c r="H2" t="n">
-        <v>-70.6439</v>
+        <v>-70.64354723358485</v>
       </c>
       <c r="I2" t="n">
         <v>3871336</v>
@@ -17103,10 +17103,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-33.4414</v>
+        <v>-33.44198933167025</v>
       </c>
       <c r="H3" t="n">
-        <v>-70.682</v>
+        <v>-70.68037428569774</v>
       </c>
       <c r="I3" t="n">
         <v>3871336</v>
@@ -17162,10 +17162,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-33.444</v>
+        <v>-33.44432093080183</v>
       </c>
       <c r="H4" t="n">
-        <v>-70.65000000000001</v>
+        <v>-70.65069471823976</v>
       </c>
       <c r="I4" t="n">
         <v>3871336</v>
@@ -17280,10 +17280,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>41.3851</v>
+        <v>41.38154687801553</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1734</v>
+        <v>2.139053349698989</v>
       </c>
       <c r="I6" t="n">
         <v>3128760</v>
@@ -17811,10 +17811,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-34.6037</v>
+        <v>-34.62815117682938</v>
       </c>
       <c r="H15" t="n">
-        <v>-58.3816</v>
+        <v>-58.44653347584588</v>
       </c>
       <c r="I15" t="n">
         <v>3435910</v>
@@ -17924,10 +17924,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-23.534</v>
+        <v>-23.53422346887216</v>
       </c>
       <c r="H17" t="n">
-        <v>-46.6322</v>
+        <v>-46.63368673405564</v>
       </c>
       <c r="I17" t="n">
         <v>3448439</v>
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>14.6407</v>
+        <v>14.63829337820492</v>
       </c>
       <c r="H21" t="n">
-        <v>-90.5132</v>
+        <v>-90.51453891900114</v>
       </c>
       <c r="I21" t="n">
         <v>3598132</v>
@@ -18337,10 +18337,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-33.4398</v>
+        <v>-33.43993915856012</v>
       </c>
       <c r="H24" t="n">
-        <v>-70.6823</v>
+        <v>-70.67955889415381</v>
       </c>
       <c r="I24" t="n">
         <v>3871336</v>
@@ -18396,10 +18396,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-35.8454</v>
+        <v>-35.84964236458835</v>
       </c>
       <c r="H25" t="n">
-        <v>-71.5976</v>
+        <v>-71.59618571625025</v>
       </c>
       <c r="I25" t="n">
         <v>3883167</v>
@@ -18455,10 +18455,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-36.8282</v>
+        <v>-36.82713507857586</v>
       </c>
       <c r="H26" t="n">
-        <v>-73.03959999999999</v>
+        <v>-73.0394315045538</v>
       </c>
       <c r="I26" t="n">
         <v>3893894</v>
@@ -19919,10 +19919,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>-36.8282</v>
+        <v>-36.82410307907857</v>
       </c>
       <c r="H52" t="n">
-        <v>-73.0498</v>
+        <v>-73.04222691804569</v>
       </c>
       <c r="I52" t="n">
         <v>3893894</v>
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>-36.6066</v>
+        <v>-36.60655467138508</v>
       </c>
       <c r="H58" t="n">
-        <v>-72.10339999999999</v>
+        <v>-72.09909088922245</v>
       </c>
       <c r="I58" t="n">
         <v>3894406</v>
@@ -20336,6 +20336,120 @@
         <v>0</v>
       </c>
       <c r="M60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>LOC_0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UAI Sede Presidente Errázuriz</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sede Universitaria</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>-33.42121365946592</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-70.59154788940485</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LOC_0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>UAI Campus Peñalolén</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sede Universitaria</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>-33.48439393710956</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-70.5182663382937</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>UChile Campus Juan Gomez Millas</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sede Universitaria</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>-33.46665877200571</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-70.59598366056628</v>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>exact</t>
         </is>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F297"/>
+  <dimension ref="A1:F298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15106,6 +15106,34 @@
       <c r="F297" t="inlineStr">
         <is>
           <t>Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>REL_0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>COM_0006</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>LOC_0041</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -15130,7 +15130,6 @@
           <t>LOC_0041</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
@@ -16970,7 +16969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19407,7 +19406,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pontificia Universidad Católica de Chile (Casa Central / Campus Oriente)</t>
+          <t>Campus Oriente UC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -19417,7 +19416,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Santiago / Providencia</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -19431,10 +19430,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>-33.4411</v>
+        <v>-33.44584429023698</v>
       </c>
       <c r="H43" t="n">
-        <v>-70.64060000000001</v>
+        <v>-70.5935286335842</v>
       </c>
       <c r="I43" t="n">
         <v>3871336</v>
@@ -19751,7 +19750,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Centro de Estudios Árabes y Judaicos UCH</t>
+          <t>Centro de Estudios Judaicos, Universidad de Chile</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -19761,7 +19760,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ñuñoa / Santiago</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -19775,10 +19774,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>-33.444</v>
+        <v>-33.43553605588056</v>
       </c>
       <c r="H49" t="n">
-        <v>-70.65000000000001</v>
+        <v>-70.64569885871492</v>
       </c>
       <c r="I49" t="n">
         <v>3871336</v>
@@ -20478,6 +20477,49 @@
         <v>-70.59598366056628</v>
       </c>
       <c r="L63" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>LOC_0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Centro de Estudios Árabes "Eugenio Chahuán", Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Centro de Investigación</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>-33.46513656821872</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-70.59510712009342</v>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>exact</t>
         </is>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F298"/>
+  <dimension ref="A1:F310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15133,6 +15133,342 @@
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>REL_0296</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>ORG_0003</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>LOC_0003</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Universidad de Chile ubicada en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>REL_0297</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ORG_0004</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>LOC_0001</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Universidad Adolfo Ibáñez en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>REL_0298</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ORG_0006</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>LOC_0001</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Centro Nacional de Conservación en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>REL_0299</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ORG_0007</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>LOC_0001</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Servicio Nacional del Patrimonio en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>REL_0300</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ORG_0010</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>LOC_0001</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>USACH IDEA ubicada en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>REL_0301</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ORG_0013</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>LOC_0012</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Ministerio MECD ubicado en Madrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>REL_0302</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>ORG_0026</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>LOC_0023</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Museo de la Memoria ubicado en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>REL_0303</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>ORG_0030</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>LOC_0016</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>UNIFESP ubicada en São Paulo</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>REL_0304</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ORG_0031</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>LOC_0014</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>CAIA/UBA ubicada en Buenos Aires</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>REL_0305</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>ORG_0032</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>LOC_0041</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>UNMDP ubicada en Mar del Plata</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>REL_0306</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>ORG_0033</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>LOC_0042</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>PUC Campus Oriente en Santiago</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>REL_0307</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>COM_0007</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>LOC_0016</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Jornadas de historia del arte en Pinacoteca</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,36 +6575,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F310"/>
+  <dimension ref="A1:F326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_relacion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_origen</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>predicado_cidoc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>id_destino</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion_semantica</t>
         </is>
@@ -8295,6 +8295,7 @@
           <t>ORG_0001</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Asistente Curatorial y de Exposiciones Temporales</t>
@@ -8322,6 +8323,7 @@
           <t>ORG_0002</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
@@ -8349,6 +8351,7 @@
           <t>ORG_0004</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Profesor Universitario de Cátedra</t>
@@ -8376,6 +8379,7 @@
           <t>ORG_0006</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Investigador Independiente de Patrimonio</t>
@@ -8403,6 +8407,7 @@
           <t>ORG_0008</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Evaluador de Proyectos Culturales (FONDART)</t>
@@ -8430,6 +8435,7 @@
           <t>ORG_0011</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Asistente de Investigación y Catalogación</t>
@@ -8457,6 +8463,7 @@
           <t>ORG_0012</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Asistente de Investigación en Archivística y Documentación</t>
@@ -8484,6 +8491,7 @@
           <t>ORG_0022</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Co-Editor y Gestor Editorial</t>
@@ -8511,6 +8519,7 @@
           <t>ORG_0034</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Evaluador Externo (Arbitraje por pares ciego)</t>
@@ -8538,6 +8547,7 @@
           <t>ORG_0037</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Profesor de Estética y Diseño Múltiple</t>
@@ -8565,6 +8575,7 @@
           <t>ORG_0038</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Formación: Prevención de Riesgos</t>
@@ -8592,6 +8603,7 @@
           <t>ORG_0003</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
@@ -8619,6 +8631,7 @@
           <t>ORG_0005</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Máster Universitario en Humanidades Digitales</t>
@@ -8646,6 +8659,7 @@
           <t>ORG_0007</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
@@ -8673,6 +8687,7 @@
           <t>ORG_0009</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Diplomado en Gobierno y Gestión Pública</t>
@@ -8700,6 +8715,7 @@
           <t>ORG_0010</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Diplomado en Museos y Museología (IDEA)</t>
@@ -8727,6 +8743,7 @@
           <t>ORG_0013</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
@@ -8754,6 +8771,7 @@
           <t>ORG_0014</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Equivalencia a nivel académico de Grado en España</t>
@@ -8781,6 +8799,7 @@
           <t>ORG_0033</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Curso Estatuto Administrativo</t>
@@ -8808,6 +8827,7 @@
           <t>ORG_0035</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
@@ -8835,6 +8855,7 @@
           <t>ORG_0036</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
@@ -8862,6 +8883,7 @@
           <t>PER_0008</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Co-curador: Camila Caris Seguel</t>
@@ -8889,6 +8911,7 @@
           <t>PER_0004</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Co-curador: Manuel Alvarado Cornejo</t>
@@ -8916,6 +8939,7 @@
           <t>PER_0011</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Co-curadora: Montserrat Rojas Corradi</t>
@@ -8943,6 +8967,7 @@
           <t>PER_0011</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Colaboración en exposiciones</t>
@@ -8975,6 +9000,7 @@
           <t>Rodrigo Rojas De Negri es sujeto del FONDART Archivo Fotográfico</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9002,6 +9028,7 @@
           <t>Rodrigo Rojas De Negri es sujeto del libro de investigación</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9029,6 +9056,7 @@
           <t>Exposición "A 30 años de Rodrigo Rojas de Negri" (2016)</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9056,6 +9084,7 @@
           <t>Exposición "Un exilio sin retorno. Rodrigo Rojas De Negri"</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9083,6 +9112,7 @@
           <t>Rodrigo Rojas De Negri residió en exilio en Washington D.C.</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9110,6 +9140,7 @@
           <t>Tema de charla de mediación curatorial</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9137,6 +9168,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9164,6 +9196,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M01</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9191,6 +9224,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M02</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9218,6 +9252,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M03</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9245,6 +9280,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M04</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9272,6 +9308,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M05</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9299,6 +9336,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M06</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9326,6 +9364,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M07</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9353,6 +9392,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M08</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9380,6 +9420,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M09</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9407,6 +9448,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M10</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9434,6 +9476,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M11</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9461,6 +9504,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M12</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9488,6 +9532,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M13</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9515,6 +9560,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0002</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9542,6 +9588,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0005</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9569,6 +9616,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0006</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9596,6 +9644,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0007</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9623,6 +9672,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0008</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9650,6 +9700,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0009</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9677,6 +9728,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9704,6 +9756,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010_1</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9731,6 +9784,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_01</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9758,6 +9812,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_02</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9785,6 +9840,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_03</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9812,6 +9868,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0001</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9839,6 +9896,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0002</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9866,6 +9924,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0003</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9893,6 +9952,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0004</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9920,6 +9980,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0005</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9947,6 +10008,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0006</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9974,6 +10036,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0007</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10001,6 +10064,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0008</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10028,6 +10092,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0009</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10055,6 +10120,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0010</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10082,6 +10148,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0011</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10109,6 +10176,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0012</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10136,6 +10204,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0013</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10163,6 +10232,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0014</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10190,6 +10260,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0015</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10217,6 +10288,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0016</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10244,6 +10316,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0017</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10271,6 +10344,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0018</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10298,6 +10372,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0019</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10325,6 +10400,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0020</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10352,6 +10428,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0021</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10379,6 +10456,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0022</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10406,6 +10484,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0023</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10433,6 +10512,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0024</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10460,6 +10540,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0025</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10487,6 +10568,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0026</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10514,6 +10596,7 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0027</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10541,6 +10624,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0003</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10568,6 +10652,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0004</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10595,6 +10680,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0007</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10622,6 +10708,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N01</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10649,6 +10736,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N02</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10676,6 +10764,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N03</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10703,6 +10792,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N04</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10730,6 +10820,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0011</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10757,6 +10848,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0012</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10784,6 +10876,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0013</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10811,6 +10904,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0014</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10838,6 +10932,7 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0015</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10865,6 +10960,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0001</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10892,6 +10988,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0002</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10919,6 +11016,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0003</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10946,6 +11044,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0004</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10973,6 +11072,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0006</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11000,6 +11100,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0007</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11027,6 +11128,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0008</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11054,6 +11156,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0009</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11081,6 +11184,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0010</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11108,6 +11212,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0011</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11135,6 +11240,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0012</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11162,6 +11268,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0013</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11189,6 +11296,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0014</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11216,6 +11324,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0015</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11243,6 +11352,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0016</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11270,6 +11380,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0017</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11297,6 +11408,7 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0018</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11324,6 +11436,7 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0003</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11351,6 +11464,7 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0004</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11378,6 +11492,7 @@
           <t>Camila Caris Seguel participated/curated EXP_0002</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11405,6 +11520,7 @@
           <t>Camila Caris Seguel participated/curated EXP_0008</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11432,6 +11548,7 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0007</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11459,6 +11576,7 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13181,6 +13299,7 @@
           <t>LOC_0058</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin registra colecciones en Nancagua</t>
@@ -13208,6 +13327,7 @@
           <t>LOC_0058</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>Traslado de colección privada en Nancagua</t>
@@ -13235,6 +13355,7 @@
           <t>ORG_0002</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>Colección documentada en contexto de investigación MNBA</t>
@@ -13262,6 +13383,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Jaime participó en entrevista radial</t>
@@ -13289,6 +13411,7 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Comunicación trata sobre exposición</t>
@@ -13316,6 +13439,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Jaime participó en podcast</t>
@@ -13343,6 +13467,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Podcast trata sobre Monvoisin en América</t>
@@ -13370,6 +13495,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13397,6 +13523,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Ponencia resultado de investigación Monvoisin</t>
@@ -13424,6 +13551,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13451,6 +13579,7 @@
           <t>PRJ_0006</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto Clara Filleul</t>
@@ -13478,6 +13607,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Jaime mencionado como experto</t>
@@ -13505,6 +13635,7 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Reportaje trata sobre exposición Monvoisin</t>
@@ -13532,6 +13663,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>Jaime condujo ciclo de Instagram</t>
@@ -13559,6 +13691,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>Ciclo divulga proyecto Monvoisin</t>
@@ -13586,6 +13719,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>Jaime participó en lanzamiento</t>
@@ -13613,6 +13747,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>Lanzamiento presenta proyecto Monvoisin</t>
@@ -13640,6 +13775,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>Jaime creó/participó en cápsula</t>
@@ -13667,6 +13803,7 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>Cápsula trata sobre exposición Monvoisin</t>
@@ -13694,6 +13831,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13721,6 +13859,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13748,6 +13887,7 @@
           <t>PRJ_0006</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
@@ -13775,6 +13915,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Ponencia se relaciona con Monvoisin</t>
@@ -13802,6 +13943,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia en UNIFESP</t>
@@ -13829,6 +13971,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13856,6 +13999,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13883,6 +14027,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13910,6 +14055,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13937,6 +14083,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Jaime dio charla de mediación</t>
@@ -13964,6 +14111,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Jaime organizó y moderó encuentro</t>
@@ -13991,6 +14139,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Jaime dio charla especializada</t>
@@ -14018,6 +14167,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Jaime dio charla de archivo</t>
@@ -14045,6 +14195,7 @@
           <t>EXP_0008</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Charla trata sobre Salón de Estudiantes 2013</t>
@@ -14072,6 +14223,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Jaime presentó modelo de gestión</t>
@@ -14099,6 +14251,7 @@
           <t>EXP_0008</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Presentación trata sobre Salón de Estudiantes</t>
@@ -14126,6 +14279,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
@@ -14153,6 +14307,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
@@ -14180,6 +14335,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Jaime curó conversatorio</t>
@@ -14207,6 +14363,7 @@
           <t>EXP_0003</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Conversatorio trata sobre exposición</t>
@@ -14234,6 +14391,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Jaime hizo visita mediada</t>
@@ -14261,6 +14419,7 @@
           <t>EXP_0003</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Visita mediada trata sobre exposición</t>
@@ -14288,6 +14447,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>Jaime es sujeto/experto mencionado</t>
@@ -14315,6 +14475,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>Entrevista trata sobre Monvoisin</t>
@@ -14342,6 +14503,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>Jaime es experto mencionado en noticia</t>
@@ -14369,6 +14531,7 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia técnica</t>
@@ -14401,6 +14564,7 @@
           <t>Communication produces digital resource (QUINSAC platform launch)</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14423,6 +14587,7 @@
           <t>PRJ_0009</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>Charla Artistas del Acero es producto de investigación Archivo Fotográfico Rodrigo Rojas</t>
@@ -14450,6 +14615,7 @@
           <t>PRJ_0010</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>Matriz Imaginada es producto de investigación Salón de Estudiantes (FVL + FDI)</t>
@@ -14477,6 +14643,7 @@
           <t>PRJ_0010</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>Presentación Tabacalera Madrid es producto de investigación Salón de Estudiantes</t>
@@ -14504,6 +14671,7 @@
           <t>EXP_0006</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>Charla sobre archivo Rodrigo Rojas trata exposición A 30 años (Museo Memoria DDHH)</t>
@@ -14531,6 +14699,7 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>Marcela Drien participó en proyecto Monvoisin</t>
@@ -15130,6 +15299,7 @@
           <t>LOC_0041</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
@@ -15469,6 +15639,486 @@
       <c r="F310" t="inlineStr">
         <is>
           <t>Jornadas de historia del arte en Pinacoteca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>REL_0308</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>EDU_0003</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>LOC_0060</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Magíster en Historia del Arte - UAI Sede Presidente Errázuriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>REL_0309</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>EDU_0003</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>LOC_0061</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Magíster en Historia del Arte - UAI Campus Peñalolén</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>REL_0310</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>EDU_0008</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>LOC_0061</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Diplomado en Curaduría - UAI Campus Peñalolén</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>REL_0311</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>EDU_0004</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Licenciatura en Artes c/m Teoría e Historia del Arte - UChile Juan Gómez Millas</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>REL_0312</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>EDU_0006</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Diplomado Postítulo Estudios Internacionales - UChile Juan Gómez Millas</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>REL_0313</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>EDU_0012</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Diplomado Extensión Ciencia de la Religión c/m Judaísmo - UChile Juan Gómez Millas</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>REL_0314</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>EDU_0013</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Seminario Especialización Egiptología Medio Oriente - UChile Juan Gómez Millas</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>REL_0315</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>EXP_0010_1</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>LOC_0051</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Violeta y sus contemporáneas - Artistas del Acero</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>REL_0316</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>EXP_0011_02</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>LOC_0051</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Antúnez: Paisaje y Poesía - Artistas del Acero</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>REL_0317</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>LOC_0017</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Participación arte contemporáneo Mendoza</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>REL_0318</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>LOC_0052</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Espacios investigación patrimonio - BVMK</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>REL_0319</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>LOC_0049</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Investigación recursos digitales patrimonio</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>REL_0320</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>crm:P12_occurred_in_the_presence_of</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>LOC_0053</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Investigación memoria exilio - Rodrigo Rojas</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>REL_0321</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>crm:P12_occurred_in_the_presence_of</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>LOC_0054</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Investigación redes escultóricas Europa</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>REL_0322</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>crm:P11_had_participant</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>LOC_0018</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Colaboración académica curaduría - UNSAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>REL_0323</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>EDU_0013</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>crm:P87_is_identified_by</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>LOC_0063</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Seminario Especialización Egiptología y Medio Oriente - Centro de Estudios Árabes, UChile</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -8295,7 +8295,6 @@
           <t>ORG_0001</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Asistente Curatorial y de Exposiciones Temporales</t>
@@ -8323,7 +8322,6 @@
           <t>ORG_0002</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
@@ -8351,7 +8349,6 @@
           <t>ORG_0004</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Profesor Universitario de Cátedra</t>
@@ -8379,7 +8376,6 @@
           <t>ORG_0006</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Investigador Independiente de Patrimonio</t>
@@ -8407,7 +8403,6 @@
           <t>ORG_0008</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Evaluador de Proyectos Culturales (FONDART)</t>
@@ -8435,7 +8430,6 @@
           <t>ORG_0011</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Asistente de Investigación y Catalogación</t>
@@ -8463,7 +8457,6 @@
           <t>ORG_0012</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Asistente de Investigación en Archivística y Documentación</t>
@@ -8491,7 +8484,6 @@
           <t>ORG_0022</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Co-Editor y Gestor Editorial</t>
@@ -8519,7 +8511,6 @@
           <t>ORG_0034</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Evaluador Externo (Arbitraje por pares ciego)</t>
@@ -8547,7 +8538,6 @@
           <t>ORG_0037</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Profesor de Estética y Diseño Múltiple</t>
@@ -8575,7 +8565,6 @@
           <t>ORG_0038</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Formación: Prevención de Riesgos</t>
@@ -8603,7 +8592,6 @@
           <t>ORG_0003</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
@@ -8631,7 +8619,6 @@
           <t>ORG_0005</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Máster Universitario en Humanidades Digitales</t>
@@ -8659,7 +8646,6 @@
           <t>ORG_0007</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
@@ -8687,7 +8673,6 @@
           <t>ORG_0009</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Diplomado en Gobierno y Gestión Pública</t>
@@ -8715,7 +8700,6 @@
           <t>ORG_0010</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Diplomado en Museos y Museología (IDEA)</t>
@@ -8743,7 +8727,6 @@
           <t>ORG_0013</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
@@ -8771,7 +8754,6 @@
           <t>ORG_0014</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Equivalencia a nivel académico de Grado en España</t>
@@ -8799,7 +8781,6 @@
           <t>ORG_0033</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Curso Estatuto Administrativo</t>
@@ -8827,7 +8808,6 @@
           <t>ORG_0035</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
@@ -8855,7 +8835,6 @@
           <t>ORG_0036</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
@@ -8883,7 +8862,6 @@
           <t>PER_0008</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Co-curador: Camila Caris Seguel</t>
@@ -8911,7 +8889,6 @@
           <t>PER_0004</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Co-curador: Manuel Alvarado Cornejo</t>
@@ -8939,7 +8916,6 @@
           <t>PER_0011</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Co-curadora: Montserrat Rojas Corradi</t>
@@ -8967,7 +8943,6 @@
           <t>PER_0011</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Colaboración en exposiciones</t>
@@ -9000,7 +8975,6 @@
           <t>Rodrigo Rojas De Negri es sujeto del FONDART Archivo Fotográfico</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9028,7 +9002,6 @@
           <t>Rodrigo Rojas De Negri es sujeto del libro de investigación</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9056,7 +9029,6 @@
           <t>Exposición "A 30 años de Rodrigo Rojas de Negri" (2016)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9084,7 +9056,6 @@
           <t>Exposición "Un exilio sin retorno. Rodrigo Rojas De Negri"</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9112,7 +9083,6 @@
           <t>Rodrigo Rojas De Negri residió en exilio en Washington D.C.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9140,7 +9110,6 @@
           <t>Tema de charla de mediación curatorial</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9168,7 +9137,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9196,7 +9164,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M01</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9224,7 +9191,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M02</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9252,7 +9218,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M03</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9280,7 +9245,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M04</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9308,7 +9272,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M05</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9336,7 +9299,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M06</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9364,7 +9326,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M07</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9392,7 +9353,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M08</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9420,7 +9380,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M09</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9448,7 +9407,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M10</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9476,7 +9434,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M11</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9504,7 +9461,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M12</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9532,7 +9488,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M13</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9560,7 +9515,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0002</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9588,7 +9542,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0005</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9616,7 +9569,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0006</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9644,7 +9596,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0007</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9672,7 +9623,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0008</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9700,7 +9650,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0009</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9728,7 +9677,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9756,7 +9704,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010_1</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9784,7 +9731,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_01</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9812,7 +9758,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_02</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9840,7 +9785,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_03</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9868,7 +9812,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0001</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9896,7 +9839,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0002</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9924,7 +9866,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0003</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9952,7 +9893,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0004</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9980,7 +9920,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0005</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10008,7 +9947,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0006</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10036,7 +9974,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0007</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10064,7 +10001,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0008</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10092,7 +10028,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0009</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10120,7 +10055,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0010</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10148,7 +10082,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0011</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10176,7 +10109,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0012</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10204,7 +10136,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0013</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10232,7 +10163,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0014</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10260,7 +10190,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0015</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10288,7 +10217,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0016</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10316,7 +10244,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0017</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10344,7 +10271,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0018</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10372,7 +10298,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0019</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10400,7 +10325,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0020</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10428,7 +10352,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0021</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10456,7 +10379,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0022</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10484,7 +10406,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0023</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10512,7 +10433,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0024</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10540,7 +10460,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0025</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10568,7 +10487,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0026</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10596,7 +10514,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0027</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10624,7 +10541,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0003</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10652,7 +10568,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0004</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10680,7 +10595,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0007</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10708,7 +10622,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N01</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10736,7 +10649,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N02</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10764,7 +10676,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N03</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10792,7 +10703,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N04</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10820,7 +10730,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0011</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10848,7 +10757,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0012</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10876,7 +10784,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0013</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10904,7 +10811,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0014</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10932,7 +10838,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0015</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10960,7 +10865,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0001</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10988,7 +10892,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0002</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11016,7 +10919,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0003</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11044,7 +10946,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0004</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11072,7 +10973,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0006</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11100,7 +11000,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0007</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11128,7 +11027,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0008</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11156,7 +11054,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0009</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11184,7 +11081,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0010</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11212,7 +11108,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0011</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11240,7 +11135,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0012</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11268,7 +11162,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0013</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11296,7 +11189,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0014</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11324,7 +11216,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0015</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11352,7 +11243,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0016</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11380,7 +11270,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0017</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11408,7 +11297,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0018</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11436,7 +11324,6 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0003</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11464,7 +11351,6 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0004</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11492,7 +11378,6 @@
           <t>Camila Caris Seguel participated/curated EXP_0002</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11520,7 +11405,6 @@
           <t>Camila Caris Seguel participated/curated EXP_0008</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11548,7 +11432,6 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0007</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11576,7 +11459,6 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -13299,7 +13181,6 @@
           <t>LOC_0058</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin registra colecciones en Nancagua</t>
@@ -13327,7 +13208,6 @@
           <t>LOC_0058</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>Traslado de colección privada en Nancagua</t>
@@ -13355,7 +13235,6 @@
           <t>ORG_0002</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>Colección documentada en contexto de investigación MNBA</t>
@@ -13383,7 +13262,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Jaime participó en entrevista radial</t>
@@ -13411,7 +13289,6 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Comunicación trata sobre exposición</t>
@@ -13439,7 +13316,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Jaime participó en podcast</t>
@@ -13467,7 +13343,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Podcast trata sobre Monvoisin en América</t>
@@ -13495,7 +13370,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13523,7 +13397,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Ponencia resultado de investigación Monvoisin</t>
@@ -13551,7 +13424,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13579,7 +13451,6 @@
           <t>PRJ_0006</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto Clara Filleul</t>
@@ -13607,7 +13478,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Jaime mencionado como experto</t>
@@ -13635,7 +13505,6 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Reportaje trata sobre exposición Monvoisin</t>
@@ -13663,7 +13532,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>Jaime condujo ciclo de Instagram</t>
@@ -13691,7 +13559,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>Ciclo divulga proyecto Monvoisin</t>
@@ -13719,7 +13586,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>Jaime participó en lanzamiento</t>
@@ -13747,7 +13613,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>Lanzamiento presenta proyecto Monvoisin</t>
@@ -13775,7 +13640,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>Jaime creó/participó en cápsula</t>
@@ -13803,7 +13667,6 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>Cápsula trata sobre exposición Monvoisin</t>
@@ -13831,7 +13694,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13859,7 +13721,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13887,7 +13748,6 @@
           <t>PRJ_0006</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
@@ -13915,7 +13775,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Ponencia se relaciona con Monvoisin</t>
@@ -13943,7 +13802,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia en UNIFESP</t>
@@ -13971,7 +13829,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -13999,7 +13856,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -14027,7 +13883,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -14055,7 +13910,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
@@ -14083,7 +13937,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Jaime dio charla de mediación</t>
@@ -14111,7 +13964,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Jaime organizó y moderó encuentro</t>
@@ -14139,7 +13991,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Jaime dio charla especializada</t>
@@ -14167,7 +14018,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Jaime dio charla de archivo</t>
@@ -14195,7 +14045,6 @@
           <t>EXP_0008</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Charla trata sobre Salón de Estudiantes 2013</t>
@@ -14223,7 +14072,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Jaime presentó modelo de gestión</t>
@@ -14251,7 +14099,6 @@
           <t>EXP_0008</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Presentación trata sobre Salón de Estudiantes</t>
@@ -14279,7 +14126,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
@@ -14307,7 +14153,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
@@ -14335,7 +14180,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Jaime curó conversatorio</t>
@@ -14363,7 +14207,6 @@
           <t>EXP_0003</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Conversatorio trata sobre exposición</t>
@@ -14391,7 +14234,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Jaime hizo visita mediada</t>
@@ -14419,7 +14261,6 @@
           <t>EXP_0003</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Visita mediada trata sobre exposición</t>
@@ -14447,7 +14288,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>Jaime es sujeto/experto mencionado</t>
@@ -14475,7 +14315,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>Entrevista trata sobre Monvoisin</t>
@@ -14503,7 +14342,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>Jaime es experto mencionado en noticia</t>
@@ -14531,7 +14369,6 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia técnica</t>
@@ -14564,7 +14401,6 @@
           <t>Communication produces digital resource (QUINSAC platform launch)</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14587,7 +14423,6 @@
           <t>PRJ_0009</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>Charla Artistas del Acero es producto de investigación Archivo Fotográfico Rodrigo Rojas</t>
@@ -14615,7 +14450,6 @@
           <t>PRJ_0010</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>Matriz Imaginada es producto de investigación Salón de Estudiantes (FVL + FDI)</t>
@@ -14643,7 +14477,6 @@
           <t>PRJ_0010</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>Presentación Tabacalera Madrid es producto de investigación Salón de Estudiantes</t>
@@ -14671,7 +14504,6 @@
           <t>EXP_0006</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>Charla sobre archivo Rodrigo Rojas trata exposición A 30 años (Museo Memoria DDHH)</t>
@@ -14699,7 +14531,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>Marcela Drien participó en proyecto Monvoisin</t>
@@ -15299,7 +15130,6 @@
           <t>LOC_0041</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
@@ -15327,7 +15157,6 @@
           <t>LOC_0003</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>Universidad de Chile ubicada en Santiago</t>
@@ -15355,7 +15184,6 @@
           <t>LOC_0001</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>Universidad Adolfo Ibáñez en Santiago</t>
@@ -15383,7 +15211,6 @@
           <t>LOC_0001</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>Centro Nacional de Conservación en Santiago</t>
@@ -15411,7 +15238,6 @@
           <t>LOC_0001</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>Servicio Nacional del Patrimonio en Santiago</t>
@@ -15439,7 +15265,6 @@
           <t>LOC_0001</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>USACH IDEA ubicada en Santiago</t>
@@ -15467,7 +15292,6 @@
           <t>LOC_0012</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>Ministerio MECD ubicado en Madrid</t>
@@ -15495,7 +15319,6 @@
           <t>LOC_0023</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>Museo de la Memoria ubicado en Santiago</t>
@@ -15523,7 +15346,6 @@
           <t>LOC_0016</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>UNIFESP ubicada en São Paulo</t>
@@ -15548,10 +15370,9 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LOC_0014</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr"/>
+          <t>LOC_0064</t>
+        </is>
+      </c>
       <c r="F307" t="inlineStr">
         <is>
           <t>CAIA/UBA ubicada en Buenos Aires</t>
@@ -15579,7 +15400,6 @@
           <t>LOC_0041</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>UNMDP ubicada en Mar del Plata</t>
@@ -15607,7 +15427,6 @@
           <t>LOC_0042</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>PUC Campus Oriente en Santiago</t>
@@ -15635,7 +15454,6 @@
           <t>LOC_0016</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>Jornadas de historia del arte en Pinacoteca</t>
@@ -17955,7 +17773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18800,7 +18618,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fundación TyPA / CAIA UBA (Buenos Aires)</t>
+          <t>Fundación TyPA (Buenos Aires)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -21506,6 +21324,60 @@
         <v>-70.59510712009342</v>
       </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LOC_0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CAIA / Universidad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Centro de Investigación</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Comuna 1</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>-34.62815</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-58.44653</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3435910</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>ORG_0031</t>
+        </is>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>exact</t>
         </is>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F326"/>
+  <dimension ref="A1:F327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15937,6 +15937,38 @@
       <c r="F326" t="inlineStr">
         <is>
           <t>Seminario Especialización Egiptología y Medio Oriente - Centro de Estudios Árabes, UChile</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>REL_0324</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>LOC_0013</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas realizó investigación de archivo en Harvard University (Cambridge, MA) como parte del proyecto FONDECYT Cultures of Reading, marzo-abril 2018</t>
         </is>
       </c>
     </row>
@@ -30764,7 +30796,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ORG_0007</t>
+          <t>ORG_0002</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -30841,7 +30873,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ORG_0007</t>
+          <t>ORG_0002</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -30918,7 +30950,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ORG_0015</t>
+          <t>ORG_0008</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -30943,12 +30975,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>42.3770,-71.1167</t>
+          <t>42.37436609415559,-71.11692392881085</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F298"/>
+  <dimension ref="A1:F299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15133,6 +15133,34 @@
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>REL_299</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>EDU_0001</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>LOC_0005</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Máster en Humanidades Digitales se cursó en UB FIMA</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F299"/>
+  <dimension ref="A1:F304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15157,10 +15157,124 @@
           <t>LOC_0005</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>Máster en Humanidades Digitales se cursó en UB FIMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>REL_300</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>EDU_0004</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>LOC_0062</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>REL_301</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>EDU_0006</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>LOC_0064</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>REL_302</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>EDU_0012</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>LOC_0048</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>REL_303</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>EDU_0013</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>LOC_0063</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>REL_304</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>ORG_0003</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>rdf:type</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>LOC_0046</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>EXCLUDE_DERIVATION</t>
         </is>
       </c>
     </row>
@@ -16997,7 +17111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20548,6 +20662,44 @@
         <v>-70.59510712009342</v>
       </c>
       <c r="L64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>LOC_0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios Internacionales de la Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Departamento Universitario</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>-33.43714059270721</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-70.62813240660158</v>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
@@ -21660,7 +21812,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Aprobado con Distinción Máxima (Beca Bicentenario)</t>
+          <t>LOC_0062</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -21826,7 +21978,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Aprobado con Calificación 6,6 (216 hrs)</t>
+          <t>LOC_0064</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -22324,7 +22476,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Certificación de Extensión Universitaria</t>
+          <t>LOC_0048</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -22407,7 +22559,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Certificación de Formación Continua</t>
+          <t>LOC_0063</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -15251,33 +15251,7 @@
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>REL_304</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>ORG_0003</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>rdf:type</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>LOC_0046</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>EXCLUDE_DERIVATION</t>
-        </is>
-      </c>
-    </row>
+    <row r="304"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19779,7 +19753,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ISUCH - Universidad de Chile</t>
+          <t>ISUCH (Instituto de Estudios Secundarios)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -19810,11 +19784,6 @@
       </c>
       <c r="I47" t="n">
         <v>3871336</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>ORG_0003</t>
-        </is>
       </c>
       <c r="L47" t="b">
         <v>0</v>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15251,7 +15251,6 @@
         </is>
       </c>
     </row>
-    <row r="304"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23469,7 +23468,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>LOC_0046</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6575,7 +6575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F303"/>
+  <dimension ref="A1:F309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15248,6 +15248,168 @@
       <c r="D303" t="inlineStr">
         <is>
           <t>LOC_0063</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>REL_304</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>EXP_0010</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CAR_0013</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>EXP_0010 was coordinated via CAR_0013 (Itinerancias role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>REL_305</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>EXP_0010_1</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>CAR_0013</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>EXP_0010_1 was coordinated via CAR_0013 (Itinerancias role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>REL_306</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>EXP_0011_01</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CAR_0013</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>EXP_0011_01 was coordinated via CAR_0013 (Itinerancias role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>REL_307</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>EXP_0011_02</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>CAR_0013</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>EXP_0011_02 was coordinated via CAR_0013 (Itinerancias role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>REL_308</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>EXP_0011_03</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>CAR_0013</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>EXP_0011_03 was coordinated via CAR_0013 (Itinerancias role)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>REL_309</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>PRJ_0007</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>LOC_0013</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Harvard-UAI collaborative project includes research location at Harvard</t>
         </is>
       </c>
     </row>
@@ -22831,7 +22993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23911,6 +24073,89 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>Laboratorio de investigación | Infraestructura digital patrimonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CAR_0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Coordinador de Itinerancias Expositivas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ministerio de las Culturas, las Artes y el Patrimonio</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ORG_0008</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Planificación | Embalaje especializado | Conservación preventiva | Coordinación territorial | Montaje de exposiciones</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Coordinación nacional de itinerancias: Exposiciones del Centenario de Nemesio Antúnez (Pinacoteca UdeC, CECAL Chillán); *Violeta y sus contemporáneas* (Museo de Linares, Pinacoteca UdeC). Especialización en logística, conservación preventiva y circulación descentralizada de patrimonio visual.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.cultura.gob.cl</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Curaduría y descentralización | Circulación regional | Patrimonio visual</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -5734,7 +5734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6561,6 +6561,56 @@
       <c r="P11" t="inlineStr">
         <is>
           <t>Difusión audiovisual | Educación abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DIG_0006</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>QUINSAC: Catálogo Razonado Transnacional Monvoisin en América</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://quinsac.mnba.gob.cl/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Plataforma de consulta y gestión del catálogo razonado del proyecto transnacional Monvoisin en América</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Catálogo digital | Base de datos | Plataforma de investigación</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Museo Nacional de Bellas Artes (MNBA)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Proyecto Monvoisin en América | Investigación histórico-artística transnacional</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F309"/>
+  <dimension ref="A1:F312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15410,6 +15460,87 @@
       <c r="F309" t="inlineStr">
         <is>
           <t>Harvard-UAI collaborative project includes research location at Harvard</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>REL_310</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>dcat:produces</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>DIG_0006</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Proyecto Monvoisin genera producto digital QUINSAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>REL_311</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Exposición Episodio Monvoisin coordinada como parte del proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>REL_312</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>CAR_0014</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Rol investigador vinculado al proyecto</t>
         </is>
       </c>
     </row>
@@ -22993,7 +23124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24156,6 +24287,89 @@
       <c r="Q14" t="inlineStr">
         <is>
           <t>Curaduría y descentralización | Circulación regional | Patrimonio visual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CAR_0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investigador - Proyecto Monvoisin en América</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Museo Nacional de Bellas Artes (MNBA)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Investigación histórico-artística | Catalogación transnacional | Desarrollo de plataformas digitales | Gestión de datos patrimoniales</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Co-liderazgo en catastro transnacional de obra pictórica de Raymond Monvoisin y sus discípulos (Clara Filleul, Procesa Sarmiento, Gregorio Torres, Francisco Javier Mandiola) en museos y colecciones privadas de 4 países. Director técnico en desarrollo de producto digital QUINSAC para gestión y consulta del catálogo razonado.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://quinsac.mnba.gob.cl/</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Transnacional</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Investigación artística | Catalogación | Plataforma digital | Circulación transnacional</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6625,7 +6625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F312"/>
+  <dimension ref="A1:F314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15541,6 +15541,60 @@
       <c r="F312" t="inlineStr">
         <is>
           <t>Rol investigador vinculado al proyecto</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>REL_313</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>CAR_0015</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>EXP_0001</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Gestor coordinó logística de Exposición Episodio Monvoisin</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>REL_314</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>CAR_0017</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>crm:P14i_performed</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>EXP_DESACATOS</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Pasante en investigación para Exposición Desacatos</t>
         </is>
       </c>
     </row>
@@ -23124,7 +23178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23227,7 +23281,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
+          <t>Investigador de Colecciones</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -23241,19 +23295,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="G2" t="n">
         <v>2025</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Humanidades Digitales | CIDOC-CRM | Bases de Datos Relacionales | Conservación Preventiva | Logística Clavo a Clavo | Descolonización de Metadatos</t>
+          <t>Análisis histórico-artístico | Catalogación | Gestión de autoridades | Conservación preventiva | Administración de colecciones | Tramitación ante Consejo de Monumentos Nacionales</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Desarrollo plataforma web Quinsac | Implementación Plan Nacional de Patrimonios Digitales | Coordinación logística expo Episodio Monvoisin ($1.273M en seguros)</t>
+          <t>Análisis exhaustivo del acervo MNBA; ingreso y control de autoridades en bases de datos nacionales; tramitación de préstamos interinstitucionales; supervisión de conservación preventiva en sala durante montaje y exhibición</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -23288,12 +23342,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nacional | Transnacional</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Gestión patrimonial | Digitalización del acervo</t>
+          <t>Investigación patrimonial | Catalogación | Conservación</t>
         </is>
       </c>
     </row>
@@ -24370,6 +24424,255 @@
       <c r="Q15" t="inlineStr">
         <is>
           <t>Investigación artística | Catalogación | Plataforma digital | Circulación transnacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CAR_0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Gestor de Proyectos Patrimoniales</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Museo Nacional de Bellas Artes (MNBA)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Gestión presupuestaria | Licitaciones de servicios museológicos | Logística especializada | Conservación preventiva | Administración de seguros</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Liderazgo crítico en coordinación logística de la exposición "Episodio Monvoisin": 74 obras de gran formato desde 6 regiones, provenientes de 14 instituciones distintas. Gestión de transporte, embalaje especializado y seguros contra todo riesgo.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.mnba.gob.cl</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Gestión de proyectos | Logística patrimonial</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CAR_0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Punto Focal - Estrategia Nacional de Patrimonios Digitales (ENPD)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Museo Nacional de Bellas Artes / Subsecretaría del Patrimonio Cultural</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Humanidades Digitales | Estrategia de Patrimonios Digitales | Gestión de colecciones digitales | Políticas públicas de digitalización | Representación institucional</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Liderazgo como Punto Focal en delineación de la Estrategia Nacional de Patrimonios Digitales. Alineación del MNBA con Plan de Acción ENPD 2024-2029. Representante oficial ante Subsecretaría del Patrimonio Cultural para reportería y rendición de cuentas (período enero-junio 2025).</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.mnba.gob.cl</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Estrategia digital nacional | Políticas públicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CAR_0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Asistente de Investigación en Curatoría</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Museo Nacional de Bellas Artes (MNBA)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ORG_0002</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Investigación curatorial | Historia del arte feminista | Análisis histórico de acervos públicos</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Asistencia de investigación bajo dirección de Gloria Cortés Aliaga para la exposición "Desacatos. Prácticas artísticas femeninas 1835-1938", orientada a subvertir la omisión androcéntrica en el acervo público chileno.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.mnba.gob.cl</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-33.4352,-70.6439</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>[N/A]</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Formación | Historia del arte | Curaduría</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6625,38 +6625,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:I319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_relacion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_origen</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>predicado_cidoc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>id_destino</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion_semantica</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>nodo_origen</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>nodo_destino</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>año</t>
         </is>
       </c>
     </row>
@@ -6691,6 +6706,9 @@
           <t>Jaime Cuevas co-dirige y coordina el proyecto internacional Monvoisin en América</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6723,6 +6741,9 @@
           <t>Monvoisin en América produce el catálogo razonado y plataforma QUINSAC</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6755,6 +6776,9 @@
           <t>Monvoisin en América produce la cartografía interactiva StoryMaps</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6787,6 +6811,9 @@
           <t>Monvoisin en América produce el libro Monvoisin en América: Identidades, atribuciones y mercado</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6819,6 +6846,9 @@
           <t>Monvoisin en América produce el capítulo introductorio</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6851,6 +6881,9 @@
           <t>Monvoisin en América produce el capítulo sobre autenticidad y mercado</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6883,6 +6916,9 @@
           <t>Monvoisin en América produce el capítulo sobre catastro y Elisa Bravo</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6915,6 +6951,9 @@
           <t>Monvoisin en América sustenta curatorial y documentalmente la exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6947,6 +6986,9 @@
           <t>Episodio Monvoisin incluye traslado de obra monumental Cristo y Magdalena desde Concepción</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6979,6 +7021,9 @@
           <t>Episodio Monvoisin incluye traslado de obra José Tomás de Urmeneta desde Victoria</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7011,6 +7056,9 @@
           <t>Episodio Monvoisin incluye traslado de Palacio Cousiño</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7043,6 +7091,9 @@
           <t>Episodio Monvoisin incluye traslado de Abdicación de O'Higgins desde Maipú</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7075,6 +7126,9 @@
           <t>Monvoisin en América integra el Nodo Argentina - San Juan (Museo Franklin Rawson)</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7107,6 +7161,9 @@
           <t>Monvoisin en América integra el Nodo Argentina - Buenos Aires (IIPC-TAREA UNSAM)</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7139,6 +7196,9 @@
           <t>Monvoisin en América integra el Nodo Perú (MALI)</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7171,6 +7231,9 @@
           <t>Monvoisin en América integra el Nodo Brasil (Pinacoteca de São Paulo)</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7203,6 +7266,9 @@
           <t>Monvoisin en América es difundido en entrevista radial El Semáforo</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7235,6 +7301,9 @@
           <t>Monvoisin en América es analizado en podcast La Hora del Museo</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7267,6 +7336,9 @@
           <t>Monvoisin en América genera el ciclo de 5 conversatorios Live en Instagram MNBA</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7299,6 +7371,9 @@
           <t>Jaime Cuevas es Investigador Responsable del proyecto FONDART Arquitectura Art Déco</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7331,6 +7406,9 @@
           <t>Proyecto Art Déco produce el ecosistema digital semántico artdeco-santiago.cl</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7363,6 +7441,9 @@
           <t>Jaime Cuevas es Asistente de Investigación y Arquitecto de Datos en FONDECYT Mármoles y Bronces</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7395,6 +7476,9 @@
           <t>FONDECYT Mármoles y Bronces produce la plataforma analítica marmoles-y-bronces.vercel.app</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7427,6 +7511,9 @@
           <t>Jaime Cuevas es Director de Datos e Investigador en Callejera Madrid</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7459,6 +7546,9 @@
           <t>Jaime Cuevas es Investigador Responsable del FAIP Colección Marcos Segundo Maturana</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7491,6 +7581,9 @@
           <t>Proyecto Maturana produce el informe de investigación oficial FAIP 2021</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7523,6 +7616,9 @@
           <t>Jaime Cuevas es Coinvestigador en el FAIP Ausencias y omisiones femeninas</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7555,6 +7651,9 @@
           <t>Proyecto produce el informe de investigación oficial FAIP 2018</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7587,6 +7686,9 @@
           <t>Jaime Cuevas es Investigador Responsable del FONDART Creación Archivo Fotográfico Rodrigo Rojas De Negri (Folio 84311)</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7619,6 +7721,9 @@
           <t>FONDART 84311 produce el libro Rodrigo Rojas De Negri. Un exilio sin retorno (LOM Ediciones)</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7651,6 +7756,9 @@
           <t>FONDART 84311 produce la exposición A 30 años de Rodrigo Rojas De Negri en MMDH</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7683,6 +7791,9 @@
           <t>Jaime Cuevas es Responsable del proyecto Fondo Valentín Letelier Salón de Estudiantes 2013</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7715,6 +7826,9 @@
           <t>FVL-2011 produce la muestra Salón de Estudiantes 2013 en MAC Quinta Normal</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7747,6 +7861,9 @@
           <t>FVL-2011 produce la plataforma web salonestudiantes.cl</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7779,6 +7896,9 @@
           <t>FVL-2011 produce el catálogo y texto Matriz Imaginada</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7811,6 +7931,9 @@
           <t>Jaime Cuevas es autor del ensayo El canon revisitado galardonado por Fundación TyPA</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7843,6 +7966,9 @@
           <t>Ensayo corresponde a la Convocatoria Iberoamericana TyPA / Wikimedia Argentina</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7875,6 +8001,9 @@
           <t>Jaime Cuevas es Co-Curador de la exposición Adquisiciones en contexto en Sala Chile MNBA</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7907,6 +8036,9 @@
           <t>Exposición produce el catálogo oficial Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7939,6 +8071,9 @@
           <t>Exposición produce el librillo de mediación patrimonial</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7971,6 +8106,9 @@
           <t>Jaime Cuevas es Co-Curador y Coordinador Editorial de El canon revisitado</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8003,6 +8141,9 @@
           <t>Exposición produce el catálogo binacional El canon revisitado (MNBA / San Carlos)</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8035,6 +8176,9 @@
           <t>Jaime Cuevas es Curador Asistente en Crisis, crisis, crisis en Matucana 100</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8067,6 +8211,9 @@
           <t>Jaime Cuevas es Curador de la exposición individual Sonata en Isabel Croxatto Galería</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8099,6 +8246,9 @@
           <t>La exposición Sonata tiene lugar en Isabel Croxatto Galería</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8131,6 +8281,9 @@
           <t>Itinerancia Antúnez Estación Ñuble tiene lugar en CECAL UdeC Chillán</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8163,6 +8316,9 @@
           <t>Laboratorio Arte y Crisis incluye obras de la Colección MUSAC León España</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8195,6 +8351,9 @@
           <t>Jaime Cuevas co-ejecutó el proyecto FONDART Nacional 89451</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8227,6 +8386,9 @@
           <t>Montserrat Rojas Corradi fue la Editora Principal del FONDART 89451</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8259,6 +8421,9 @@
           <t>El FONDART 89451 produjo la publicación seriada S/T Revista de Fotografía</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8291,6 +8456,9 @@
           <t>S/T Revista fue co-editada y distribuida por LOM Ediciones</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8323,6 +8491,9 @@
           <t>FONDART Nacional 89451 fue financiado por CNCA / MINCAP</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8345,11 +8516,15 @@
           <t>ORG_0001</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Asistente Curatorial y de Exposiciones Temporales</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8372,11 +8547,15 @@
           <t>ORG_0002</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8399,11 +8578,15 @@
           <t>ORG_0004</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Profesor Universitario de Cátedra</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8426,11 +8609,15 @@
           <t>ORG_0006</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Investigador Independiente de Patrimonio</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8453,11 +8640,15 @@
           <t>ORG_0008</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Evaluador de Proyectos Culturales (FONDART)</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8480,11 +8671,15 @@
           <t>ORG_0011</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Asistente de Investigación y Catalogación</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8507,11 +8702,15 @@
           <t>ORG_0012</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Asistente de Investigación en Archivística y Documentación</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8534,11 +8733,15 @@
           <t>ORG_0022</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Co-Editor y Gestor Editorial</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8561,11 +8764,15 @@
           <t>ORG_0034</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Evaluador Externo (Arbitraje por pares ciego)</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8588,11 +8795,15 @@
           <t>ORG_0037</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Profesor de Estética y Diseño Múltiple</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8615,11 +8826,15 @@
           <t>ORG_0038</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Formación: Prevención de Riesgos</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8642,11 +8857,15 @@
           <t>ORG_0003</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8669,11 +8888,15 @@
           <t>ORG_0005</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Máster Universitario en Humanidades Digitales</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8696,11 +8919,15 @@
           <t>ORG_0007</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8723,11 +8950,15 @@
           <t>ORG_0009</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Diplomado en Gobierno y Gestión Pública</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8750,11 +8981,15 @@
           <t>ORG_0010</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Diplomado en Museos y Museología (IDEA)</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8777,11 +9012,15 @@
           <t>ORG_0013</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8804,11 +9043,15 @@
           <t>ORG_0014</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Equivalencia a nivel académico de Grado en España</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8831,11 +9074,15 @@
           <t>ORG_0033</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Curso Estatuto Administrativo</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8858,11 +9105,15 @@
           <t>ORG_0035</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8885,11 +9136,15 @@
           <t>ORG_0036</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8912,11 +9167,15 @@
           <t>PER_0008</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Co-curador: Camila Caris Seguel</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8939,11 +9198,15 @@
           <t>PER_0004</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Co-curador: Manuel Alvarado Cornejo</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8966,11 +9229,15 @@
           <t>PER_0011</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Co-curadora: Montserrat Rojas Corradi</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8993,11 +9260,15 @@
           <t>PER_0011</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Colaboración en exposiciones</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9025,6 +9296,10 @@
           <t>Rodrigo Rojas De Negri es sujeto del FONDART Archivo Fotográfico</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9052,6 +9327,10 @@
           <t>Rodrigo Rojas De Negri es sujeto del libro de investigación</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9079,6 +9358,10 @@
           <t>Exposición "A 30 años de Rodrigo Rojas de Negri" (2016)</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9106,6 +9389,10 @@
           <t>Exposición "Un exilio sin retorno. Rodrigo Rojas De Negri"</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9133,6 +9420,10 @@
           <t>Rodrigo Rojas De Negri residió en exilio en Washington D.C.</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9160,6 +9451,10 @@
           <t>Tema de charla de mediación curatorial</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9187,6 +9482,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9214,6 +9513,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M01</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9241,6 +9544,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M02</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9268,6 +9575,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M03</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9295,6 +9606,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M04</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9322,6 +9637,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M05</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9349,6 +9668,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M06</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9376,6 +9699,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M07</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9403,6 +9730,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M08</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9430,6 +9761,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M09</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9457,6 +9792,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M10</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9484,6 +9823,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M11</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9511,6 +9854,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M12</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9538,6 +9885,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M13</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9565,6 +9916,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0002</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9592,6 +9947,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0005</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9619,6 +9978,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0006</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9646,6 +10009,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0007</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9673,6 +10040,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0008</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9700,6 +10071,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0009</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9727,6 +10102,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9754,6 +10133,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010_1</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9781,6 +10164,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_01</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9808,6 +10195,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_02</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9835,6 +10226,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_03</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9862,6 +10257,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0001</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9889,6 +10288,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0002</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9916,6 +10319,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0003</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9943,6 +10350,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0004</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9970,6 +10381,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0005</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9997,6 +10412,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0006</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10024,6 +10443,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0007</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10051,6 +10474,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0008</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10078,6 +10505,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0009</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10105,6 +10536,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0010</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10132,6 +10567,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0011</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10159,6 +10598,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0012</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10186,6 +10629,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0013</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10213,6 +10660,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0014</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10240,6 +10691,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0015</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10267,6 +10722,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0016</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10294,6 +10753,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0017</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10321,6 +10784,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0018</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10348,6 +10815,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0019</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10375,6 +10846,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0020</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10402,6 +10877,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0021</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10429,6 +10908,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0022</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10456,6 +10939,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0023</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10483,6 +10970,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0024</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10510,6 +11001,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0025</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10537,6 +11032,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0026</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10564,6 +11063,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0027</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10591,6 +11094,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0003</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10618,6 +11125,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0004</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10645,6 +11156,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0007</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10672,6 +11187,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N01</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10699,6 +11218,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N02</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10726,6 +11249,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N03</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10753,6 +11280,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N04</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10780,6 +11311,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0011</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10807,6 +11342,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0012</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10834,6 +11373,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0013</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10861,6 +11404,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0014</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10888,6 +11435,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0015</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10915,6 +11466,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0001</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10942,6 +11497,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0002</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10969,6 +11528,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0003</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10996,6 +11559,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0004</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11023,6 +11590,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0006</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11050,6 +11621,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0007</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11077,6 +11652,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0008</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11104,6 +11683,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0009</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11131,6 +11714,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0010</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11158,6 +11745,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0011</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11185,6 +11776,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0012</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11212,6 +11807,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0013</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11239,6 +11838,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0014</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11266,6 +11869,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0015</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11293,6 +11900,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0016</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11320,6 +11931,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0017</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11347,6 +11962,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0018</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11374,6 +11993,10 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0003</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11401,6 +12024,10 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0004</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11428,6 +12055,10 @@
           <t>Camila Caris Seguel participated/curated EXP_0002</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11455,6 +12086,10 @@
           <t>Camila Caris Seguel participated/curated EXP_0008</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11482,6 +12117,10 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0007</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11509,6 +12148,10 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11539,6 +12182,9 @@
           <t>Gloria Cortés co-editó y co-autorizó el libro Monvoisin en América</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11571,6 +12217,9 @@
           <t>Gloria Cortés co-dirige el proyecto Monvoisin en América</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11603,6 +12252,9 @@
           <t>Antonia Viu participó en proyecto Cultures of reading</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11635,6 +12287,9 @@
           <t>Katherine Vyhmeister trabajó en proyecto Arquitectura Art Déco</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11667,6 +12322,9 @@
           <t>Jaime Cuevas fue asistente de investigación de Fernando Guzmán en la UAI</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11699,6 +12357,9 @@
           <t>Jaime Cuevas fue asistente de investigación de Marcela Drien en la UAI</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11731,6 +12392,9 @@
           <t>Jaime Cuevas fue asistente de investigación de Katherine Vyhmeister en la UAI</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11761,6 +12425,9 @@
           <t>Jaime Cuevas participó en congreso internacional de CAIA en Buenos Aires</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11791,6 +12458,9 @@
           <t>Jaime Cuevas ganó Premio Iberoamericano de Wikimedia Argentina/TyPA</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11821,6 +12491,9 @@
           <t>Jaime Cuevas participó/curó exposición de Corporación CCU</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11853,6 +12526,9 @@
           <t>Antonia Viu realizó pasantía académica en Harvard University</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11883,6 +12559,9 @@
           <t>Laura Rodig fue artista principal en exposición Desacatos</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11915,6 +12594,9 @@
           <t>Estefanía Granja desarrolló plataforma digital de Callejera Madrid</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11947,6 +12629,9 @@
           <t>Jaime Cuevas participó en curación de Callejera Madrid</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11977,6 +12662,9 @@
           <t>Raymond Monvoisin es sujeto principal de Monvoisin en América</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12007,6 +12695,9 @@
           <t>Monvoisin es tema central en introducción</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12037,6 +12728,9 @@
           <t>Catastro y documentación de obra de Monvoisin</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12067,6 +12761,9 @@
           <t>Clara Filleul mencionada en estudio de comercialización</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12097,6 +12794,9 @@
           <t>Clara Filleul es sujeto de investigación sobre discipulaje</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12127,6 +12827,9 @@
           <t>Procesa Sarmiento es sujeto de investigación sobre discipulaje</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12157,6 +12860,9 @@
           <t>Alessandro Ciccarelli es sujeto único del artículo sobre Fuerte Bulnes</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12187,6 +12893,9 @@
           <t>Iván Navarro participó en exposición La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12217,6 +12926,9 @@
           <t>Alfredo Jaar participó en exposición La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12247,6 +12959,9 @@
           <t>Voluspa Jarpa participó en exposición La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12277,6 +12992,9 @@
           <t>Iván Navarro es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12307,6 +13025,9 @@
           <t>Alfredo Jaar es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12337,6 +13058,9 @@
           <t>Voluspa Jarpa es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12367,6 +13091,9 @@
           <t>Raymond Monvoisin es artista principal en Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12397,6 +13124,9 @@
           <t>Clara Filleul participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12427,6 +13157,9 @@
           <t>Procesa Sarmiento participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12457,6 +13190,9 @@
           <t>Gregorio Torres participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12487,6 +13223,9 @@
           <t>Francisco Javier Mandiola participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12519,6 +13258,9 @@
           <t>Raymond Monvoisin es sujeto del proyecto Monvoisin en América</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12549,6 +13291,9 @@
           <t>Clara Filleul es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12579,6 +13324,9 @@
           <t>Procesa Sarmiento es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12609,6 +13357,9 @@
           <t>Milencka Vidal co-autora de Catastro y visualidad de afromestizos</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12639,6 +13390,9 @@
           <t>Daniela Colleoni co-autora de Matriz imaginada</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12669,6 +13423,9 @@
           <t>Jesús Arana participó en Prácticas de reiteración</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12699,6 +13456,9 @@
           <t>Gonzalo Cueto participó en Crisis, crisis, crisis</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12729,6 +13489,9 @@
           <t>Oskar Trepte participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12759,6 +13522,9 @@
           <t>Pedro Reszka Moreau participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12789,6 +13555,9 @@
           <t>Virginio Arias Cruz participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12819,6 +13588,9 @@
           <t>Benito Rebolledo Correa participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12849,6 +13621,9 @@
           <t>Aristodemo Lattanzi Borghini participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12879,6 +13654,9 @@
           <t>Violeta Parra artista en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12909,6 +13687,9 @@
           <t>Inés Puyó participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12939,6 +13720,9 @@
           <t>Ximena Cristi participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12969,6 +13753,9 @@
           <t>Laura Rodig participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12999,6 +13786,9 @@
           <t>Henriette Petit participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13029,6 +13819,9 @@
           <t>Nemesio Antúnez en centenario - Estación Ñuble</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13059,6 +13852,9 @@
           <t>Nemesio Antúnez en centenario - Estación Biobío</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13089,6 +13885,9 @@
           <t>Nemesio Antúnez en centenario - Estación Maule</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13119,6 +13918,9 @@
           <t>Luis Camnitzer participó en Sala de Fotografía Emergente</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13149,6 +13951,9 @@
           <t>Wladymir Bernechea artista en Sonata</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13179,6 +13984,9 @@
           <t>Rodrigo Rojas De Negri en A 30 años</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13209,6 +14017,9 @@
           <t>Rodrigo Rojas De Negri en Un exilio sin retorno</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13231,11 +14042,15 @@
           <t>LOC_0058</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin registra colecciones en Nancagua</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13258,11 +14073,15 @@
           <t>LOC_0058</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>Traslado de colección privada en Nancagua</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13285,11 +14104,15 @@
           <t>ORG_0002</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>Colección documentada en contexto de investigación MNBA</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13312,11 +14135,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Jaime participó en entrevista radial</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13339,11 +14166,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Comunicación trata sobre exposición</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13366,11 +14197,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Jaime participó en podcast</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13393,11 +14228,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Podcast trata sobre Monvoisin en América</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13420,11 +14259,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13447,11 +14290,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Ponencia resultado de investigación Monvoisin</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13474,11 +14321,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13501,11 +14352,15 @@
           <t>PRJ_0006</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto Clara Filleul</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13528,11 +14383,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Jaime mencionado como experto</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13555,11 +14414,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Reportaje trata sobre exposición Monvoisin</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13582,11 +14445,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>Jaime condujo ciclo de Instagram</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13609,11 +14476,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>Ciclo divulga proyecto Monvoisin</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13636,11 +14507,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>Jaime participó en lanzamiento</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13663,11 +14538,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>Lanzamiento presenta proyecto Monvoisin</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13690,11 +14569,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>Jaime creó/participó en cápsula</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13717,11 +14600,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>Cápsula trata sobre exposición Monvoisin</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13744,11 +14631,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13771,11 +14662,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13798,11 +14693,15 @@
           <t>PRJ_0006</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13825,11 +14724,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Ponencia se relaciona con Monvoisin</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13852,11 +14755,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia en UNIFESP</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13879,11 +14786,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13906,11 +14817,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13933,11 +14848,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13960,11 +14879,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13987,11 +14910,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Jaime dio charla de mediación</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14014,11 +14941,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Jaime organizó y moderó encuentro</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14041,11 +14972,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Jaime dio charla especializada</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14068,11 +15003,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Jaime dio charla de archivo</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14095,11 +15034,15 @@
           <t>EXP_0008</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Charla trata sobre Salón de Estudiantes 2013</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14122,11 +15065,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Jaime presentó modelo de gestión</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14149,11 +15096,15 @@
           <t>EXP_0008</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Presentación trata sobre Salón de Estudiantes</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14176,11 +15127,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14203,11 +15158,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14230,11 +15189,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Jaime curó conversatorio</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14257,11 +15220,15 @@
           <t>EXP_0003</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Conversatorio trata sobre exposición</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14284,11 +15251,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Jaime hizo visita mediada</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14311,11 +15282,15 @@
           <t>EXP_0003</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Visita mediada trata sobre exposición</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14338,11 +15313,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>Jaime es sujeto/experto mencionado</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14365,11 +15344,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>Entrevista trata sobre Monvoisin</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14392,11 +15375,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>Jaime es experto mencionado en noticia</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14419,11 +15406,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia técnica</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14451,6 +15442,10 @@
           <t>Communication produces digital resource (QUINSAC platform launch)</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14473,11 +15468,15 @@
           <t>PRJ_0009</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>Charla Artistas del Acero es producto de investigación Archivo Fotográfico Rodrigo Rojas</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14500,11 +15499,15 @@
           <t>PRJ_0010</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>Matriz Imaginada es producto de investigación Salón de Estudiantes (FVL + FDI)</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14527,11 +15530,15 @@
           <t>PRJ_0010</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>Presentación Tabacalera Madrid es producto de investigación Salón de Estudiantes</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14554,11 +15561,15 @@
           <t>EXP_0006</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>Charla sobre archivo Rodrigo Rojas trata exposición A 30 años (Museo Memoria DDHH)</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14581,11 +15592,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>Marcela Drien participó en proyecto Monvoisin</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14616,6 +15631,9 @@
           <t>Proyecto Monvoisin produjo libro colectivo</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14646,6 +15664,9 @@
           <t>Proyecto Archivo Rodrigo Rojas produjo libro</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14676,6 +15697,9 @@
           <t>Exposición produjo catálogo investigación SNBA</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14706,6 +15730,9 @@
           <t>Exposición produjo catálogo arte europeo/latinoamericano</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14736,6 +15763,9 @@
           <t>Exposición CCU produjo catálogo curatorial</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14766,6 +15796,9 @@
           <t>Proyecto Salón de Estudiantes produjo catálogo</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14796,6 +15829,9 @@
           <t>Prólogo del libro Monvoisin en América</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14826,6 +15862,9 @@
           <t>Capítulo sobre mercado de arte en libro Monvoisin</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14856,6 +15895,9 @@
           <t>Proyecto Coleccionismo Chile siglo XIX produjo capítulo</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14886,6 +15928,9 @@
           <t>Capítulo sobre catastro Monvoisin en libro investigación</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14916,6 +15961,9 @@
           <t>Proyecto Clara Filleul/Procesa produjo capítulo género</t>
         </is>
       </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14946,6 +15994,9 @@
           <t>Proyecto Revista Fotografía FONDART produjo publicación periódica</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14976,6 +16027,9 @@
           <t>Exposición Desacatos produjo comentario obra en catálogo</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15006,6 +16060,9 @@
           <t>Charla sobre curaduría archivo Rodrigo Rojas trata sobre exposición</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15036,6 +16093,9 @@
           <t>Nota de prensa trata sobre traslado Cristo y Magdalena</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15066,6 +16126,9 @@
           <t>Magister Historia del Arte UAI produjo libro catastro afromestizos</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15096,6 +16159,9 @@
           <t>Magister Historia del Arte UAI produjo artículo científico afromestizos</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15126,6 +16192,9 @@
           <t>Magister Historia del Arte UAI produjo capítulo visualidades</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15158,6 +16227,9 @@
           <t>Media</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15180,11 +16252,15 @@
           <t>LOC_0041</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15207,11 +16283,15 @@
           <t>LOC_0005</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>Máster en Humanidades Digitales se cursó en UB FIMA</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15234,6 +16314,11 @@
           <t>LOC_0062</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15256,6 +16341,11 @@
           <t>LOC_0064</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15278,6 +16368,11 @@
           <t>LOC_0048</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15300,6 +16395,11 @@
           <t>LOC_0063</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15322,11 +16422,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>EXP_0010 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15349,11 +16453,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>EXP_0010_1 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15376,11 +16484,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>EXP_0011_01 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15403,11 +16515,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>EXP_0011_02 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15430,11 +16546,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>EXP_0011_03 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15457,11 +16577,15 @@
           <t>LOC_0013</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>Harvard-UAI collaborative project includes research location at Harvard</t>
         </is>
       </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15484,11 +16608,15 @@
           <t>DIG_0006</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin genera producto digital QUINSAC</t>
         </is>
       </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15511,11 +16639,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>Exposición Episodio Monvoisin coordinada como parte del proyecto</t>
         </is>
       </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15538,11 +16670,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>Rol investigador vinculado al proyecto</t>
         </is>
       </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15565,11 +16701,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>Gestor coordinó logística de Exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15592,9 +16732,228 @@
           <t>EXP_DESACATOS</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>Pasante en investigación para Exposición Desacatos</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>REL_0320</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LOC_0016</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Brasil tomó lugar en Pinacoteca do Estado</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>LOC_0016</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>REL_0321</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>LOC_0017</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Argentina (San Juan) tomó lugar en Museo Franklin Rawson</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>LOC_0017</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>REL_0322</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>LOC_0014</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Argentina (Buenos Aires) tomó lugar en Fundación TyPA/CAIA UBA</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>LOC_0014</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>REL_0323</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>LOC_0018</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Argentina (Buenos Aires) tomó lugar en IIPC-TAREA, UNSAM</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>LOC_0018</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>REL_0324</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>crm:P14_carried_out_by</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas realizó investigación en Monvoisin en América</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6625,38 +6625,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:I325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_relacion</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id_origen</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>predicado_cidoc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>id_destino</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ano</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion_semantica</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>nodo_origen</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>nodo_destino</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>año</t>
         </is>
       </c>
     </row>
@@ -6691,6 +6706,9 @@
           <t>Jaime Cuevas co-dirige y coordina el proyecto internacional Monvoisin en América</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6723,6 +6741,9 @@
           <t>Monvoisin en América produce el catálogo razonado y plataforma QUINSAC</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6755,6 +6776,9 @@
           <t>Monvoisin en América produce la cartografía interactiva StoryMaps</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6787,6 +6811,9 @@
           <t>Monvoisin en América produce el libro Monvoisin en América: Identidades, atribuciones y mercado</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6819,6 +6846,9 @@
           <t>Monvoisin en América produce el capítulo introductorio</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6851,6 +6881,9 @@
           <t>Monvoisin en América produce el capítulo sobre autenticidad y mercado</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6883,6 +6916,9 @@
           <t>Monvoisin en América produce el capítulo sobre catastro y Elisa Bravo</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6915,6 +6951,9 @@
           <t>Monvoisin en América sustenta curatorial y documentalmente la exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6947,6 +6986,9 @@
           <t>Episodio Monvoisin incluye traslado de obra monumental Cristo y Magdalena desde Concepción</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6979,6 +7021,9 @@
           <t>Episodio Monvoisin incluye traslado de obra José Tomás de Urmeneta desde Victoria</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7011,6 +7056,9 @@
           <t>Episodio Monvoisin incluye traslado de Palacio Cousiño</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7043,6 +7091,9 @@
           <t>Episodio Monvoisin incluye traslado de Abdicación de O'Higgins desde Maipú</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7075,6 +7126,9 @@
           <t>Monvoisin en América integra el Nodo Argentina - San Juan (Museo Franklin Rawson)</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7107,6 +7161,9 @@
           <t>Monvoisin en América integra el Nodo Argentina - Buenos Aires (IIPC-TAREA UNSAM)</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7139,6 +7196,9 @@
           <t>Monvoisin en América integra el Nodo Perú (MALI)</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7171,6 +7231,9 @@
           <t>Monvoisin en América integra el Nodo Brasil (Pinacoteca de São Paulo)</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7203,6 +7266,9 @@
           <t>Monvoisin en América es difundido en entrevista radial El Semáforo</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7235,6 +7301,9 @@
           <t>Monvoisin en América es analizado en podcast La Hora del Museo</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7267,6 +7336,9 @@
           <t>Monvoisin en América genera el ciclo de 5 conversatorios Live en Instagram MNBA</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7299,6 +7371,9 @@
           <t>Jaime Cuevas es Investigador Responsable del proyecto FONDART Arquitectura Art Déco</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7331,6 +7406,9 @@
           <t>Proyecto Art Déco produce el ecosistema digital semántico artdeco-santiago.cl</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7363,6 +7441,9 @@
           <t>Jaime Cuevas es Asistente de Investigación y Arquitecto de Datos en FONDECYT Mármoles y Bronces</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7395,6 +7476,9 @@
           <t>FONDECYT Mármoles y Bronces produce la plataforma analítica marmoles-y-bronces.vercel.app</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7427,6 +7511,9 @@
           <t>Jaime Cuevas es Director de Datos e Investigador en Callejera Madrid</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7459,6 +7546,9 @@
           <t>Jaime Cuevas es Investigador Responsable del FAIP Colección Marcos Segundo Maturana</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7491,6 +7581,9 @@
           <t>Proyecto Maturana produce el informe de investigación oficial FAIP 2021</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7523,6 +7616,9 @@
           <t>Jaime Cuevas es Coinvestigador en el FAIP Ausencias y omisiones femeninas</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7555,6 +7651,9 @@
           <t>Proyecto produce el informe de investigación oficial FAIP 2018</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7587,6 +7686,9 @@
           <t>Jaime Cuevas es Investigador Responsable del FONDART Creación Archivo Fotográfico Rodrigo Rojas De Negri (Folio 84311)</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7619,6 +7721,9 @@
           <t>FONDART 84311 produce el libro Rodrigo Rojas De Negri. Un exilio sin retorno (LOM Ediciones)</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7651,6 +7756,9 @@
           <t>FONDART 84311 produce la exposición A 30 años de Rodrigo Rojas De Negri en MMDH</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7683,6 +7791,9 @@
           <t>Jaime Cuevas es Responsable del proyecto Fondo Valentín Letelier Salón de Estudiantes 2013</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7715,6 +7826,9 @@
           <t>FVL-2011 produce la muestra Salón de Estudiantes 2013 en MAC Quinta Normal</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7747,6 +7861,9 @@
           <t>FVL-2011 produce la plataforma web salonestudiantes.cl</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7779,6 +7896,9 @@
           <t>FVL-2011 produce el catálogo y texto Matriz Imaginada</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7811,6 +7931,9 @@
           <t>Jaime Cuevas es autor del ensayo El canon revisitado galardonado por Fundación TyPA</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7843,6 +7966,9 @@
           <t>Ensayo corresponde a la Convocatoria Iberoamericana TyPA / Wikimedia Argentina</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7875,6 +8001,9 @@
           <t>Jaime Cuevas es Co-Curador de la exposición Adquisiciones en contexto en Sala Chile MNBA</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7907,6 +8036,9 @@
           <t>Exposición produce el catálogo oficial Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7939,6 +8071,9 @@
           <t>Exposición produce el librillo de mediación patrimonial</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7971,6 +8106,9 @@
           <t>Jaime Cuevas es Co-Curador y Coordinador Editorial de El canon revisitado</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8003,6 +8141,9 @@
           <t>Exposición produce el catálogo binacional El canon revisitado (MNBA / San Carlos)</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8035,6 +8176,9 @@
           <t>Jaime Cuevas es Curador Asistente en Crisis, crisis, crisis en Matucana 100</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8067,6 +8211,9 @@
           <t>Jaime Cuevas es Curador de la exposición individual Sonata en Isabel Croxatto Galería</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8099,6 +8246,9 @@
           <t>La exposición Sonata tiene lugar en Isabel Croxatto Galería</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8131,6 +8281,9 @@
           <t>Itinerancia Antúnez Estación Ñuble tiene lugar en CECAL UdeC Chillán</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8163,6 +8316,9 @@
           <t>Laboratorio Arte y Crisis incluye obras de la Colección MUSAC León España</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8195,6 +8351,9 @@
           <t>Jaime Cuevas co-ejecutó el proyecto FONDART Nacional 89451</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8227,6 +8386,9 @@
           <t>Montserrat Rojas Corradi fue la Editora Principal del FONDART 89451</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8259,6 +8421,9 @@
           <t>El FONDART 89451 produjo la publicación seriada S/T Revista de Fotografía</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8291,6 +8456,9 @@
           <t>S/T Revista fue co-editada y distribuida por LOM Ediciones</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8323,6 +8491,9 @@
           <t>FONDART Nacional 89451 fue financiado por CNCA / MINCAP</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8345,11 +8516,15 @@
           <t>ORG_0001</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Asistente Curatorial y de Exposiciones Temporales</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8372,11 +8547,15 @@
           <t>ORG_0002</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8399,11 +8578,15 @@
           <t>ORG_0004</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Profesor Universitario de Cátedra</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8426,11 +8609,15 @@
           <t>ORG_0006</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Investigador Independiente de Patrimonio</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8453,11 +8640,15 @@
           <t>ORG_0008</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Evaluador de Proyectos Culturales (FONDART)</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8480,11 +8671,15 @@
           <t>ORG_0011</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Asistente de Investigación y Catalogación</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8507,11 +8702,15 @@
           <t>ORG_0012</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Asistente de Investigación en Archivística y Documentación</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8534,11 +8733,15 @@
           <t>ORG_0022</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Co-Editor y Gestor Editorial</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8561,11 +8764,15 @@
           <t>ORG_0034</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Evaluador Externo (Arbitraje por pares ciego)</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8588,11 +8795,15 @@
           <t>ORG_0037</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Profesor de Estética y Diseño Múltiple</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8615,11 +8826,15 @@
           <t>ORG_0038</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Formación: Prevención de Riesgos</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8642,11 +8857,15 @@
           <t>ORG_0003</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8669,11 +8888,15 @@
           <t>ORG_0005</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Máster Universitario en Humanidades Digitales</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8696,11 +8919,15 @@
           <t>ORG_0007</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8723,11 +8950,15 @@
           <t>ORG_0009</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Diplomado en Gobierno y Gestión Pública</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8750,11 +8981,15 @@
           <t>ORG_0010</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Diplomado en Museos y Museología (IDEA)</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8777,11 +9012,15 @@
           <t>ORG_0013</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8804,11 +9043,15 @@
           <t>ORG_0014</t>
         </is>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Equivalencia a nivel académico de Grado en España</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8831,11 +9074,15 @@
           <t>ORG_0033</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Curso Estatuto Administrativo</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8858,11 +9105,15 @@
           <t>ORG_0035</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8885,11 +9136,15 @@
           <t>ORG_0036</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8912,11 +9167,15 @@
           <t>PER_0008</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Co-curador: Camila Caris Seguel</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8939,11 +9198,15 @@
           <t>PER_0004</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Co-curador: Manuel Alvarado Cornejo</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8966,11 +9229,15 @@
           <t>PER_0011</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Co-curadora: Montserrat Rojas Corradi</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8993,11 +9260,15 @@
           <t>PER_0011</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Colaboración en exposiciones</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9025,6 +9296,10 @@
           <t>Rodrigo Rojas De Negri es sujeto del FONDART Archivo Fotográfico</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9052,6 +9327,10 @@
           <t>Rodrigo Rojas De Negri es sujeto del libro de investigación</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9079,6 +9358,10 @@
           <t>Exposición "A 30 años de Rodrigo Rojas de Negri" (2016)</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9106,6 +9389,10 @@
           <t>Exposición "Un exilio sin retorno. Rodrigo Rojas De Negri"</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9133,6 +9420,10 @@
           <t>Rodrigo Rojas De Negri residió en exilio en Washington D.C.</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9160,6 +9451,10 @@
           <t>Tema de charla de mediación curatorial</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9187,6 +9482,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9214,6 +9513,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M01</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9241,6 +9544,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M02</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9268,6 +9575,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M03</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9295,6 +9606,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M04</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9322,6 +9637,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M05</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9349,6 +9668,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M06</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9376,6 +9699,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M07</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9403,6 +9730,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M08</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9430,6 +9761,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M09</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9457,6 +9792,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M10</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9484,6 +9823,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M11</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9511,6 +9854,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M12</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9538,6 +9885,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M13</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9565,6 +9916,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0002</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9592,6 +9947,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0005</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9619,6 +9978,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0006</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9646,6 +10009,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0007</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9673,6 +10040,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0008</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9700,6 +10071,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0009</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9727,6 +10102,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9754,6 +10133,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010_1</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9781,6 +10164,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_01</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9808,6 +10195,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_02</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -9835,6 +10226,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_03</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -9862,6 +10257,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0001</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9889,6 +10288,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0002</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9916,6 +10319,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0003</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9943,6 +10350,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0004</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9970,6 +10381,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0005</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9997,6 +10412,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0006</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10024,6 +10443,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0007</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10051,6 +10474,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0008</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10078,6 +10505,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0009</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10105,6 +10536,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0010</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10132,6 +10567,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0011</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10159,6 +10598,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0012</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10186,6 +10629,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0013</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10213,6 +10660,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0014</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10240,6 +10691,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0015</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10267,6 +10722,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0016</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10294,6 +10753,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0017</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10321,6 +10784,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0018</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10348,6 +10815,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0019</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10375,6 +10846,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0020</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10402,6 +10877,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0021</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10429,6 +10908,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0022</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10456,6 +10939,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0023</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10483,6 +10970,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0024</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10510,6 +11001,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0025</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10537,6 +11032,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0026</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -10564,6 +11063,10 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0027</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -10591,6 +11094,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0003</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10618,6 +11125,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0004</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10645,6 +11156,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0007</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10672,6 +11187,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N01</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10699,6 +11218,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N02</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10726,6 +11249,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N03</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10753,6 +11280,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N04</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10780,6 +11311,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0011</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10807,6 +11342,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0012</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10834,6 +11373,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0013</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10861,6 +11404,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0014</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10888,6 +11435,10 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0015</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10915,6 +11466,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0001</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10942,6 +11497,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0002</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10969,6 +11528,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0003</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10996,6 +11559,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0004</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11023,6 +11590,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0006</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11050,6 +11621,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0007</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11077,6 +11652,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0008</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11104,6 +11683,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0009</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11131,6 +11714,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0010</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11158,6 +11745,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0011</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11185,6 +11776,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0012</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11212,6 +11807,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0013</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11239,6 +11838,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0014</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11266,6 +11869,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0015</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11293,6 +11900,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0016</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11320,6 +11931,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0017</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11347,6 +11962,10 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0018</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11374,6 +11993,10 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0003</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11401,6 +12024,10 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0004</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11428,6 +12055,10 @@
           <t>Camila Caris Seguel participated/curated EXP_0002</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11455,6 +12086,10 @@
           <t>Camila Caris Seguel participated/curated EXP_0008</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11482,6 +12117,10 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0007</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11509,6 +12148,10 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11539,6 +12182,9 @@
           <t>Gloria Cortés co-editó y co-autorizó el libro Monvoisin en América</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11571,6 +12217,9 @@
           <t>Gloria Cortés co-dirige el proyecto Monvoisin en América</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11603,6 +12252,9 @@
           <t>Antonia Viu participó en proyecto Cultures of reading</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11635,6 +12287,9 @@
           <t>Katherine Vyhmeister trabajó en proyecto Arquitectura Art Déco</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11667,6 +12322,9 @@
           <t>Jaime Cuevas fue asistente de investigación de Fernando Guzmán en la UAI</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11699,6 +12357,9 @@
           <t>Jaime Cuevas fue asistente de investigación de Marcela Drien en la UAI</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11731,6 +12392,9 @@
           <t>Jaime Cuevas fue asistente de investigación de Katherine Vyhmeister en la UAI</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11761,6 +12425,9 @@
           <t>Jaime Cuevas participó en congreso internacional de CAIA en Buenos Aires</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11791,6 +12458,9 @@
           <t>Jaime Cuevas ganó Premio Iberoamericano de Wikimedia Argentina/TyPA</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11821,6 +12491,9 @@
           <t>Jaime Cuevas participó/curó exposición de Corporación CCU</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11853,6 +12526,9 @@
           <t>Antonia Viu realizó pasantía académica en Harvard University</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11883,6 +12559,9 @@
           <t>Laura Rodig fue artista principal en exposición Desacatos</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11915,6 +12594,9 @@
           <t>Estefanía Granja desarrolló plataforma digital de Callejera Madrid</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11947,6 +12629,9 @@
           <t>Jaime Cuevas participó en curación de Callejera Madrid</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11977,6 +12662,9 @@
           <t>Raymond Monvoisin es sujeto principal de Monvoisin en América</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12007,6 +12695,9 @@
           <t>Monvoisin es tema central en introducción</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12037,6 +12728,9 @@
           <t>Catastro y documentación de obra de Monvoisin</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12067,6 +12761,9 @@
           <t>Clara Filleul mencionada en estudio de comercialización</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12097,6 +12794,9 @@
           <t>Clara Filleul es sujeto de investigación sobre discipulaje</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12127,6 +12827,9 @@
           <t>Procesa Sarmiento es sujeto de investigación sobre discipulaje</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12157,6 +12860,9 @@
           <t>Alessandro Ciccarelli es sujeto único del artículo sobre Fuerte Bulnes</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12187,6 +12893,9 @@
           <t>Iván Navarro participó en exposición La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12217,6 +12926,9 @@
           <t>Alfredo Jaar participó en exposición La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12247,6 +12959,9 @@
           <t>Voluspa Jarpa participó en exposición La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12277,6 +12992,9 @@
           <t>Iván Navarro es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12307,6 +13025,9 @@
           <t>Alfredo Jaar es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12337,6 +13058,9 @@
           <t>Voluspa Jarpa es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12367,6 +13091,9 @@
           <t>Raymond Monvoisin es artista principal en Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12397,6 +13124,9 @@
           <t>Clara Filleul participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12427,6 +13157,9 @@
           <t>Procesa Sarmiento participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12457,6 +13190,9 @@
           <t>Gregorio Torres participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12487,6 +13223,9 @@
           <t>Francisco Javier Mandiola participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12519,6 +13258,9 @@
           <t>Raymond Monvoisin es sujeto del proyecto Monvoisin en América</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12549,6 +13291,9 @@
           <t>Clara Filleul es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12579,6 +13324,9 @@
           <t>Procesa Sarmiento es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12609,6 +13357,9 @@
           <t>Milencka Vidal co-autora de Catastro y visualidad de afromestizos</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12639,6 +13390,9 @@
           <t>Daniela Colleoni co-autora de Matriz imaginada</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12669,6 +13423,9 @@
           <t>Jesús Arana participó en Prácticas de reiteración</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12699,6 +13456,9 @@
           <t>Gonzalo Cueto participó en Crisis, crisis, crisis</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12729,6 +13489,9 @@
           <t>Oskar Trepte participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12759,6 +13522,9 @@
           <t>Pedro Reszka Moreau participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12789,6 +13555,9 @@
           <t>Virginio Arias Cruz participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12819,6 +13588,9 @@
           <t>Benito Rebolledo Correa participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12849,6 +13621,9 @@
           <t>Aristodemo Lattanzi Borghini participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12879,6 +13654,9 @@
           <t>Violeta Parra artista en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12909,6 +13687,9 @@
           <t>Inés Puyó participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12939,6 +13720,9 @@
           <t>Ximena Cristi participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12969,6 +13753,9 @@
           <t>Laura Rodig participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12999,6 +13786,9 @@
           <t>Henriette Petit participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13029,6 +13819,9 @@
           <t>Nemesio Antúnez en centenario - Estación Ñuble</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13059,6 +13852,9 @@
           <t>Nemesio Antúnez en centenario - Estación Biobío</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13089,6 +13885,9 @@
           <t>Nemesio Antúnez en centenario - Estación Maule</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13119,6 +13918,9 @@
           <t>Luis Camnitzer participó en Sala de Fotografía Emergente</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13149,6 +13951,9 @@
           <t>Wladymir Bernechea artista en Sonata</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13179,6 +13984,9 @@
           <t>Rodrigo Rojas De Negri en A 30 años</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13209,6 +14017,9 @@
           <t>Rodrigo Rojas De Negri en Un exilio sin retorno</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13231,11 +14042,15 @@
           <t>LOC_0058</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin registra colecciones en Nancagua</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13258,11 +14073,15 @@
           <t>LOC_0058</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>Traslado de colección privada en Nancagua</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13285,11 +14104,15 @@
           <t>ORG_0002</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>Colección documentada en contexto de investigación MNBA</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13312,11 +14135,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Jaime participó en entrevista radial</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13339,11 +14166,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Comunicación trata sobre exposición</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13366,11 +14197,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Jaime participó en podcast</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13393,11 +14228,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Podcast trata sobre Monvoisin en América</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13420,11 +14259,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13447,11 +14290,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Ponencia resultado de investigación Monvoisin</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13474,11 +14321,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13501,11 +14352,15 @@
           <t>PRJ_0006</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto Clara Filleul</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13528,11 +14383,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Jaime mencionado como experto</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13555,11 +14414,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Reportaje trata sobre exposición Monvoisin</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13582,11 +14445,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>Jaime condujo ciclo de Instagram</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13609,11 +14476,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>Ciclo divulga proyecto Monvoisin</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13636,11 +14507,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>Jaime participó en lanzamiento</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13663,11 +14538,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>Lanzamiento presenta proyecto Monvoisin</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13690,11 +14569,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>Jaime creó/participó en cápsula</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13717,11 +14600,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>Cápsula trata sobre exposición Monvoisin</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13744,11 +14631,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13771,11 +14662,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13798,11 +14693,15 @@
           <t>PRJ_0006</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13825,11 +14724,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Ponencia se relaciona con Monvoisin</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -13852,11 +14755,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia en UNIFESP</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -13879,11 +14786,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -13906,11 +14817,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -13933,11 +14848,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -13960,11 +14879,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -13987,11 +14910,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Jaime dio charla de mediación</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14014,11 +14941,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Jaime organizó y moderó encuentro</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14041,11 +14972,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Jaime dio charla especializada</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14068,11 +15003,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Jaime dio charla de archivo</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14095,11 +15034,15 @@
           <t>EXP_0008</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Charla trata sobre Salón de Estudiantes 2013</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14122,11 +15065,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Jaime presentó modelo de gestión</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14149,11 +15096,15 @@
           <t>EXP_0008</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Presentación trata sobre Salón de Estudiantes</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14176,11 +15127,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14203,11 +15158,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14230,11 +15189,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Jaime curó conversatorio</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14257,11 +15220,15 @@
           <t>EXP_0003</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Conversatorio trata sobre exposición</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14284,11 +15251,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Jaime hizo visita mediada</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -14311,11 +15282,15 @@
           <t>EXP_0003</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Visita mediada trata sobre exposición</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14338,11 +15313,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>Jaime es sujeto/experto mencionado</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -14365,11 +15344,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>Entrevista trata sobre Monvoisin</t>
         </is>
       </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -14392,11 +15375,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>Jaime es experto mencionado en noticia</t>
         </is>
       </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -14419,11 +15406,15 @@
           <t>PER_0001</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia técnica</t>
         </is>
       </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -14451,6 +15442,10 @@
           <t>Communication produces digital resource (QUINSAC platform launch)</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -14473,11 +15468,15 @@
           <t>PRJ_0009</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>Charla Artistas del Acero es producto de investigación Archivo Fotográfico Rodrigo Rojas</t>
         </is>
       </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -14500,11 +15499,15 @@
           <t>PRJ_0010</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>Matriz Imaginada es producto de investigación Salón de Estudiantes (FVL + FDI)</t>
         </is>
       </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -14527,11 +15530,15 @@
           <t>PRJ_0010</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>Presentación Tabacalera Madrid es producto de investigación Salón de Estudiantes</t>
         </is>
       </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -14554,11 +15561,15 @@
           <t>EXP_0006</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>Charla sobre archivo Rodrigo Rojas trata exposición A 30 años (Museo Memoria DDHH)</t>
         </is>
       </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -14581,11 +15592,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>Marcela Drien participó en proyecto Monvoisin</t>
         </is>
       </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -14616,6 +15631,9 @@
           <t>Proyecto Monvoisin produjo libro colectivo</t>
         </is>
       </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -14646,6 +15664,9 @@
           <t>Proyecto Archivo Rodrigo Rojas produjo libro</t>
         </is>
       </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -14676,6 +15697,9 @@
           <t>Exposición produjo catálogo investigación SNBA</t>
         </is>
       </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -14706,6 +15730,9 @@
           <t>Exposición produjo catálogo arte europeo/latinoamericano</t>
         </is>
       </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -14736,6 +15763,9 @@
           <t>Exposición CCU produjo catálogo curatorial</t>
         </is>
       </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -14766,6 +15796,9 @@
           <t>Proyecto Salón de Estudiantes produjo catálogo</t>
         </is>
       </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -14796,6 +15829,9 @@
           <t>Prólogo del libro Monvoisin en América</t>
         </is>
       </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -14826,6 +15862,9 @@
           <t>Capítulo sobre mercado de arte en libro Monvoisin</t>
         </is>
       </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -14856,6 +15895,9 @@
           <t>Proyecto Coleccionismo Chile siglo XIX produjo capítulo</t>
         </is>
       </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -14886,6 +15928,9 @@
           <t>Capítulo sobre catastro Monvoisin en libro investigación</t>
         </is>
       </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14916,6 +15961,9 @@
           <t>Proyecto Clara Filleul/Procesa produjo capítulo género</t>
         </is>
       </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14946,6 +15994,9 @@
           <t>Proyecto Revista Fotografía FONDART produjo publicación periódica</t>
         </is>
       </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14976,6 +16027,9 @@
           <t>Exposición Desacatos produjo comentario obra en catálogo</t>
         </is>
       </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -15006,6 +16060,9 @@
           <t>Charla sobre curaduría archivo Rodrigo Rojas trata sobre exposición</t>
         </is>
       </c>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -15036,6 +16093,9 @@
           <t>Nota de prensa trata sobre traslado Cristo y Magdalena</t>
         </is>
       </c>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -15066,6 +16126,9 @@
           <t>Magister Historia del Arte UAI produjo libro catastro afromestizos</t>
         </is>
       </c>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -15096,6 +16159,9 @@
           <t>Magister Historia del Arte UAI produjo artículo científico afromestizos</t>
         </is>
       </c>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -15126,6 +16192,9 @@
           <t>Magister Historia del Arte UAI produjo capítulo visualidades</t>
         </is>
       </c>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -15158,6 +16227,9 @@
           <t>Media</t>
         </is>
       </c>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -15180,11 +16252,15 @@
           <t>LOC_0041</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
         </is>
       </c>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -15207,11 +16283,15 @@
           <t>LOC_0005</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>Máster en Humanidades Digitales se cursó en UB FIMA</t>
         </is>
       </c>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -15234,6 +16314,11 @@
           <t>LOC_0062</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -15256,6 +16341,11 @@
           <t>LOC_0064</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -15278,6 +16368,11 @@
           <t>LOC_0048</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -15300,6 +16395,11 @@
           <t>LOC_0063</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr"/>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -15322,11 +16422,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>EXP_0010 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G304" t="inlineStr"/>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -15349,11 +16453,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>EXP_0010_1 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G305" t="inlineStr"/>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -15376,11 +16484,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>EXP_0011_01 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G306" t="inlineStr"/>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -15403,11 +16515,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>EXP_0011_02 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G307" t="inlineStr"/>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -15430,11 +16546,15 @@
           <t>CAR_0013</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>EXP_0011_03 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -15457,11 +16577,15 @@
           <t>LOC_0013</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>Harvard-UAI collaborative project includes research location at Harvard</t>
         </is>
       </c>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15484,11 +16608,15 @@
           <t>DIG_0006</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin genera producto digital QUINSAC</t>
         </is>
       </c>
+      <c r="G310" t="inlineStr"/>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15511,11 +16639,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>Exposición Episodio Monvoisin coordinada como parte del proyecto</t>
         </is>
       </c>
+      <c r="G311" t="inlineStr"/>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15538,11 +16670,15 @@
           <t>PRJ_0008</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>Rol investigador vinculado al proyecto</t>
         </is>
       </c>
+      <c r="G312" t="inlineStr"/>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15565,11 +16701,15 @@
           <t>EXP_0001</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>Gestor coordinó logística de Exposición Episodio Monvoisin</t>
         </is>
       </c>
+      <c r="G313" t="inlineStr"/>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15592,11 +16732,440 @@
           <t>EXP_DESACATOS</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>Pasante en investigación para Exposición Desacatos</t>
         </is>
       </c>
+      <c r="G314" t="inlineStr"/>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>REL_0320</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LOC_0016</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Brasil tomó lugar en Pinacoteca do Estado</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>LOC_0016</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>REL_0321</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>LOC_0017</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Argentina (San Juan) tomó lugar en Museo Franklin Rawson</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>LOC_0017</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>REL_0322</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>LOC_0014</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Argentina (Buenos Aires) tomó lugar en Fundación TyPA/CAIA UBA</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>LOC_0014</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>REL_0323</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>LOC_0018</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Monvoisin en América - Nodo Argentina (Buenos Aires) tomó lugar en IIPC-TAREA, UNSAM</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>LOC_0018</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>REL_0324</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>crm:P14_carried_out_by</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas realizó investigación en Monvoisin en América</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>PRJ_0008</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>REL_0325</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>COM_0011</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>LOC_0065</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>III Encuentro CAIA/UBA tomó lugar en Facultad de Filosofía y Letras</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>REL_0326</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>COM_0006</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>LOC_0041</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>XIV Jornadas Historia de Mujeres tomó lugar en Universidad Nacional de Mar del Plata</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>REL_0327</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>COM_0007</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>crm:P7_took_place_at</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>LOC_0040</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>X Jornadas de história da arte tomó lugar en UNIFESP (São Paulo)</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>REL_0328</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>crm:P14_carried_out_by</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>COM_0011</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas realizó presentación en III Encuentro CAIA/UBA</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>REL_0329</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>crm:P14_carried_out_by</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>COM_0006</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas realizó presentación en XIV Jornadas Historia de Mujeres (Mar del Plata)</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>REL_0330</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>PER_0001</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>crm:P14_carried_out_by</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>COM_0007</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Jaime Cuevas realizó presentación en X Jornadas arte política (UNIFESP, São Paulo)</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17431,56 +19000,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id_lugar</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>toponimo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tipo_lugar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>comuna_distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ciudad</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pais</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>geonames_id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>wikidata_id</t>
         </is>
@@ -17498,6 +19067,31 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>precision_type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>wikidata</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>descripcion</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>why_relevant</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>micro_summary</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>is_core</t>
         </is>
       </c>
     </row>
@@ -17559,6 +19153,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17618,6 +19217,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17677,6 +19281,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17736,6 +19345,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17795,6 +19409,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17854,6 +19473,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17913,6 +19537,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17972,6 +19601,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18031,6 +19665,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18090,6 +19729,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18149,6 +19793,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18208,6 +19857,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18267,6 +19921,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18308,6 +19967,7 @@
       <c r="I15" t="n">
         <v>3435910</v>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>ORG_0016</t>
@@ -18321,6 +19981,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18380,6 +20045,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18439,6 +20109,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18498,6 +20173,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -18557,6 +20237,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18616,6 +20301,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18675,6 +20365,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18734,6 +20429,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18793,6 +20493,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18852,6 +20557,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18911,6 +20621,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18970,6 +20685,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19016,6 +20736,7 @@
           <t>Q1050516</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="b">
         <v>0</v>
       </c>
@@ -19024,6 +20745,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19070,6 +20796,7 @@
           <t>Q201016</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="b">
         <v>0</v>
       </c>
@@ -19078,6 +20805,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -19124,6 +20856,7 @@
           <t>Q7126294</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="b">
         <v>0</v>
       </c>
@@ -19132,6 +20865,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19191,6 +20929,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19237,6 +20980,7 @@
           <t>Q2931448</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="b">
         <v>0</v>
       </c>
@@ -19245,6 +20989,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -19291,6 +21040,7 @@
           <t>Q3691</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="b">
         <v>0</v>
       </c>
@@ -19299,6 +21049,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -19345,6 +21100,7 @@
           <t>Q56125</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="b">
         <v>0</v>
       </c>
@@ -19353,6 +21109,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19399,6 +21160,7 @@
           <t>Q14424</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="b">
         <v>0</v>
       </c>
@@ -19407,6 +21169,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -19453,6 +21220,7 @@
           <t>Q51594</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="b">
         <v>0</v>
       </c>
@@ -19461,6 +21229,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -19507,6 +21280,7 @@
           <t>Q14484</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="b">
         <v>0</v>
       </c>
@@ -19515,6 +21289,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -19574,6 +21353,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -19620,6 +21404,7 @@
           <t>Q13063</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="b">
         <v>0</v>
       </c>
@@ -19628,6 +21413,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -19674,6 +21464,7 @@
           <t>Q51048</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="b">
         <v>0</v>
       </c>
@@ -19682,6 +21473,11 @@
           <t>centroid</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -19741,6 +21537,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -19800,6 +21601,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19859,6 +21665,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19918,6 +21729,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19977,6 +21793,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20036,6 +21857,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20077,6 +21903,7 @@
       <c r="I46" t="n">
         <v>3530597</v>
       </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>ORG_0036</t>
@@ -20090,6 +21917,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -20131,6 +21963,8 @@
       <c r="I47" t="n">
         <v>3871336</v>
       </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="b">
         <v>0</v>
       </c>
@@ -20139,6 +21973,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -20198,6 +22037,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20257,6 +22101,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -20316,6 +22165,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -20362,6 +22216,7 @@
           <t>Q7203673</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="b">
         <v>0</v>
       </c>
@@ -20370,6 +22225,11 @@
           <t>approximate</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -20411,6 +22271,8 @@
       <c r="I52" t="n">
         <v>3893894</v>
       </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="b">
         <v>0</v>
       </c>
@@ -20419,6 +22281,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -20465,6 +22332,7 @@
           <t>Q6033182</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="b">
         <v>0</v>
       </c>
@@ -20473,6 +22341,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20519,6 +22392,7 @@
           <t>Q61</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="b">
         <v>0</v>
       </c>
@@ -20527,6 +22401,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20573,6 +22452,7 @@
           <t>Q38</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="b">
         <v>0</v>
       </c>
@@ -20581,6 +22461,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -20627,6 +22512,7 @@
           <t>Q954318</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="b">
         <v>0</v>
       </c>
@@ -20635,6 +22521,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -20676,6 +22567,7 @@
       <c r="I57" t="n">
         <v>3871336</v>
       </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>ORG_0040</t>
@@ -20689,6 +22581,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -20735,6 +22632,7 @@
           <t>Q113665601</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="b">
         <v>0</v>
       </c>
@@ -20743,6 +22641,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -20760,6 +22663,7 @@
           <t>Colección / Patrimonio</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Nancagua</t>
@@ -20770,9 +22674,20 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="L59" t="n">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="b">
         <v>0</v>
       </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -20811,11 +22726,13 @@
       <c r="H60" t="n">
         <v>-3.7038</v>
       </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Q9256</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="b">
         <v>0</v>
       </c>
@@ -20824,6 +22741,11 @@
           <t>exact</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -20851,17 +22773,27 @@
           <t>Chile</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>-33.42121365946592</v>
       </c>
       <c r="H61" t="n">
         <v>-70.59154788940485</v>
       </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20889,17 +22821,27 @@
           <t>Chile</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>-33.48439393710956</v>
       </c>
       <c r="H62" t="n">
         <v>-70.5182663382937</v>
       </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20927,17 +22869,27 @@
           <t>Chile</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>-33.46665877200571</v>
       </c>
       <c r="H63" t="n">
         <v>-70.59598366056628</v>
       </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20976,11 +22928,20 @@
       <c r="H64" t="n">
         <v>-70.59510712009342</v>
       </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21008,16 +22969,94 @@
           <t>Chile</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>-33.43714059270721</v>
       </c>
       <c r="H65" t="n">
         <v>-70.62813240660158</v>
       </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>LOC_0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Facultad de Filosofía y Letras, Universidad de Buenos Aires</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sede Académica</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Caballito</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>-34.6372</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-58.4531</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>ORG_0035</t>
+        </is>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Q457188</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Facultad de Filosofía y Letras de la Universidad de Buenos Aires, ubicada en Puán 480</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6625,7 +6625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I325"/>
+  <dimension ref="A1:I324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6706,9 +6706,6 @@
           <t>Jaime Cuevas co-dirige y coordina el proyecto internacional Monvoisin en América</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6741,9 +6738,6 @@
           <t>Monvoisin en América produce el catálogo razonado y plataforma QUINSAC</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6776,9 +6770,6 @@
           <t>Monvoisin en América produce la cartografía interactiva StoryMaps</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6811,9 +6802,6 @@
           <t>Monvoisin en América produce el libro Monvoisin en América: Identidades, atribuciones y mercado</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6846,9 +6834,6 @@
           <t>Monvoisin en América produce el capítulo introductorio</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6881,9 +6866,6 @@
           <t>Monvoisin en América produce el capítulo sobre autenticidad y mercado</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6916,9 +6898,6 @@
           <t>Monvoisin en América produce el capítulo sobre catastro y Elisa Bravo</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6951,9 +6930,6 @@
           <t>Monvoisin en América sustenta curatorial y documentalmente la exposición Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6986,9 +6962,6 @@
           <t>Episodio Monvoisin incluye traslado de obra monumental Cristo y Magdalena desde Concepción</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7021,9 +6994,6 @@
           <t>Episodio Monvoisin incluye traslado de obra José Tomás de Urmeneta desde Victoria</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7056,9 +7026,6 @@
           <t>Episodio Monvoisin incluye traslado de Palacio Cousiño</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7091,9 +7058,6 @@
           <t>Episodio Monvoisin incluye traslado de Abdicación de O'Higgins desde Maipú</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7126,9 +7090,6 @@
           <t>Monvoisin en América integra el Nodo Argentina - San Juan (Museo Franklin Rawson)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7161,9 +7122,6 @@
           <t>Monvoisin en América integra el Nodo Argentina - Buenos Aires (IIPC-TAREA UNSAM)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7196,9 +7154,6 @@
           <t>Monvoisin en América integra el Nodo Perú (MALI)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7231,9 +7186,6 @@
           <t>Monvoisin en América integra el Nodo Brasil (Pinacoteca de São Paulo)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7266,9 +7218,6 @@
           <t>Monvoisin en América es difundido en entrevista radial El Semáforo</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7301,9 +7250,6 @@
           <t>Monvoisin en América es analizado en podcast La Hora del Museo</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7336,9 +7282,6 @@
           <t>Monvoisin en América genera el ciclo de 5 conversatorios Live en Instagram MNBA</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7371,9 +7314,6 @@
           <t>Jaime Cuevas es Investigador Responsable del proyecto FONDART Arquitectura Art Déco</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7406,9 +7346,6 @@
           <t>Proyecto Art Déco produce el ecosistema digital semántico artdeco-santiago.cl</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7441,9 +7378,6 @@
           <t>Jaime Cuevas es Asistente de Investigación y Arquitecto de Datos en FONDECYT Mármoles y Bronces</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7476,9 +7410,6 @@
           <t>FONDECYT Mármoles y Bronces produce la plataforma analítica marmoles-y-bronces.vercel.app</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7511,9 +7442,6 @@
           <t>Jaime Cuevas es Director de Datos e Investigador en Callejera Madrid</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7546,9 +7474,6 @@
           <t>Jaime Cuevas es Investigador Responsable del FAIP Colección Marcos Segundo Maturana</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7581,9 +7506,6 @@
           <t>Proyecto Maturana produce el informe de investigación oficial FAIP 2021</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7616,9 +7538,6 @@
           <t>Jaime Cuevas es Coinvestigador en el FAIP Ausencias y omisiones femeninas</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7651,9 +7570,6 @@
           <t>Proyecto produce el informe de investigación oficial FAIP 2018</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7686,9 +7602,6 @@
           <t>Jaime Cuevas es Investigador Responsable del FONDART Creación Archivo Fotográfico Rodrigo Rojas De Negri (Folio 84311)</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7721,9 +7634,6 @@
           <t>FONDART 84311 produce el libro Rodrigo Rojas De Negri. Un exilio sin retorno (LOM Ediciones)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7756,9 +7666,6 @@
           <t>FONDART 84311 produce la exposición A 30 años de Rodrigo Rojas De Negri en MMDH</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7791,9 +7698,6 @@
           <t>Jaime Cuevas es Responsable del proyecto Fondo Valentín Letelier Salón de Estudiantes 2013</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7826,9 +7730,6 @@
           <t>FVL-2011 produce la muestra Salón de Estudiantes 2013 en MAC Quinta Normal</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7861,9 +7762,6 @@
           <t>FVL-2011 produce la plataforma web salonestudiantes.cl</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7896,9 +7794,6 @@
           <t>FVL-2011 produce el catálogo y texto Matriz Imaginada</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7931,9 +7826,6 @@
           <t>Jaime Cuevas es autor del ensayo El canon revisitado galardonado por Fundación TyPA</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7966,9 +7858,6 @@
           <t>Ensayo corresponde a la Convocatoria Iberoamericana TyPA / Wikimedia Argentina</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8001,9 +7890,6 @@
           <t>Jaime Cuevas es Co-Curador de la exposición Adquisiciones en contexto en Sala Chile MNBA</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8036,9 +7922,6 @@
           <t>Exposición produce el catálogo oficial Adquisiciones en contexto</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8071,9 +7954,6 @@
           <t>Exposición produce el librillo de mediación patrimonial</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8106,9 +7986,6 @@
           <t>Jaime Cuevas es Co-Curador y Coordinador Editorial de El canon revisitado</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8141,9 +8018,6 @@
           <t>Exposición produce el catálogo binacional El canon revisitado (MNBA / San Carlos)</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8176,9 +8050,6 @@
           <t>Jaime Cuevas es Curador Asistente en Crisis, crisis, crisis en Matucana 100</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8211,9 +8082,6 @@
           <t>Jaime Cuevas es Curador de la exposición individual Sonata en Isabel Croxatto Galería</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8246,9 +8114,6 @@
           <t>La exposición Sonata tiene lugar en Isabel Croxatto Galería</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8281,9 +8146,6 @@
           <t>Itinerancia Antúnez Estación Ñuble tiene lugar en CECAL UdeC Chillán</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8316,9 +8178,6 @@
           <t>Laboratorio Arte y Crisis incluye obras de la Colección MUSAC León España</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8351,9 +8210,6 @@
           <t>Jaime Cuevas co-ejecutó el proyecto FONDART Nacional 89451</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8386,9 +8242,6 @@
           <t>Montserrat Rojas Corradi fue la Editora Principal del FONDART 89451</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8421,9 +8274,6 @@
           <t>El FONDART 89451 produjo la publicación seriada S/T Revista de Fotografía</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8456,9 +8306,6 @@
           <t>S/T Revista fue co-editada y distribuida por LOM Ediciones</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8491,9 +8338,6 @@
           <t>FONDART Nacional 89451 fue financiado por CNCA / MINCAP</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8516,15 +8360,11 @@
           <t>ORG_0001</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Asistente Curatorial y de Exposiciones Temporales</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8547,15 +8387,11 @@
           <t>ORG_0002</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Gestor de Proyectos Patrimoniales | Punto Focal ENPD | Investigador de Colecciones</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8578,15 +8414,11 @@
           <t>ORG_0004</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Profesor Universitario de Cátedra</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8609,15 +8441,11 @@
           <t>ORG_0006</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Investigador Independiente de Patrimonio</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8640,15 +8468,11 @@
           <t>ORG_0008</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Evaluador de Proyectos Culturales (FONDART)</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8671,15 +8495,11 @@
           <t>ORG_0011</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Asistente de Investigación y Catalogación</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8702,15 +8522,11 @@
           <t>ORG_0012</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Asistente de Investigación en Archivística y Documentación</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8733,15 +8549,11 @@
           <t>ORG_0022</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Co-Editor y Gestor Editorial</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8764,15 +8576,11 @@
           <t>ORG_0034</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Evaluador Externo (Arbitraje por pares ciego)</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8795,15 +8603,11 @@
           <t>ORG_0037</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Profesor de Estética y Diseño Múltiple</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8826,15 +8630,11 @@
           <t>ORG_0038</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Formación: Prevención de Riesgos</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8857,15 +8657,11 @@
           <t>ORG_0003</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>Licenciatura en Artes c/m en Teoría e Historia del Arte</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8888,15 +8684,11 @@
           <t>ORG_0005</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Máster Universitario en Humanidades Digitales</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8919,15 +8711,11 @@
           <t>ORG_0007</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Patrimonio Cultural | Enfoque de Género | IDE Patrimonio</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8950,15 +8738,11 @@
           <t>ORG_0009</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Diplomado en Gobierno y Gestión Pública</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8981,15 +8765,11 @@
           <t>ORG_0010</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Diplomado en Museos y Museología (IDEA)</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9012,15 +8792,11 @@
           <t>ORG_0013</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Gestión de Exposiciones Temporales: un modelo de gestión</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9043,15 +8819,11 @@
           <t>ORG_0014</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Equivalencia a nivel académico de Grado en España</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9074,15 +8846,11 @@
           <t>ORG_0033</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>Curso Estatuto Administrativo</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9105,15 +8873,11 @@
           <t>ORG_0035</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Digitalización de soportes fotográficos y documentos patrimoniales</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9136,15 +8900,11 @@
           <t>ORG_0036</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Cursos Online: Museología y Herencia Africana en el Arte</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9167,15 +8927,11 @@
           <t>PER_0008</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Co-curador: Camila Caris Seguel</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9198,15 +8954,11 @@
           <t>PER_0004</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Co-curador: Manuel Alvarado Cornejo</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9229,15 +8981,11 @@
           <t>PER_0011</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Co-curadora: Montserrat Rojas Corradi</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9260,15 +9008,11 @@
           <t>PER_0011</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>Colaboración en exposiciones</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9296,10 +9040,6 @@
           <t>Rodrigo Rojas De Negri es sujeto del FONDART Archivo Fotográfico</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9327,10 +9067,6 @@
           <t>Rodrigo Rojas De Negri es sujeto del libro de investigación</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9358,10 +9094,6 @@
           <t>Exposición "A 30 años de Rodrigo Rojas de Negri" (2016)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9389,10 +9121,6 @@
           <t>Exposición "Un exilio sin retorno. Rodrigo Rojas De Negri"</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9420,10 +9148,6 @@
           <t>Rodrigo Rojas De Negri residió en exilio en Washington D.C.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9451,10 +9175,6 @@
           <t>Tema de charla de mediación curatorial</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9482,10 +9202,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9513,10 +9229,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M01</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9544,10 +9256,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M02</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9575,10 +9283,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M03</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9606,10 +9310,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M04</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9637,10 +9337,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M05</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9668,10 +9364,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M06</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9699,10 +9391,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M07</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9730,10 +9418,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M08</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9761,10 +9445,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M09</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9792,10 +9472,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M10</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9823,10 +9499,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M11</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9854,10 +9526,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M12</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9885,10 +9553,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0001_M13</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9916,10 +9580,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0002</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9947,10 +9607,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0005</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9978,10 +9634,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0006</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10009,10 +9661,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0007</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10040,10 +9688,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0008</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10071,10 +9715,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0009</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10102,10 +9742,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10133,10 +9769,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0010_1</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10164,10 +9796,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_01</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10195,10 +9823,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_02</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10226,10 +9850,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated/curated EXP_0011_03</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10257,10 +9877,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0001</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10288,10 +9904,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0002</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10319,10 +9931,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0003</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10350,10 +9958,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0004</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10381,10 +9985,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0005</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10412,10 +10012,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0006</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10443,10 +10039,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0007</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10474,10 +10066,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0008</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10505,10 +10093,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0009</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -10536,10 +10120,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0010</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -10567,10 +10147,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0011</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -10598,10 +10174,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0012</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -10629,10 +10201,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0013</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -10660,10 +10228,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0014</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10691,10 +10255,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0015</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10722,10 +10282,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0016</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10753,10 +10309,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0017</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10784,10 +10336,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0018</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10815,10 +10363,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0019</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10846,10 +10390,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0020</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10877,10 +10417,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0021</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10908,10 +10444,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0022</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10939,10 +10471,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0023</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10970,10 +10498,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0024</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -11001,10 +10525,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0025</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11032,10 +10552,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0026</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11063,10 +10579,6 @@
           <t>Jaime Arnaldo Cuevas Pérez participated in media event COM_0027</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11094,10 +10606,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0003</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11125,10 +10633,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0004</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11156,10 +10660,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0007</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -11187,10 +10687,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N01</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11218,10 +10714,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N02</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11249,10 +10741,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N03</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -11280,10 +10768,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0008_N04</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -11311,10 +10795,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0011</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11342,10 +10822,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0012</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -11373,10 +10849,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0013</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -11404,10 +10876,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0014</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -11435,10 +10903,6 @@
           <t>Jaime Arnaldo Cuevas Pérez worked on/investigated PRJ_0015</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -11466,10 +10930,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0001</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11497,10 +10957,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0002</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -11528,10 +10984,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0003</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -11559,10 +11011,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0004</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -11590,10 +11038,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0006</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11621,10 +11065,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0007</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11652,10 +11092,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0008</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11683,10 +11119,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0009</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11714,10 +11146,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0010</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11745,10 +11173,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0011</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11776,10 +11200,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0012</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11807,10 +11227,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0013</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11838,10 +11254,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0014</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11869,10 +11281,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0015</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11900,10 +11308,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0016</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11931,10 +11335,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0017</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11962,10 +11362,6 @@
           <t>Jaime Arnaldo Cuevas Pérez authored/co-authored PUB_0018</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11993,10 +11389,6 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0003</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -12024,10 +11416,6 @@
           <t>Manuel Alvarado Cornejo participated/curated EXP_0004</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12055,10 +11443,6 @@
           <t>Camila Caris Seguel participated/curated EXP_0002</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12086,10 +11470,6 @@
           <t>Camila Caris Seguel participated/curated EXP_0008</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12117,10 +11497,6 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0007</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12148,10 +11524,6 @@
           <t>Montserrat Rojas Corradi participated/curated EXP_0009</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12182,9 +11554,6 @@
           <t>Gloria Cortés co-editó y co-autorizó el libro Monvoisin en América</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12217,9 +11586,6 @@
           <t>Gloria Cortés co-dirige el proyecto Monvoisin en América</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12252,9 +11618,6 @@
           <t>Antonia Viu participó en proyecto Cultures of reading</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12287,9 +11650,6 @@
           <t>Katherine Vyhmeister trabajó en proyecto Arquitectura Art Déco</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12322,9 +11682,6 @@
           <t>Jaime Cuevas fue asistente de investigación de Fernando Guzmán en la UAI</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12357,9 +11714,6 @@
           <t>Jaime Cuevas fue asistente de investigación de Marcela Drien en la UAI</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12392,9 +11746,6 @@
           <t>Jaime Cuevas fue asistente de investigación de Katherine Vyhmeister en la UAI</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12425,9 +11776,6 @@
           <t>Jaime Cuevas participó en congreso internacional de CAIA en Buenos Aires</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12458,9 +11806,6 @@
           <t>Jaime Cuevas ganó Premio Iberoamericano de Wikimedia Argentina/TyPA</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12491,9 +11836,6 @@
           <t>Jaime Cuevas participó/curó exposición de Corporación CCU</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12526,9 +11868,6 @@
           <t>Antonia Viu realizó pasantía académica en Harvard University</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12559,9 +11898,6 @@
           <t>Laura Rodig fue artista principal en exposición Desacatos</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12594,9 +11930,6 @@
           <t>Estefanía Granja desarrolló plataforma digital de Callejera Madrid</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -12629,9 +11962,6 @@
           <t>Jaime Cuevas participó en curación de Callejera Madrid</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12662,9 +11992,6 @@
           <t>Raymond Monvoisin es sujeto principal de Monvoisin en América</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12695,9 +12022,6 @@
           <t>Monvoisin es tema central en introducción</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12728,9 +12052,6 @@
           <t>Catastro y documentación de obra de Monvoisin</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12761,9 +12082,6 @@
           <t>Clara Filleul mencionada en estudio de comercialización</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12794,9 +12112,6 @@
           <t>Clara Filleul es sujeto de investigación sobre discipulaje</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12827,9 +12142,6 @@
           <t>Procesa Sarmiento es sujeto de investigación sobre discipulaje</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12860,9 +12172,6 @@
           <t>Alessandro Ciccarelli es sujeto único del artículo sobre Fuerte Bulnes</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12893,9 +12202,6 @@
           <t>Iván Navarro participó en exposición La segunda naturaleza</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12926,9 +12232,6 @@
           <t>Alfredo Jaar participó en exposición La segunda naturaleza</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12959,9 +12262,6 @@
           <t>Voluspa Jarpa participó en exposición La segunda naturaleza</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12992,9 +12292,6 @@
           <t>Iván Navarro es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13025,9 +12322,6 @@
           <t>Alfredo Jaar es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13058,9 +12352,6 @@
           <t>Voluspa Jarpa es artista estudiado en La segunda naturaleza</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13091,9 +12382,6 @@
           <t>Raymond Monvoisin es artista principal en Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13124,9 +12412,6 @@
           <t>Clara Filleul participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13157,9 +12442,6 @@
           <t>Procesa Sarmiento participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13190,9 +12472,6 @@
           <t>Gregorio Torres participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13223,9 +12502,6 @@
           <t>Francisco Javier Mandiola participó en exposición Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -13258,9 +12534,6 @@
           <t>Raymond Monvoisin es sujeto del proyecto Monvoisin en América</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -13291,9 +12564,6 @@
           <t>Clara Filleul es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -13324,9 +12594,6 @@
           <t>Procesa Sarmiento es sujeto del proyecto sobre ausencias femeninas</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -13357,9 +12624,6 @@
           <t>Milencka Vidal co-autora de Catastro y visualidad de afromestizos</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13390,9 +12654,6 @@
           <t>Daniela Colleoni co-autora de Matriz imaginada</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -13423,9 +12684,6 @@
           <t>Jesús Arana participó en Prácticas de reiteración</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13456,9 +12714,6 @@
           <t>Gonzalo Cueto participó en Crisis, crisis, crisis</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13489,9 +12744,6 @@
           <t>Oskar Trepte participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
-      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13522,9 +12774,6 @@
           <t>Pedro Reszka Moreau participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13555,9 +12804,6 @@
           <t>Virginio Arias Cruz participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
-      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13588,9 +12834,6 @@
           <t>Benito Rebolledo Correa participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13621,9 +12864,6 @@
           <t>Aristodemo Lattanzi Borghini participó en exposición Adquisiciones en contexto</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13654,9 +12894,6 @@
           <t>Violeta Parra artista en Violeta y sus contemporáneas</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13687,9 +12924,6 @@
           <t>Inés Puyó participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13720,9 +12954,6 @@
           <t>Ximena Cristi participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13753,9 +12984,6 @@
           <t>Laura Rodig participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13786,9 +13014,6 @@
           <t>Henriette Petit participó en Violeta y sus contemporáneas</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
-      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13819,9 +13044,6 @@
           <t>Nemesio Antúnez en centenario - Estación Ñuble</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
-      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13852,9 +13074,6 @@
           <t>Nemesio Antúnez en centenario - Estación Biobío</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
-      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13885,9 +13104,6 @@
           <t>Nemesio Antúnez en centenario - Estación Maule</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
-      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13918,9 +13134,6 @@
           <t>Luis Camnitzer participó en Sala de Fotografía Emergente</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
-      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13951,9 +13164,6 @@
           <t>Wladymir Bernechea artista en Sonata</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13984,9 +13194,6 @@
           <t>Rodrigo Rojas De Negri en A 30 años</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -14017,9 +13224,6 @@
           <t>Rodrigo Rojas De Negri en Un exilio sin retorno</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -14042,15 +13246,11 @@
           <t>LOC_0058</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin registra colecciones en Nancagua</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
-      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -14073,15 +13273,11 @@
           <t>LOC_0058</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>Traslado de colección privada en Nancagua</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14104,15 +13300,11 @@
           <t>ORG_0002</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>Colección documentada en contexto de investigación MNBA</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
-      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14135,15 +13327,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Jaime participó en entrevista radial</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
-      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14166,15 +13354,11 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Comunicación trata sobre exposición</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14197,15 +13381,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Jaime participó en podcast</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14228,15 +13408,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Podcast trata sobre Monvoisin en América</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14259,15 +13435,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14290,15 +13462,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Ponencia resultado de investigación Monvoisin</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14321,15 +13489,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14352,15 +13516,11 @@
           <t>PRJ_0006</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto Clara Filleul</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14383,15 +13543,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Jaime mencionado como experto</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14414,15 +13570,11 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Reportaje trata sobre exposición Monvoisin</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14445,15 +13597,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>Jaime condujo ciclo de Instagram</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14476,15 +13624,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>Ciclo divulga proyecto Monvoisin</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14507,15 +13651,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>Jaime participó en lanzamiento</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
-      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14538,15 +13678,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>Lanzamiento presenta proyecto Monvoisin</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
-      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14569,15 +13705,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>Jaime creó/participó en cápsula</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14600,15 +13732,11 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>Cápsula trata sobre exposición Monvoisin</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14631,15 +13759,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14662,15 +13786,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14693,15 +13813,11 @@
           <t>PRJ_0006</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>Ponencia resultado de proyecto FAIP Clara y Procesa</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14724,15 +13840,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Ponencia se relaciona con Monvoisin</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14755,15 +13867,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia en UNIFESP</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14786,15 +13894,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
-      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14817,15 +13921,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14848,15 +13948,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14879,15 +13975,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14910,15 +14002,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Jaime dio charla de mediación</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
-      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14941,15 +14029,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Jaime organizó y moderó encuentro</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14972,15 +14056,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Jaime dio charla especializada</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15003,15 +14083,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Jaime dio charla de archivo</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15034,15 +14110,11 @@
           <t>EXP_0008</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Charla trata sobre Salón de Estudiantes 2013</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15065,15 +14137,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Jaime presentó modelo de gestión</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15096,15 +14164,11 @@
           <t>EXP_0008</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Presentación trata sobre Salón de Estudiantes</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
-      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15127,15 +14191,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15158,15 +14218,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Jaime fue invitado a conversatorio</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15189,15 +14245,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Jaime curó conversatorio</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15220,15 +14272,11 @@
           <t>EXP_0003</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Conversatorio trata sobre exposición</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15251,15 +14299,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Jaime hizo visita mediada</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15282,15 +14326,11 @@
           <t>EXP_0003</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Visita mediada trata sobre exposición</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15313,15 +14353,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>Jaime es sujeto/experto mencionado</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
-      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15344,15 +14380,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>Entrevista trata sobre Monvoisin</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
-      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15375,15 +14407,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>Jaime es experto mencionado en noticia</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15406,15 +14434,11 @@
           <t>PER_0001</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>Jaime presentó ponencia técnica</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15442,10 +14466,6 @@
           <t>Communication produces digital resource (QUINSAC platform launch)</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
-      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15468,15 +14488,11 @@
           <t>PRJ_0009</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>Charla Artistas del Acero es producto de investigación Archivo Fotográfico Rodrigo Rojas</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
-      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15499,15 +14515,11 @@
           <t>PRJ_0010</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>Matriz Imaginada es producto de investigación Salón de Estudiantes (FVL + FDI)</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15530,15 +14542,11 @@
           <t>PRJ_0010</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>Presentación Tabacalera Madrid es producto de investigación Salón de Estudiantes</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
-      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15561,15 +14569,11 @@
           <t>EXP_0006</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>Charla sobre archivo Rodrigo Rojas trata exposición A 30 años (Museo Memoria DDHH)</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
-      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15592,15 +14596,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>Marcela Drien participó en proyecto Monvoisin</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15631,9 +14631,6 @@
           <t>Proyecto Monvoisin produjo libro colectivo</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
-      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15664,9 +14661,6 @@
           <t>Proyecto Archivo Rodrigo Rojas produjo libro</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
-      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15697,9 +14691,6 @@
           <t>Exposición produjo catálogo investigación SNBA</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
-      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15730,9 +14721,6 @@
           <t>Exposición produjo catálogo arte europeo/latinoamericano</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
-      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15763,9 +14751,6 @@
           <t>Exposición CCU produjo catálogo curatorial</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
-      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15796,9 +14781,6 @@
           <t>Proyecto Salón de Estudiantes produjo catálogo</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15829,9 +14811,6 @@
           <t>Prólogo del libro Monvoisin en América</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
-      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15862,9 +14841,6 @@
           <t>Capítulo sobre mercado de arte en libro Monvoisin</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
-      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15895,9 +14871,6 @@
           <t>Proyecto Coleccionismo Chile siglo XIX produjo capítulo</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
-      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -15928,9 +14901,6 @@
           <t>Capítulo sobre catastro Monvoisin en libro investigación</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
-      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -15961,9 +14931,6 @@
           <t>Proyecto Clara Filleul/Procesa produjo capítulo género</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -15994,9 +14961,6 @@
           <t>Proyecto Revista Fotografía FONDART produjo publicación periódica</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16027,9 +14991,6 @@
           <t>Exposición Desacatos produjo comentario obra en catálogo</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16060,9 +15021,6 @@
           <t>Charla sobre curaduría archivo Rodrigo Rojas trata sobre exposición</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
-      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16093,9 +15051,6 @@
           <t>Nota de prensa trata sobre traslado Cristo y Magdalena</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
-      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16126,9 +15081,6 @@
           <t>Magister Historia del Arte UAI produjo libro catastro afromestizos</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
-      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16159,9 +15111,6 @@
           <t>Magister Historia del Arte UAI produjo artículo científico afromestizos</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
-      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16192,9 +15141,6 @@
           <t>Magister Historia del Arte UAI produjo capítulo visualidades</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
-      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16227,9 +15173,6 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
-      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16252,15 +15195,11 @@
           <t>LOC_0041</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>Ponencia en XIV Jornadas de Historia de las Mujeres</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
-      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16283,15 +15222,11 @@
           <t>LOC_0005</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>Máster en Humanidades Digitales se cursó en UB FIMA</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16314,11 +15249,6 @@
           <t>LOC_0062</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16341,11 +15271,6 @@
           <t>LOC_0064</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
-      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16368,11 +15293,6 @@
           <t>LOC_0048</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16395,11 +15315,6 @@
           <t>LOC_0063</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -16422,15 +15337,11 @@
           <t>CAR_0013</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>EXP_0010 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
-      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16453,15 +15364,11 @@
           <t>CAR_0013</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>EXP_0010_1 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -16484,15 +15391,11 @@
           <t>CAR_0013</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>EXP_0011_01 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
-      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -16515,15 +15418,11 @@
           <t>CAR_0013</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>EXP_0011_02 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -16546,15 +15445,11 @@
           <t>CAR_0013</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>EXP_0011_03 was coordinated via CAR_0013 (Itinerancias role)</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
-      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -16577,15 +15472,11 @@
           <t>LOC_0013</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>Harvard-UAI collaborative project includes research location at Harvard</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
-      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -16608,15 +15499,11 @@
           <t>DIG_0006</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>Proyecto Monvoisin genera producto digital QUINSAC</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr"/>
-      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -16639,15 +15526,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>Exposición Episodio Monvoisin coordinada como parte del proyecto</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
-      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -16670,15 +15553,11 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>Rol investigador vinculado al proyecto</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -16701,15 +15580,11 @@
           <t>EXP_0001</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>Gestor coordinó logística de Exposición Episodio Monvoisin</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -16732,15 +15607,11 @@
           <t>EXP_DESACATOS</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>Pasante en investigación para Exposición Desacatos</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
-      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -16763,7 +15634,6 @@
           <t>LOC_0016</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>Monvoisin en América - Nodo Brasil tomó lugar en Pinacoteca do Estado</t>
@@ -16806,7 +15676,6 @@
           <t>LOC_0017</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>Monvoisin en América - Nodo Argentina (San Juan) tomó lugar en Museo Franklin Rawson</t>
@@ -16849,7 +15718,6 @@
           <t>LOC_0014</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>Monvoisin en América - Nodo Argentina (Buenos Aires) tomó lugar en Fundación TyPA/CAIA UBA</t>
@@ -16892,7 +15760,6 @@
           <t>LOC_0018</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>Monvoisin en América - Nodo Argentina (Buenos Aires) tomó lugar en IIPC-TAREA, UNSAM</t>
@@ -16935,7 +15802,6 @@
           <t>PRJ_0008</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>Jaime Cuevas realizó investigación en Monvoisin en América</t>
@@ -16988,9 +15854,6 @@
           <t>III Encuentro CAIA/UBA tomó lugar en Facultad de Filosofía y Letras</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
-      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17000,7 +15863,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>COM_0006</t>
+          <t>COM_0007</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -17010,22 +15873,19 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LOC_0041</t>
+          <t>LOC_0040</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>XIV Jornadas Historia de Mujeres tomó lugar en Universidad Nacional de Mar del Plata</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
-      <c r="I321" t="inlineStr"/>
+          <t>X Jornadas de história da arte tomó lugar en UNIFESP (São Paulo)</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -17035,32 +15895,29 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>COM_0007</t>
+          <t>PER_0001</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>crm:P7_took_place_at</t>
+          <t>crm:P14_carried_out_by</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LOC_0040</t>
+          <t>COM_0011</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>X Jornadas de história da arte tomó lugar en UNIFESP (São Paulo)</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
-      <c r="I322" t="inlineStr"/>
+          <t>Jaime Cuevas realizó presentación en III Encuentro CAIA/UBA</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17080,22 +15937,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>COM_0011</t>
+          <t>COM_0006</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Jaime Cuevas realizó presentación en III Encuentro CAIA/UBA</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
-      <c r="I323" t="inlineStr"/>
+          <t>Jaime Cuevas realizó presentación en XIV Jornadas Historia de Mujeres (Mar del Plata)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -17115,57 +15969,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>COM_0006</t>
+          <t>COM_0007</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Jaime Cuevas realizó presentación en XIV Jornadas Historia de Mujeres (Mar del Plata)</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
-      <c r="I324" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>REL_0330</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>PER_0001</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>crm:P14_carried_out_by</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>COM_0007</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
           <t>Jaime Cuevas realizó presentación en X Jornadas arte política (UNIFESP, São Paulo)</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
-      <c r="I325" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19153,11 +17969,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19217,11 +18028,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19281,11 +18087,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19345,11 +18146,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19409,11 +18205,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19473,11 +18264,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19537,11 +18323,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19601,11 +18382,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19665,11 +18441,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19729,11 +18500,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19793,11 +18559,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19857,11 +18618,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19921,11 +18677,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19967,7 +18718,6 @@
       <c r="I15" t="n">
         <v>3435910</v>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>ORG_0016</t>
@@ -19981,11 +18731,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20045,11 +18790,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20109,11 +18849,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20173,11 +18908,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20237,11 +18967,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20301,11 +19026,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -20365,11 +19085,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -20429,11 +19144,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -20493,11 +19203,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -20557,11 +19262,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20621,11 +19321,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20685,11 +19380,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -20736,7 +19426,6 @@
           <t>Q1050516</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="b">
         <v>0</v>
       </c>
@@ -20745,11 +19434,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -20796,7 +19480,6 @@
           <t>Q201016</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="b">
         <v>0</v>
       </c>
@@ -20805,11 +19488,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -20856,7 +19534,6 @@
           <t>Q7126294</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="b">
         <v>0</v>
       </c>
@@ -20865,11 +19542,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -20929,11 +19601,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -20980,7 +19647,6 @@
           <t>Q2931448</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="b">
         <v>0</v>
       </c>
@@ -20989,11 +19655,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -21040,7 +19701,6 @@
           <t>Q3691</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="b">
         <v>0</v>
       </c>
@@ -21049,11 +19709,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -21100,7 +19755,6 @@
           <t>Q56125</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="b">
         <v>0</v>
       </c>
@@ -21109,11 +19763,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -21160,7 +19809,6 @@
           <t>Q14424</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="b">
         <v>0</v>
       </c>
@@ -21169,11 +19817,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -21220,7 +19863,6 @@
           <t>Q51594</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="b">
         <v>0</v>
       </c>
@@ -21229,11 +19871,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -21280,7 +19917,6 @@
           <t>Q14484</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="b">
         <v>0</v>
       </c>
@@ -21289,11 +19925,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -21353,11 +19984,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -21404,7 +20030,6 @@
           <t>Q13063</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="b">
         <v>0</v>
       </c>
@@ -21413,11 +20038,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21464,7 +20084,6 @@
           <t>Q51048</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="b">
         <v>0</v>
       </c>
@@ -21473,11 +20092,6 @@
           <t>centroid</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -21537,11 +20151,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -21601,11 +20210,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -21665,11 +20269,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -21729,11 +20328,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -21793,11 +20387,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -21857,11 +20446,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -21903,7 +20487,6 @@
       <c r="I46" t="n">
         <v>3530597</v>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>ORG_0036</t>
@@ -21917,11 +20500,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -21963,8 +20541,6 @@
       <c r="I47" t="n">
         <v>3871336</v>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="b">
         <v>0</v>
       </c>
@@ -21973,11 +20549,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -22037,11 +20608,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22101,11 +20667,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22165,11 +20726,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -22216,7 +20772,6 @@
           <t>Q7203673</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="b">
         <v>0</v>
       </c>
@@ -22225,11 +20780,6 @@
           <t>approximate</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -22271,8 +20821,6 @@
       <c r="I52" t="n">
         <v>3893894</v>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="b">
         <v>0</v>
       </c>
@@ -22281,11 +20829,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -22332,7 +20875,6 @@
           <t>Q6033182</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="b">
         <v>0</v>
       </c>
@@ -22341,11 +20883,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -22392,7 +20929,6 @@
           <t>Q61</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="b">
         <v>0</v>
       </c>
@@ -22401,11 +20937,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -22452,7 +20983,6 @@
           <t>Q38</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="b">
         <v>0</v>
       </c>
@@ -22461,11 +20991,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -22512,7 +21037,6 @@
           <t>Q954318</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="b">
         <v>0</v>
       </c>
@@ -22521,11 +21045,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -22567,7 +21086,6 @@
       <c r="I57" t="n">
         <v>3871336</v>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>ORG_0040</t>
@@ -22581,11 +21099,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -22632,7 +21145,6 @@
           <t>Q113665601</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="b">
         <v>0</v>
       </c>
@@ -22641,11 +21153,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -22663,7 +21170,6 @@
           <t>Colección / Patrimonio</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Nancagua</t>
@@ -22674,20 +21180,9 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="b">
         <v>0</v>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -22726,13 +21221,11 @@
       <c r="H60" t="n">
         <v>-3.7038</v>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Q9256</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="b">
         <v>0</v>
       </c>
@@ -22741,11 +21234,6 @@
           <t>exact</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -22773,27 +21261,17 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>-33.42121365946592</v>
       </c>
       <c r="H61" t="n">
         <v>-70.59154788940485</v>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -22821,27 +21299,17 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>-33.48439393710956</v>
       </c>
       <c r="H62" t="n">
         <v>-70.5182663382937</v>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -22869,27 +21337,17 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>-33.46665877200571</v>
       </c>
       <c r="H63" t="n">
         <v>-70.59598366056628</v>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -22928,20 +21386,11 @@
       <c r="H64" t="n">
         <v>-70.59510712009342</v>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -22969,27 +21418,17 @@
           <t>Chile</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>-33.43714059270721</v>
       </c>
       <c r="H65" t="n">
         <v>-70.62813240660158</v>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -23028,8 +21467,6 @@
       <c r="H66" t="n">
         <v>-58.4531</v>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>ORG_0035</t>
@@ -23053,8 +21490,6 @@
           <t>Facultad de Filosofía y Letras de la Universidad de Buenos Aires, ubicada en Puán 480</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="b">
         <v>0</v>
       </c>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -18686,7 +18686,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fundación TyPA / CAIA UBA (Buenos Aires)</t>
+          <t>Fundación TyPA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -18155,7 +18155,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Universitat de Barcelona (FIMA / Plaça Universitat)</t>
+          <t>FIMA - Facultad de Información y Medios Audiovisuales (Universitat de Barcelona)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>40.4168</v>
+        <v>40.4094</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.7038</v>
+        <v>-3.6954</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.4168,-3.7038</t>
+          <t>40.4094,-3.6954</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>40.4094</v>
+        <v>40.40663337469876</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.6954</v>
+        <v>-3.703136525126451</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -6625,7 +6625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I324"/>
+  <dimension ref="A1:I325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15980,6 +15980,53 @@
       <c r="F324" t="inlineStr">
         <is>
           <t>Jaime Cuevas realizó presentación en X Jornadas arte política (UNIFESP, São Paulo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>REL_0330</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>ORG_0043</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>crm:P355_is_area_of</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ORG_0013</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Promoción del Arte es un área del Ministerio de Educación, Cultura y Deporte</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>ORG_0043</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>ORG_0013</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -15994,7 +16041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17802,6 +17849,38 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>[N/A]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ORG_0043</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PDA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Promoción del Arte</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Departamento / Área Ministerial</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>España</t>
         </is>
       </c>
     </row>

--- a/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
+++ b/data/CV_Dataset_Maestro_Jaime_Cuevas.xlsx
@@ -21305,6 +21305,11 @@
           <t>Q9256</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ORG_0043</t>
+        </is>
+      </c>
       <c r="L60" t="b">
         <v>0</v>
       </c>
@@ -23084,7 +23089,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ORG_0013</t>
+          <t>ORG_0043</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -23110,7 +23115,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.4094,-3.6954</t>
+          <t>40.40663337469876,-3.703136525126451</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
